--- a/Results/Hydrogen/hydrogen photochemical ozone formation results.xlsx
+++ b/Results/Hydrogen/hydrogen photochemical ozone formation results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08525123755514964</v>
+        <v>0.08525123755515017</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05191630204564399</v>
+        <v>0.05191630204564382</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1694755403253595</v>
+        <v>0.1694755403253592</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05191630204564399</v>
+        <v>0.05191630204564382</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05191630204564399</v>
+        <v>0.05191630204564382</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1214463725586999</v>
+        <v>0.1214463725586996</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2389036818016624</v>
+        <v>0.2389036818016615</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05191630204564399</v>
+        <v>0.05191630204564382</v>
       </c>
       <c r="J2" t="n">
-        <v>0.152083184367431</v>
+        <v>0.1520831843674304</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05958216583016976</v>
+        <v>0.05958216583016948</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3681314073785203</v>
+        <v>0.09804254212428259</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002447472661805912</v>
+        <v>0.00244747266180591</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002295295294137583</v>
+        <v>0.002295295294137587</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002447472661805912</v>
+        <v>0.00244747266180591</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002356448963090831</v>
+        <v>0.002356448963090838</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002356448963090831</v>
+        <v>0.002356448963090836</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002444069538033249</v>
+        <v>0.002444069538033234</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002447472661805912</v>
+        <v>0.00244747266180591</v>
       </c>
       <c r="I3" t="n">
         <v>0.002426250318469695</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002447472661805912</v>
+        <v>0.00244747266180591</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002447472661805912</v>
+        <v>0.00244747266180591</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002447472661805912</v>
+        <v>0.00244747266180591</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006429336736010872</v>
+        <v>0.003803844908782871</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003668397372595528</v>
+        <v>0.003668397372595511</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003959518277380238</v>
+        <v>0.003959501764127141</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003513999018221119</v>
+        <v>0.003513999018221125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003779583833363694</v>
+        <v>0.003779583833363699</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006425933612238211</v>
+        <v>0.006425933612238218</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006608690727069811</v>
+        <v>0.006608690727069787</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00640811439267466</v>
+        <v>0.003782622565446658</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003968679755440546</v>
+        <v>0.003968679755440626</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003738987196650064</v>
+        <v>0.003738987196650061</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003903423395847118</v>
+        <v>0.003903423395847117</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004825237718683759</v>
+        <v>0.004825237718683751</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004804015375347553</v>
+        <v>0.004804015375347551</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004825076009250692</v>
+        <v>0.004825076009250697</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004801504756458282</v>
+        <v>0.004801504756458286</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004801504756458282</v>
+        <v>0.004801504756458286</v>
       </c>
       <c r="G5" t="n">
         <v>0.004821834594911101</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004825237718683759</v>
+        <v>0.004825237718683751</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004804015375347553</v>
+        <v>0.004804015375347551</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004825237718683759</v>
+        <v>0.004825237718683751</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004825237718683759</v>
+        <v>0.004825237718683751</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004825237718683759</v>
+        <v>0.004825237718683751</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007433306720444866</v>
+        <v>0.007433306720444851</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0113023291145443</v>
+        <v>0.01130232911454433</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01213195659095291</v>
+        <v>0.01213195659095294</v>
       </c>
       <c r="E6" t="n">
         <v>0.01023810457216025</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007534043511422057</v>
+        <v>0.007534043511422076</v>
       </c>
       <c r="G6" t="n">
-        <v>0.011321587465443</v>
+        <v>0.01132158746544298</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01132499058921572</v>
+        <v>0.01132499058921582</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01130376824587946</v>
+        <v>0.01130376824587941</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01132575541110204</v>
+        <v>0.01132575541110205</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007361016695134261</v>
+        <v>0.007361016695134253</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01539017980220269</v>
+        <v>0.01539017980220264</v>
       </c>
     </row>
     <row r="7">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01299911338313662</v>
+        <v>0.01299911338313663</v>
       </c>
       <c r="C7" t="n">
         <v>0.0162110112499887</v>
@@ -727,25 +727,25 @@
         <v>0.01994196022014042</v>
       </c>
       <c r="F7" t="n">
-        <v>0.016211007876688</v>
+        <v>0.01621100787668795</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01622883046955224</v>
+        <v>0.01622883046955226</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01623223359332488</v>
+        <v>0.01623223359332492</v>
       </c>
       <c r="I7" t="n">
         <v>0.0162110112499887</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01623223359332488</v>
+        <v>0.01623223359332492</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01216115784707214</v>
+        <v>0.01435895151948652</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01623223359332488</v>
+        <v>0.01623223359332492</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01360352976596088</v>
+        <v>0.01360352976596097</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01439248842073948</v>
+        <v>0.01439248842073947</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01184819297339643</v>
+        <v>0.01184819297339642</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01439248842073948</v>
+        <v>0.01439248842073947</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01439248842073948</v>
+        <v>0.01439248842073947</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01292592901904735</v>
+        <v>0.01292592901904736</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01093814382495994</v>
+        <v>0.01093814382495993</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01439248842073948</v>
+        <v>0.01439248842073947</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01239314532046431</v>
+        <v>0.01239314532046432</v>
       </c>
       <c r="K8" t="n">
         <v>0.01420542153658416</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01358922871371969</v>
+        <v>0.01358922871371968</v>
       </c>
     </row>
     <row r="9">
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01440934405941935</v>
+        <v>0.01440934405941936</v>
       </c>
       <c r="C9" t="n">
         <v>0.01475280475580074</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01369450146315277</v>
+        <v>0.01369450146315278</v>
       </c>
       <c r="E9" t="n">
         <v>0.01475280475580074</v>
@@ -810,7 +810,7 @@
         <v>0.01475280475580074</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0141264904045614</v>
+        <v>0.01412649040456141</v>
       </c>
       <c r="H9" t="n">
         <v>0.01332792668297189</v>
@@ -819,13 +819,13 @@
         <v>0.01475280475580074</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01391751894552567</v>
+        <v>0.01391751894552565</v>
       </c>
       <c r="K9" t="n">
         <v>0.01465455528967272</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01440488965310743</v>
+        <v>0.01440488965310744</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007908069937214646</v>
+        <v>0.007908069937214622</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02183012290606765</v>
+        <v>0.02183012290606761</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01625440881031478</v>
+        <v>0.01625440881031481</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02183012290606765</v>
+        <v>0.02183012290606761</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02183012290606765</v>
+        <v>0.02183012290606761</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02461823126793079</v>
+        <v>0.02461823126793045</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01625376362460504</v>
+        <v>0.01625376362460502</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02183012290606765</v>
+        <v>0.02183012290606761</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06394229831931378</v>
+        <v>0.06394229831931381</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01930124217881781</v>
+        <v>0.01930124217881787</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01531912100860658</v>
+        <v>0.01356804827290346</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001901277892631339</v>
+        <v>0.001901277892631337</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001785357883627893</v>
+        <v>0.001785357883627884</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001901277892631339</v>
+        <v>0.001901277892631337</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001830024318261662</v>
+        <v>0.001830024318261652</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001830024318261662</v>
+        <v>0.001830024318261652</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001899313657202716</v>
+        <v>0.001899313657202712</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001901277892631339</v>
+        <v>0.001901277892631337</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001888896264506871</v>
+        <v>0.001888896264506861</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001901277892631339</v>
+        <v>0.001901277892631337</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001901277892631339</v>
+        <v>0.001901277892631337</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001901277892631339</v>
+        <v>0.001901277892631337</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004604037442183371</v>
+        <v>0.004604037442183369</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002886061585157237</v>
+        <v>0.002886061585157213</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002906137835450512</v>
+        <v>0.004642483195929393</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002759529601853778</v>
+        <v>0.002759529601853771</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002911460271440281</v>
+        <v>0.002911460271440275</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004602073206754741</v>
+        <v>0.002920989171488856</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004714557885389625</v>
+        <v>0.004714557885389615</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002910571778793009</v>
+        <v>0.002910571778793</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004647338311370387</v>
+        <v>0.004647338311370386</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002928626416012577</v>
+        <v>0.002928626416012615</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002924052132511707</v>
+        <v>0.002924052132511706</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00344826235761008</v>
+        <v>0.003448262357610072</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003435880729485615</v>
+        <v>0.0034358807294856</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003448128376123631</v>
+        <v>0.003448128376123624</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003433621171084126</v>
+        <v>0.003433621171084113</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003433621171084126</v>
+        <v>0.003433621171084113</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003446298122181458</v>
+        <v>0.00344629812218145</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00344826235761008</v>
+        <v>0.003448262357610072</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003435880729485615</v>
+        <v>0.0034358807294856</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00344826235761008</v>
+        <v>0.003448262357610072</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00344826235761008</v>
+        <v>0.003448262357610072</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00344826235761008</v>
+        <v>0.003448262357610072</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005250001058071092</v>
+        <v>0.005250001058071073</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007882072845136815</v>
+        <v>0.007882072845136784</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008444584332906064</v>
+        <v>0.00844458433290605</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007158561448354334</v>
+        <v>0.007158561448354307</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005320223382761074</v>
+        <v>0.005320223382761057</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007893968854398312</v>
+        <v>0.007893968854398284</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007895933089826994</v>
+        <v>0.007895933089826982</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007883551461702462</v>
+        <v>0.007883551461702436</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007896453086672727</v>
+        <v>0.00789645308667271</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005200851512617842</v>
+        <v>0.005200851512617828</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01065983034182301</v>
+        <v>0.01065983034182299</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006788592891581355</v>
+        <v>0.006788592891581333</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00835336682333261</v>
+        <v>0.008353366823332584</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008365749602778255</v>
+        <v>0.008365749602778231</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01017337156806549</v>
+        <v>0.01017337156806546</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008353366526505467</v>
+        <v>0.008353366526505444</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008363784216028458</v>
+        <v>0.008363784216028434</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008365748451457079</v>
+        <v>0.008365748451457067</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00835336682333261</v>
+        <v>0.008353366823332584</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008365748451457079</v>
+        <v>0.008365748451457067</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007451938810338422</v>
+        <v>0.007451938810338396</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008365748451457079</v>
+        <v>0.008365748451457067</v>
       </c>
     </row>
     <row r="8">
@@ -1169,7 +1169,7 @@
         <v>0.01417143938663255</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01442287270658021</v>
+        <v>0.01442287270658022</v>
       </c>
       <c r="I8" t="n">
         <v>0.0140928348814209</v>
@@ -1178,10 +1178,10 @@
         <v>0.01329049151180535</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01427803548980266</v>
+        <v>0.01427803548980267</v>
       </c>
       <c r="L8" t="n">
-        <v>0.014437833136543</v>
+        <v>0.01449694056989674</v>
       </c>
     </row>
     <row r="9">
@@ -1206,10 +1206,10 @@
         <v>0.01413130185005036</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01424135160433577</v>
+        <v>0.01424135160433578</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01434540998121629</v>
+        <v>0.0143454099812163</v>
       </c>
       <c r="I9" t="n">
         <v>0.01413130185005036</v>
@@ -1218,7 +1218,7 @@
         <v>0.01388445618876643</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01428614804722492</v>
+        <v>0.01428614804722494</v>
       </c>
       <c r="L9" t="n">
         <v>0.01435143359609451</v>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02017937845475279</v>
+        <v>0.02017937845475284</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03667394993898702</v>
+        <v>0.03667394993898707</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05533204121894651</v>
+        <v>0.05533204121894646</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02869525037621008</v>
+        <v>0.02869525037621015</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02869525037621008</v>
+        <v>0.02869525037621015</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05067688236220614</v>
+        <v>0.0506768823622061</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1011655714639695</v>
+        <v>0.1011655714639694</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02869525037621008</v>
+        <v>0.02869525037621015</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09703422757538757</v>
+        <v>0.09703422757538765</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03056654682833799</v>
+        <v>0.03056654682833806</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0827975916561062</v>
+        <v>0.08279759165610616</v>
       </c>
     </row>
     <row r="3">
@@ -1350,28 +1350,28 @@
         <v>0.002012644970363203</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00178557673610704</v>
+        <v>0.001785576736107039</v>
       </c>
       <c r="D3" t="n">
         <v>0.002012644970363203</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001909039259144134</v>
+        <v>0.001909039259144128</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001909039259144136</v>
+        <v>0.001909039259144129</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002008401807504673</v>
+        <v>0.002008401807504666</v>
       </c>
       <c r="H3" t="n">
         <v>0.002012644970363203</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001985351979532624</v>
+        <v>0.00198535197953261</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002012644970363201</v>
+        <v>0.002012644970363203</v>
       </c>
       <c r="K3" t="n">
         <v>0.002012644970363203</v>
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005010039419114079</v>
+        <v>0.003038528291032711</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002979706148378691</v>
+        <v>0.002979706148378686</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003069370145652064</v>
+        <v>0.003069356272315258</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002826356149524531</v>
+        <v>0.002826356149524532</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003008070306203201</v>
+        <v>0.003008070306203202</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005005796256255549</v>
+        <v>0.005005796256255545</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005199754867077167</v>
+        <v>0.00519975486707717</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004982746428283495</v>
+        <v>0.004982746428283496</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005053444591619023</v>
+        <v>0.005053444591619027</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002999972742191885</v>
+        <v>0.002999972742191872</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003051520541824135</v>
+        <v>0.003051520541824138</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003918566515788874</v>
+        <v>0.003918566515788882</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003915757157897681</v>
+        <v>0.003915757157897678</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003918432204494796</v>
+        <v>0.003918432204494803</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003887658126519125</v>
+        <v>0.003887658126519122</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003887658126519125</v>
+        <v>0.003887658126519122</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003914323352930346</v>
+        <v>0.003914323352930347</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003918566515788874</v>
+        <v>0.003918566515788882</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003891273524958292</v>
+        <v>0.003891273524958289</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003918566515788874</v>
+        <v>0.003918566515788882</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003918566515788874</v>
+        <v>0.003918566515788882</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003918566515788874</v>
+        <v>0.003918566515788882</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006078540350645987</v>
+        <v>0.006078540350645985</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0092685552300801</v>
+        <v>0.009268555230104981</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009936634555679544</v>
+        <v>0.009936634555679525</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008370385330207565</v>
+        <v>0.008370385330207553</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006150462785790674</v>
+        <v>0.006150462785790659</v>
       </c>
       <c r="G6" t="n">
         <v>0.009269785976225606</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009274029139088535</v>
+        <v>0.009274029139088525</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009246736148253557</v>
+        <v>0.009246736148253545</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009274657139239228</v>
+        <v>0.009274657139239214</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006019182506322549</v>
+        <v>0.006019182506322544</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01261198437632391</v>
+        <v>0.01261198437632388</v>
       </c>
     </row>
     <row r="7">
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008585366257043741</v>
+        <v>0.008585366257043734</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01066667923497317</v>
+        <v>0.01066667923497316</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01066948954978978</v>
+        <v>0.01066948954978979</v>
       </c>
       <c r="E7" t="n">
         <v>0.01304722769512771</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01064219419647246</v>
+        <v>0.01064219419647245</v>
       </c>
       <c r="G7" t="n">
         <v>0.01066524543000582</v>
@@ -1528,13 +1528,13 @@
         <v>0.01066948859286436</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01064219560203377</v>
+        <v>0.01064219560203376</v>
       </c>
       <c r="J7" t="n">
         <v>0.01066948859286436</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008045206309530628</v>
+        <v>0.009461940328988993</v>
       </c>
       <c r="L7" t="n">
         <v>0.01066948859286436</v>
@@ -1550,7 +1550,7 @@
         <v>0.01303044872696621</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003781841388241001</v>
+        <v>0.003781841388241002</v>
       </c>
       <c r="D8" t="n">
         <v>0.03113757327166265</v>
@@ -1562,16 +1562,16 @@
         <v>0.01262266919288654</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01278784280584176</v>
+        <v>0.01278784280584175</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03035010030436468</v>
+        <v>0.0303501003043647</v>
       </c>
       <c r="I8" t="n">
         <v>0.01262266919288654</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01763412868052223</v>
+        <v>0.01763412868052224</v>
       </c>
       <c r="K8" t="n">
         <v>0.01701578953077497</v>
@@ -1590,31 +1590,31 @@
         <v>0.01302502993078951</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004136309827476039</v>
+        <v>0.004136309827476033</v>
       </c>
       <c r="D9" t="n">
         <v>0.03132523069330777</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01274133155806041</v>
+        <v>0.0127413315580604</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01274133155806041</v>
+        <v>0.0127413315580604</v>
       </c>
       <c r="G9" t="n">
         <v>0.013181572756307</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03100634608542752</v>
+        <v>0.03100634608542753</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01274133155806041</v>
+        <v>0.0127413315580604</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01852565944286497</v>
+        <v>0.01852565944286498</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01709261818618093</v>
+        <v>0.01709261818618094</v>
       </c>
       <c r="L9" t="n">
         <v>0.02108445027286289</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0115010635752005</v>
+        <v>0.01150106357520047</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02501378776389329</v>
+        <v>0.02501378776389319</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03803109370171223</v>
+        <v>0.03803109370171219</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01784971344082624</v>
+        <v>0.01784971344082617</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01784971344082624</v>
+        <v>0.01784971344082617</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03210595431697847</v>
+        <v>0.0321059543169782</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05244000961871279</v>
+        <v>0.05244000961871276</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01784971344082624</v>
+        <v>0.01784971344082617</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06532979888783931</v>
+        <v>0.06532979888783927</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01664020731105281</v>
+        <v>0.01664020731105277</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03330052889549233</v>
+        <v>0.03330052889549228</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001880076817890263</v>
+        <v>0.001880076817890242</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001709940213403884</v>
+        <v>0.001709940213403883</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001880076817890263</v>
+        <v>0.001880076817890242</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001906983319205215</v>
+        <v>0.001906983319205205</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001906983319205215</v>
+        <v>0.001906983319205211</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001876406328541575</v>
+        <v>0.001876406328541559</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001880076817890263</v>
+        <v>0.001880076817890242</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001856492705292009</v>
+        <v>0.00185649270529201</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001880076817890263</v>
+        <v>0.001880076817890241</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001880076817890263</v>
+        <v>0.001880076817890242</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001880076817890263</v>
+        <v>0.001880076817890242</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004643165569899054</v>
+        <v>0.004643165569899018</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002819648132401414</v>
+        <v>0.002819648132401369</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002888481209856675</v>
+        <v>0.004670205257941746</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002690183747137603</v>
+        <v>0.002690183747137601</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002846242241834367</v>
+        <v>0.002846242241834356</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002859128201048189</v>
+        <v>0.002859128201048171</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004801418038413175</v>
+        <v>0.004801418038413156</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002839214577798619</v>
+        <v>0.002839214577798611</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002983442229743649</v>
+        <v>0.002983442229743633</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002842155469164774</v>
+        <v>0.002842155469164762</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002859553858728021</v>
+        <v>0.002859553858727997</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003579249873729454</v>
+        <v>0.003579249873729446</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003576851418844061</v>
+        <v>0.00357685141884406</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003579122236192861</v>
+        <v>0.003579122236192866</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003553149367682022</v>
+        <v>0.003553149367682013</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003553149367682022</v>
+        <v>0.003553149367682013</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003575579384380763</v>
+        <v>0.003575579384380765</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003579249873729454</v>
+        <v>0.003579249873729446</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003555665761131205</v>
+        <v>0.003555665761131203</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003579249873729454</v>
+        <v>0.003579249873729446</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003579249873729454</v>
+        <v>0.003579249873729446</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003579249873729454</v>
+        <v>0.003579249873729446</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005560112600593394</v>
+        <v>0.005560112600593357</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008449911095183756</v>
+        <v>0.008449911095207558</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009054056466183551</v>
+        <v>0.009054056466183529</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007637424993152903</v>
+        <v>0.007637424993152885</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005626834983157094</v>
+        <v>0.005626834983157082</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008450321279724411</v>
+        <v>0.008450321279724402</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00845399176908058</v>
+        <v>0.008453991769080548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008430407656474849</v>
+        <v>0.008430407656474825</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008454560494587933</v>
+        <v>0.008454560494587919</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005506357309777988</v>
+        <v>0.005506357309777947</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01147689053836785</v>
+        <v>0.0114768905383678</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007225837037737253</v>
+        <v>0.007225837037737225</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008943673303064895</v>
+        <v>0.008943673303064883</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008946072789159059</v>
+        <v>0.008946072789159041</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01090760198602966</v>
+        <v>0.01090760198602964</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00892248685833511</v>
+        <v>0.008922486858335082</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008942401268601602</v>
+        <v>0.008942401268601579</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008946071757950284</v>
+        <v>0.00894607175795026</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008922487645352032</v>
+        <v>0.008922487645352022</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008946071757950284</v>
+        <v>0.00894607175795026</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007949361438898187</v>
+        <v>0.007949361438898163</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008946071757950284</v>
+        <v>0.00894607175795026</v>
       </c>
     </row>
     <row r="8">
@@ -1946,34 +1946,34 @@
         <v>0.01314572082114871</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003913787417192318</v>
+        <v>0.003913787417192319</v>
       </c>
       <c r="D8" t="n">
         <v>0.03137360797477601</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01275270811944802</v>
+        <v>0.01275270811944803</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01275270811944802</v>
+        <v>0.01275270811944803</v>
       </c>
       <c r="G8" t="n">
         <v>0.01308022395466229</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03116878930581578</v>
+        <v>0.03116878930581577</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01275270811944802</v>
+        <v>0.01275270811944803</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01819918272365592</v>
+        <v>0.0181991827236559</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01721536624281849</v>
+        <v>0.01721536624281847</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02078927510190937</v>
+        <v>0.02078927510190936</v>
       </c>
     </row>
     <row r="9">
@@ -1986,10 +1986,10 @@
         <v>0.01303452949330743</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004133037772227437</v>
+        <v>0.004133037772227439</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03135518464994278</v>
+        <v>0.03135518464994279</v>
       </c>
       <c r="E9" t="n">
         <v>0.01273939356800504</v>
@@ -1998,22 +1998,22 @@
         <v>0.01273939356800504</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01325216225025392</v>
+        <v>0.01325216225025391</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03127275092032231</v>
+        <v>0.0312727509203223</v>
       </c>
       <c r="I9" t="n">
         <v>0.01273939356800504</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01872641483669775</v>
+        <v>0.01872641483669772</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01711650056800175</v>
+        <v>0.01711650056800174</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02080971748765291</v>
+        <v>0.0208097174876529</v>
       </c>
     </row>
   </sheetData>
@@ -2102,34 +2102,34 @@
         <v>0.006317282618925005</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01850849819421502</v>
+        <v>0.01850849819421504</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02501493141887258</v>
+        <v>0.0250149314188725</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008255769111006471</v>
+        <v>0.008255769111006402</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008255769111006471</v>
+        <v>0.008255769111006402</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0202834199597541</v>
+        <v>0.02028341995975397</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02814118649697364</v>
+        <v>0.02814118649697358</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008255769111006471</v>
+        <v>0.008255769111006402</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03756974007875737</v>
+        <v>0.03756974007875735</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009371036070201445</v>
+        <v>0.00937103607020145</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01510323359316561</v>
+        <v>0.0151032335931656</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001804573889659522</v>
+        <v>0.001804573889659526</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001660257834835547</v>
+        <v>0.001660257834835548</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001804573889659522</v>
+        <v>0.001804573889659526</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001809346691486445</v>
+        <v>0.00180934669148644</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001809346691486445</v>
+        <v>0.00180934669148644</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001801528345550215</v>
+        <v>0.00180152834555022</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001804573889659522</v>
+        <v>0.001804573889659526</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001785120299744231</v>
+        <v>0.001785120299744236</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001804573889659522</v>
+        <v>0.001804573889659526</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001804573889659522</v>
+        <v>0.001804573889659526</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001804573889659522</v>
+        <v>0.001804573889659526</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004474298114014365</v>
+        <v>0.002761257913489919</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00273051723512333</v>
+        <v>0.002730517235123053</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002770651306005332</v>
+        <v>0.002770651306004955</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002590899613561095</v>
+        <v>0.002590899613561105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00274556486894201</v>
+        <v>0.002745564868942008</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00275821236938061</v>
+        <v>0.004471252569905063</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004615790281404464</v>
+        <v>0.004615790281404479</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002741804323574627</v>
+        <v>0.004454844524099079</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002874187376789217</v>
+        <v>0.004497648341420711</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002752819996364716</v>
+        <v>0.002752819996364723</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002752360384827826</v>
+        <v>0.002752360384828006</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003424328745116834</v>
+        <v>0.003424328745116838</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003422281266917224</v>
+        <v>0.003422281266917215</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00342420108151457</v>
+        <v>0.003424201081514569</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003402070175125494</v>
+        <v>0.003402070175125488</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003402070175125494</v>
+        <v>0.003402070175125488</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003421283201007548</v>
+        <v>0.003421283201007533</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003424328745116834</v>
+        <v>0.003424328745116838</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003404875155201562</v>
+        <v>0.003404875155201552</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003424328745116834</v>
+        <v>0.003424328745116838</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003424328745116834</v>
+        <v>0.003424328745116838</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003424328745116834</v>
+        <v>0.003424328745116838</v>
       </c>
     </row>
     <row r="6">
@@ -2259,34 +2259,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005351058077064681</v>
+        <v>0.005351058077064662</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008137412681727659</v>
+        <v>0.008137412681704074</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008720040708066241</v>
+        <v>0.008720040708066238</v>
       </c>
       <c r="E6" t="n">
         <v>0.007357042547622488</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0054184580560153</v>
+        <v>0.005418458056015299</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008138391837805136</v>
+        <v>0.008138391837805126</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00814143738192169</v>
+        <v>0.008141437381921687</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008121983791999139</v>
+        <v>0.00812198379199913</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008141985766825729</v>
+        <v>0.008141985766825741</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005299225349344412</v>
+        <v>0.005299225349344408</v>
       </c>
       <c r="L6" t="n">
         <v>0.01105622188921168</v>
@@ -2302,34 +2302,34 @@
         <v>0.006461936229051304</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007981629278335085</v>
+        <v>0.007981629278335073</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007983677739699931</v>
+        <v>0.007983677739699923</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009720279654942432</v>
+        <v>0.009720279654942416</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007964222604185696</v>
+        <v>0.007964222604185686</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007980631212425407</v>
+        <v>0.007980631212425393</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0079836767565347</v>
+        <v>0.007983676756534695</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007964223166619421</v>
+        <v>0.007964223166619409</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0079836767565347</v>
+        <v>0.007983676756534695</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00706620292731368</v>
+        <v>0.006067533547894487</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0079836767565347</v>
+        <v>0.007983676756534695</v>
       </c>
     </row>
     <row r="8">
@@ -2339,34 +2339,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01321442097115582</v>
+        <v>0.01321442097115584</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003973469957205046</v>
+        <v>0.003973469957205045</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03158550570000036</v>
+        <v>0.03158550570000035</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0126863428218265</v>
+        <v>0.01268634282182651</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0126863428218265</v>
+        <v>0.01268634282182651</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01318137390588794</v>
+        <v>0.01318137390588795</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03158611522285858</v>
+        <v>0.03158611522285859</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0126863428218265</v>
+        <v>0.01268634282182651</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01801283402822753</v>
+        <v>0.01801283402822754</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01733040891645333</v>
+        <v>0.01733040891645334</v>
       </c>
       <c r="L8" t="n">
         <v>0.02105067518007834</v>
@@ -2379,19 +2379,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01303174530828395</v>
+        <v>0.01303174530828393</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004103028441628766</v>
+        <v>0.004103028441628763</v>
       </c>
       <c r="D9" t="n">
         <v>0.03138089396196921</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01254069352182793</v>
+        <v>0.01254069352182794</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01254069352182793</v>
+        <v>0.01254069352182794</v>
       </c>
       <c r="G9" t="n">
         <v>0.01319047266448171</v>
@@ -2400,7 +2400,7 @@
         <v>0.0313816518727442</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01254069352182793</v>
+        <v>0.01254069352182794</v>
       </c>
       <c r="J9" t="n">
         <v>0.01817202710165415</v>
@@ -2409,7 +2409,7 @@
         <v>0.01712821200148185</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02084553529335622</v>
+        <v>0.02084553529335621</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008388538039507037</v>
+        <v>0.008388538039507036</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006137795201643184</v>
+        <v>0.006137795201643195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03134147627226714</v>
+        <v>0.03134147627226712</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01528411396059478</v>
+        <v>0.01528411396059481</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01528411396059478</v>
+        <v>0.01528411396059481</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03339442840766515</v>
+        <v>0.03339442840766498</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07933456951320422</v>
+        <v>0.07933456951320431</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01528411396059478</v>
+        <v>0.01528411396059481</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08962499778150922</v>
+        <v>0.08962499778150901</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02172253553758009</v>
+        <v>0.02172253553758004</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07232629067457072</v>
+        <v>0.07232629067457073</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001886809246219492</v>
+        <v>0.001886809246219494</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001648299554604902</v>
+        <v>0.001648299554604904</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001886809246219492</v>
+        <v>0.001886809246219494</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001790817847928813</v>
+        <v>0.00179081784792881</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001790817847928811</v>
+        <v>0.00179081784792881</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001882715376070063</v>
+        <v>0.00188271537607006</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001886809246219492</v>
+        <v>0.001886809246219494</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001860457238970536</v>
+        <v>0.001860457238970533</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001886809246219492</v>
+        <v>0.001886809246219494</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001886809246219492</v>
+        <v>0.001886809246219494</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001886809246219492</v>
+        <v>0.001886809246219494</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004702221368349145</v>
+        <v>0.002841669375381188</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002753579018363832</v>
+        <v>0.002753579018363816</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00285440932247011</v>
+        <v>0.002854409322470075</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002639821923523737</v>
+        <v>0.002639821923523765</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002812360300715148</v>
+        <v>0.002812360300715146</v>
       </c>
       <c r="G4" t="n">
         <v>0.002837575505231753</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004882068985960431</v>
+        <v>0.00488206898596043</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004675869361100181</v>
+        <v>0.002815317368132226</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004740643537151609</v>
+        <v>0.004740643537151651</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002815375813007792</v>
+        <v>0.002815375813007793</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002855394401103263</v>
+        <v>0.002855394401103266</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003677748585038003</v>
+        <v>0.003677748585037997</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003674744582635021</v>
+        <v>0.003674744582635017</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003677616607705856</v>
+        <v>0.003677616607705859</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003649171432922777</v>
+        <v>0.00364917143292277</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003649171432922777</v>
+        <v>0.00364917143292277</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003673654714888571</v>
+        <v>0.003673654714888568</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003677748585038003</v>
+        <v>0.003677748585037997</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003651396577789044</v>
+        <v>0.003651396577789039</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003677748585038003</v>
+        <v>0.003677748585037997</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003677748585038003</v>
+        <v>0.003677748585037997</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003677748585038003</v>
+        <v>0.003677748585037997</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005765691605476731</v>
+        <v>0.005765691605476726</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008813260737671809</v>
+        <v>0.008813260737671795</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009450472131752874</v>
+        <v>0.00945047213175286</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007955349721173509</v>
+        <v>0.007955349721173503</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005834832733933203</v>
+        <v>0.005834832733933193</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008813538469241582</v>
+        <v>0.008813538469241577</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008817632339394733</v>
+        <v>0.00881763233939472</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008791280332142064</v>
+        <v>0.008791280332142045</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008818232128258427</v>
+        <v>0.008818232128258418</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005709000239961958</v>
+        <v>0.005709000239961952</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01200563963040368</v>
+        <v>0.01200563963040365</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00795124152515996</v>
+        <v>0.007951241525159955</v>
       </c>
       <c r="C7" t="n">
         <v>0.009881029632084769</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009884034511382127</v>
+        <v>0.009884034511382126</v>
       </c>
       <c r="E7" t="n">
         <v>0.01208808216605156</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009857680534252563</v>
+        <v>0.009857680534252556</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009879939764338324</v>
+        <v>0.009879939764338323</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009884033634487761</v>
+        <v>0.009884033634487751</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009857681627238787</v>
+        <v>0.009857681627238775</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009884033634487761</v>
+        <v>0.009884033634487751</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007450303139400721</v>
+        <v>0.007450303139400719</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009884033634487761</v>
+        <v>0.009884033634487751</v>
       </c>
     </row>
     <row r="8">
@@ -2738,31 +2738,31 @@
         <v>0.01297647063303007</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004321332306626832</v>
+        <v>0.00432133230662683</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03154135758051136</v>
+        <v>0.03154135758051137</v>
       </c>
       <c r="E8" t="n">
         <v>0.01280499326453413</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01280499326453413</v>
+        <v>0.01280499326453414</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01304427234481765</v>
+        <v>0.01304427234481764</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03064465934144673</v>
+        <v>0.03064465934144672</v>
       </c>
       <c r="I8" t="n">
         <v>0.01280499326453413</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01768145314740406</v>
+        <v>0.01768145314740405</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01708647292303036</v>
+        <v>0.01708647292303034</v>
       </c>
       <c r="L8" t="n">
         <v>0.02062228674485029</v>
@@ -2778,7 +2778,7 @@
         <v>0.01282030330955895</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004272062263729212</v>
+        <v>0.00427206226372921</v>
       </c>
       <c r="D9" t="n">
         <v>0.03140370114696397</v>
@@ -2799,13 +2799,13 @@
         <v>0.01274470477401195</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01847926407473056</v>
+        <v>0.01847926407473055</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0170456883969196</v>
+        <v>0.01704568839691959</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02107513776456154</v>
+        <v>0.02107513776456153</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005198466382038587</v>
+        <v>0.005198466382038588</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005127845214557038</v>
+        <v>0.005127845214557044</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007112503526792918</v>
+        <v>0.00711250352679292</v>
       </c>
       <c r="E2" t="n">
-        <v>0.009081793582635802</v>
+        <v>0.009081793582635845</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009081793582635802</v>
+        <v>0.009081793582635845</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009517418256800646</v>
+        <v>0.009517418256800671</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01047196825025019</v>
+        <v>0.01047196825025021</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009081793582635802</v>
+        <v>0.009081793582635845</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03248225024539839</v>
+        <v>0.03248225024539838</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007080222848930489</v>
+        <v>0.007080222848930499</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0144791309993898</v>
+        <v>0.01447913099938981</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00175466993829652</v>
+        <v>0.001754669938296525</v>
       </c>
       <c r="C3" t="n">
         <v>0.001583517109753739</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00175466993829652</v>
+        <v>0.001754669938296525</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00179696435656098</v>
+        <v>0.00179696435656099</v>
       </c>
       <c r="F3" t="n">
         <v>0.00179696435656099</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001751525319613147</v>
+        <v>0.001751525319613145</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00175466993829652</v>
+        <v>0.001754669938296525</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001734429856190033</v>
+        <v>0.001734429856190042</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00175466993829652</v>
+        <v>0.001754669938296525</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00175466993829652</v>
+        <v>0.001754669938296525</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00175466993829652</v>
+        <v>0.001754669938296525</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002672961301823675</v>
+        <v>0.002672961301823669</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002626612840408717</v>
+        <v>0.002626612840408738</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004340880291037979</v>
+        <v>0.002669955821201308</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002527037261642954</v>
+        <v>0.002527037261642961</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002661118796918101</v>
+        <v>0.002661118796918107</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002669816683140302</v>
+        <v>0.004320491282586176</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004462816965655167</v>
+        <v>0.004462816965655172</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002652721219717197</v>
+        <v>0.004303395819163073</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002778857106846743</v>
+        <v>0.002778857106846744</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002666931222593025</v>
+        <v>0.002666931222593022</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002666080672504623</v>
+        <v>0.002666080672504581</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003291057149198617</v>
+        <v>0.00329105714919862</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003289065050191361</v>
+        <v>0.003289065050191362</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00329093226287997</v>
+        <v>0.003290932262879975</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003269534039581208</v>
+        <v>0.003269534039581222</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003269534039581208</v>
+        <v>0.003269534039581222</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003287912530515245</v>
+        <v>0.003287912530515249</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003291057149198617</v>
+        <v>0.00329105714919862</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003270817067092135</v>
+        <v>0.003270817067092143</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003291057149198617</v>
+        <v>0.00329105714919862</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003291057149198617</v>
+        <v>0.00329105714919862</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003291057149198617</v>
+        <v>0.00329105714919862</v>
       </c>
     </row>
     <row r="6">
@@ -3051,16 +3051,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005161504581047072</v>
+        <v>0.005161504581047077</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007845751202898269</v>
+        <v>0.007845751202898276</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008405414219182675</v>
+        <v>0.008405414219182674</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007092722057283988</v>
+        <v>0.007092722057283985</v>
       </c>
       <c r="F6" t="n">
         <v>0.005225740609654746</v>
@@ -3072,16 +3072,16 @@
         <v>0.007848291457842549</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007828051375730427</v>
+        <v>0.007828051375730432</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007848819483759893</v>
+        <v>0.007848819483759895</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005111596135872943</v>
+        <v>0.005111596135872939</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01065486501166153</v>
+        <v>0.01065486501166152</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00653542741497775</v>
+        <v>0.006535427414977753</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008082833249957252</v>
+        <v>0.008082833249957257</v>
       </c>
       <c r="D7" t="n">
         <v>0.008084826294991481</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009852558173167396</v>
+        <v>0.009852558173167408</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008064585017132702</v>
+        <v>0.008064585017132706</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00808168073028113</v>
+        <v>0.008081680730281133</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008084825348964498</v>
+        <v>0.008084825348964503</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008064585266858024</v>
+        <v>0.00806458526685803</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008084825348964498</v>
+        <v>0.008084825348964503</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007187098498952583</v>
+        <v>0.006133856538332408</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008084825348964498</v>
+        <v>0.008084825348964503</v>
       </c>
     </row>
     <row r="8">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01287524622692725</v>
+        <v>0.01287524622692727</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004245569685165851</v>
+        <v>0.004245569685165849</v>
       </c>
       <c r="D8" t="n">
         <v>0.03196251147943562</v>
@@ -3146,7 +3146,7 @@
         <v>0.01281992243581753</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01344455845152681</v>
+        <v>0.01344455845152682</v>
       </c>
       <c r="H8" t="n">
         <v>0.0319066131772968</v>
@@ -3155,10 +3155,10 @@
         <v>0.01281992243581753</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01877521331686113</v>
+        <v>0.01877521331686112</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01726249802772416</v>
+        <v>0.01726249802772419</v>
       </c>
       <c r="L8" t="n">
         <v>0.02106109238040337</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01268281693799129</v>
+        <v>0.0126828169379913</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00418802342048617</v>
+        <v>0.004188023420486172</v>
       </c>
       <c r="D9" t="n">
         <v>0.03150035813141605</v>
@@ -3189,7 +3189,7 @@
         <v>0.01330279899261397</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03147775799525564</v>
+        <v>0.03147775799525565</v>
       </c>
       <c r="I9" t="n">
         <v>0.01268422928757309</v>
@@ -3198,10 +3198,10 @@
         <v>0.01885482905251635</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01702967172765272</v>
+        <v>0.01702967172765275</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02084855014082518</v>
+        <v>0.02084855014082519</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00478760113840273</v>
+        <v>0.004787601138402727</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005026994911116977</v>
+        <v>0.005026994911117034</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006280820107376119</v>
+        <v>0.006280820107376111</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007059053534686532</v>
+        <v>0.007059053534686497</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007059053534686532</v>
+        <v>0.007059053534686497</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006272650339458404</v>
+        <v>0.006272650339458353</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007278489898038326</v>
+        <v>0.007278489898038309</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007059053534686532</v>
+        <v>0.007059053534686497</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01065386674301334</v>
+        <v>0.01065386674301336</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004726061164590067</v>
+        <v>0.004726061164590055</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0063418814741889</v>
+        <v>0.006341881474188891</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00171526000403662</v>
+        <v>0.001715260004036619</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00156716416300896</v>
+        <v>0.001567164163008961</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00171526000403662</v>
+        <v>0.001715260004036619</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001735374915828846</v>
+        <v>0.00173537491582884</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001735374915828846</v>
+        <v>0.00173537491582884</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001712698551005855</v>
+        <v>0.001712698551005935</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00171526000403662</v>
+        <v>0.001715260004036619</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001698887514830011</v>
+        <v>0.001698887514830149</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00171526000403662</v>
+        <v>0.001715260004036619</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00171526000403662</v>
+        <v>0.001715260004036619</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00171526000403662</v>
+        <v>0.001715260004036619</v>
       </c>
     </row>
     <row r="4">
@@ -3370,34 +3370,34 @@
         <v>0.004268627390457136</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002610500526610471</v>
+        <v>0.002610500526610462</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002637706488720835</v>
+        <v>0.002637706488720838</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002501700226981076</v>
+        <v>0.002501700226981079</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002636958291846581</v>
+        <v>0.00263695829184658</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004266065937426373</v>
+        <v>0.004266065937426369</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004395333062943364</v>
+        <v>0.00439533306294336</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002630964937101157</v>
+        <v>0.00263096493710115</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004286838261771844</v>
+        <v>0.004286838261771842</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002648745385733795</v>
+        <v>0.002648745385733776</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002636162290615633</v>
+        <v>0.002636162290615634</v>
       </c>
     </row>
     <row r="5">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003183400990814462</v>
+        <v>0.003183400990814461</v>
       </c>
       <c r="C5" t="n">
         <v>0.003181624251000152</v>
@@ -3416,28 +3416,28 @@
         <v>0.003183275443933316</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003165521453556899</v>
+        <v>0.003165521453556894</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003165521453556899</v>
+        <v>0.003165521453556894</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003180839537783696</v>
+        <v>0.003180839537783694</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003183400990814462</v>
+        <v>0.003183400990814461</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003167028501607853</v>
+        <v>0.003167028501607847</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003183400990814462</v>
+        <v>0.003183400990814461</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003183400990814462</v>
+        <v>0.003183400990814461</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003183400990814462</v>
+        <v>0.003183400990814461</v>
       </c>
     </row>
     <row r="6">
@@ -3447,34 +3447,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005009888663704417</v>
+        <v>0.005009888663704419</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007606034390875913</v>
+        <v>0.007606034390875907</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008147446270319993</v>
+        <v>0.008147446270319983</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006880771545345501</v>
+        <v>0.006880771545345486</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005075066828264372</v>
+        <v>0.005075066828264366</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007606027403659819</v>
+        <v>0.007606027403659813</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007608588856696109</v>
+        <v>0.007608588856696104</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007592216367483982</v>
+        <v>0.007592216367483973</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007609099571085798</v>
+        <v>0.007609099571085791</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004961616473902798</v>
+        <v>0.004961616473902795</v>
       </c>
       <c r="L6" t="n">
         <v>0.0103231485036184</v>
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006031524560798189</v>
+        <v>0.006031524560798187</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007443379053544839</v>
+        <v>0.007443379053544841</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007445156657496269</v>
+        <v>0.007445156657496268</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009060084258291318</v>
+        <v>0.009060084258291317</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007428783067693082</v>
+        <v>0.007428783067693085</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007442594340328379</v>
+        <v>0.007442594340328376</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007445155793359145</v>
+        <v>0.007445155793359142</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007428783304152531</v>
+        <v>0.007428783304152529</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007445155793359145</v>
+        <v>0.007445155793359142</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006626092668907767</v>
+        <v>0.006592862208258009</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007445155793359145</v>
+        <v>0.007445155793359142</v>
       </c>
     </row>
     <row r="8">
@@ -3527,10 +3527,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01269249558780867</v>
+        <v>0.01269249558780865</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004184656732816538</v>
+        <v>0.004184656732816539</v>
       </c>
       <c r="D8" t="n">
         <v>0.0319222429505335</v>
@@ -3542,7 +3542,7 @@
         <v>0.01260147207500169</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01336079773555992</v>
+        <v>0.0133607977355599</v>
       </c>
       <c r="H8" t="n">
         <v>0.03191482320120554</v>
@@ -3551,7 +3551,7 @@
         <v>0.01260147207500169</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0184740040817822</v>
+        <v>0.01847400408178218</v>
       </c>
       <c r="K8" t="n">
         <v>0.01730800078548638</v>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01249735257578452</v>
+        <v>0.01249735257578451</v>
       </c>
       <c r="C9" t="n">
         <v>0.004126695335222626</v>
@@ -3582,7 +3582,7 @@
         <v>0.01244101569445684</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01317603367184915</v>
+        <v>0.01317603367184914</v>
       </c>
       <c r="H9" t="n">
         <v>0.03144614895959225</v>
@@ -3591,10 +3591,10 @@
         <v>0.01244101569445684</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01826640385518088</v>
+        <v>0.01826640385518086</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01704150898927294</v>
+        <v>0.01704150898927293</v>
       </c>
       <c r="L9" t="n">
         <v>0.02081594406070841</v>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007103434848175358</v>
+        <v>0.007103434848175331</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005532287927936904</v>
+        <v>0.00553228792793691</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0114202256410062</v>
+        <v>0.01142022564100612</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01225451085715711</v>
+        <v>0.01225451085715709</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01225451085715711</v>
+        <v>0.01225451085715709</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01815712033422192</v>
+        <v>0.01815712033422169</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06630544994135408</v>
+        <v>0.06630544994135412</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01225451085715711</v>
+        <v>0.01225451085715709</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0286843411343016</v>
+        <v>0.02868434113430157</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01292335779125228</v>
+        <v>0.01292335779125222</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05838504761100131</v>
+        <v>0.0583850476110012</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001835046932388057</v>
+        <v>0.00183504693238802</v>
       </c>
       <c r="C3" t="n">
         <v>0.001607930547774585</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001835046932388057</v>
+        <v>0.00183504693238802</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001750123958038374</v>
+        <v>0.001750123958038376</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001750123958038374</v>
+        <v>0.001750123958038376</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001831376945112636</v>
+        <v>0.001831376945112622</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001835046932388057</v>
+        <v>0.00183504693238802</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001811388639970357</v>
+        <v>0.001811388639970366</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001835046932388057</v>
+        <v>0.00183504693238802</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001835046932388057</v>
+        <v>0.00183504693238802</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001835046932388057</v>
+        <v>0.00183504693238802</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004537646276069195</v>
+        <v>0.002741923681192476</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002676149818165937</v>
+        <v>0.002676149818165979</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002735658204615763</v>
+        <v>0.00273565820461568</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002563433306903293</v>
+        <v>0.002563433306903295</v>
       </c>
       <c r="F4" t="n">
         <v>0.002716560433817557</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004533976288793764</v>
+        <v>0.004533976288793722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004711932119390473</v>
+        <v>0.004711932119390429</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002718265388774842</v>
+        <v>0.004513987983651503</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004570817771892588</v>
+        <v>0.004570817771892532</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002718714568802323</v>
+        <v>0.002718714568802271</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002751903437710992</v>
+        <v>0.002751903437710974</v>
       </c>
     </row>
     <row r="5">
@@ -3803,13 +3803,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003530631108976244</v>
+        <v>0.003530631108976231</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00352827259964256</v>
+        <v>0.003528272599642559</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0035304996864409</v>
+        <v>0.003530499686440865</v>
       </c>
       <c r="E5" t="n">
         <v>0.003505179885141848</v>
@@ -3818,22 +3818,22 @@
         <v>0.003505179885141848</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003526961121700818</v>
+        <v>0.003526961121700788</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003530631108976244</v>
+        <v>0.003530631108976231</v>
       </c>
       <c r="I5" t="n">
         <v>0.003506972816558556</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003530631108976244</v>
+        <v>0.003530631108976231</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003530631108976244</v>
+        <v>0.003530631108976231</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003530631108976244</v>
+        <v>0.003530631108976231</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005553806513798606</v>
+        <v>0.005553806513798553</v>
       </c>
       <c r="C6" t="n">
         <v>0.008481471662992662</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009092571244205701</v>
+        <v>0.009092571244205665</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007658643185182546</v>
+        <v>0.007658643185182562</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005622065301070479</v>
+        <v>0.00562206530107049</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008481138834936062</v>
+        <v>0.008481138834936048</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008484808822215152</v>
+        <v>0.008484808822215167</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008461150529793795</v>
+        <v>0.008461150529793812</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008485384843225426</v>
+        <v>0.008485384843225408</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005499361641626105</v>
+        <v>0.005499361641626096</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01154648581509287</v>
+        <v>0.01154648581509289</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007513877490128573</v>
+        <v>0.007513877490128536</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009329315218013471</v>
+        <v>0.009329315218013468</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009331674249963284</v>
+        <v>0.009331674249963257</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01140571298639454</v>
+        <v>0.01140571298639455</v>
       </c>
       <c r="F7" t="n">
         <v>0.009308014446759274</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009328003740071731</v>
+        <v>0.009328003740071703</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009331673727347159</v>
+        <v>0.00933167372734714</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009308015434929467</v>
+        <v>0.009308015434929465</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009331673727347159</v>
+        <v>0.00933167372734714</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008235704448577739</v>
+        <v>0.008278435668276274</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009331673727347159</v>
+        <v>0.009331673727347141</v>
       </c>
     </row>
     <row r="8">
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01288060869667599</v>
+        <v>0.01288060869667596</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004291681786235065</v>
+        <v>0.004291681786235068</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0319325523386306</v>
+        <v>0.03193255233863058</v>
       </c>
       <c r="E8" t="n">
         <v>0.01280677093188643</v>
@@ -3938,10 +3938,10 @@
         <v>0.01280677093188643</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01330466873369814</v>
+        <v>0.01330466873369813</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03084110019057141</v>
+        <v>0.0308411001905714</v>
       </c>
       <c r="I8" t="n">
         <v>0.01280677093188643</v>
@@ -3950,10 +3950,10 @@
         <v>0.01888759825989961</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01717626247295973</v>
+        <v>0.01717626247295969</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02084264631578011</v>
+        <v>0.0208426463157801</v>
       </c>
     </row>
     <row r="9">
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01270931833035495</v>
+        <v>0.01270931833035491</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004235167133906714</v>
+        <v>0.004235167133906717</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03152328788603367</v>
+        <v>0.03152328788603363</v>
       </c>
       <c r="E9" t="n">
         <v>0.01270670841145483</v>
@@ -3981,19 +3981,19 @@
         <v>0.01327033424234771</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03107996001259003</v>
+        <v>0.03107996001259</v>
       </c>
       <c r="I9" t="n">
         <v>0.01270670841145483</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01889462190420479</v>
+        <v>0.01889462190420478</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01701740316711429</v>
+        <v>0.01701740316711428</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02113124768423743</v>
+        <v>0.02113124768423742</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005354084426659762</v>
+        <v>0.005354084426659737</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005172352947111838</v>
+        <v>0.005172352947111832</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006501485706427701</v>
+        <v>0.006501485706427696</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008350195041873402</v>
+        <v>0.008350195041873353</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008350195041873402</v>
+        <v>0.008350195041873353</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006707667015885197</v>
+        <v>0.006707667015885079</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007554173753358385</v>
+        <v>0.00755417375335835</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008350195041873402</v>
+        <v>0.008350195041873353</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01057396227069987</v>
+        <v>0.01057396227069986</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00596753408237431</v>
+        <v>0.005967534082374193</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006730537782381751</v>
+        <v>0.006730537782381709</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001725946124658036</v>
+        <v>0.00172594612465803</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001559300971515476</v>
+        <v>0.001559300971515475</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001725946124658036</v>
+        <v>0.00172594612465803</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001772047360134173</v>
+        <v>0.001772047360134172</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001772047360134173</v>
+        <v>0.001772047360134172</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001722914569032455</v>
+        <v>0.001722914569032447</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001725946124658036</v>
+        <v>0.00172594612465803</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001706431343308611</v>
+        <v>0.001706431343308604</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001725946124658036</v>
+        <v>0.00172594612465803</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001725946124658036</v>
+        <v>0.00172594612465803</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001725946124658036</v>
+        <v>0.00172594612465803</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004266925551971289</v>
+        <v>0.002637685308026777</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002595980857572868</v>
+        <v>0.002595980857572902</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002637172202506119</v>
+        <v>0.002637157652887501</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002496893742078495</v>
+        <v>0.002496893742078492</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002626680198691955</v>
+        <v>0.002626680198691953</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002634653752401188</v>
+        <v>0.002634653752401192</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004402230362985159</v>
+        <v>0.004402230362985155</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002618170526677348</v>
+        <v>0.004247410770621858</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002734974356471038</v>
+        <v>0.004283989771770829</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002633082506303086</v>
+        <v>0.002633082506303082</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002628500010218419</v>
+        <v>0.002628500010218414</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003199223320201442</v>
+        <v>0.00319922332020143</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003197375124349463</v>
+        <v>0.003197375124349464</v>
       </c>
       <c r="D5" t="n">
         <v>0.003199098327213353</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0031789349630234</v>
+        <v>0.003178934963023404</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0031789349630234</v>
+        <v>0.003178934963023404</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003196191764575847</v>
+        <v>0.003196191764575849</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003199223320201442</v>
+        <v>0.00319922332020143</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003179708538852003</v>
+        <v>0.003179708538852008</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003199223320201442</v>
+        <v>0.00319922332020143</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003199223320201442</v>
+        <v>0.00319922332020143</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003199223320201442</v>
+        <v>0.00319922332020143</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005022010809132936</v>
+        <v>0.005022010809132922</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007622888743013463</v>
+        <v>0.00762288874301345</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00816452240637488</v>
+        <v>0.008164522406374856</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006893359591802243</v>
+        <v>0.006893359591802238</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005084613967108621</v>
+        <v>0.005084613967108605</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007621782617816218</v>
+        <v>0.007621782617816182</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007624814173447477</v>
+        <v>0.007624814173447454</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007605299392092374</v>
+        <v>0.007605299392092355</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007625325694220694</v>
+        <v>0.007625325694220673</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004973662400818498</v>
+        <v>0.004973662400818494</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01034365992591165</v>
+        <v>0.01034365992591163</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006407180663522137</v>
+        <v>0.006407180663522125</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00792128676565464</v>
+        <v>0.007921286765654628</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007923135841584049</v>
+        <v>0.007923135841584026</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009652999838470212</v>
+        <v>0.009652999838470198</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007903619977189975</v>
+        <v>0.007903619977189963</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007920103405881016</v>
+        <v>0.007920103405881005</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007923134961506611</v>
+        <v>0.007923134961506593</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007903620180157177</v>
+        <v>0.007903620180157164</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007923134961506611</v>
+        <v>0.007923134961506593</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006014277675361997</v>
+        <v>0.007044785457799557</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007923134961506611</v>
+        <v>0.007923134961506593</v>
       </c>
     </row>
     <row r="8">
@@ -4319,13 +4319,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01201542540907252</v>
+        <v>0.01201542540907251</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004215689634909163</v>
+        <v>0.004215689634909165</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03192790107988222</v>
+        <v>0.03192790107988223</v>
       </c>
       <c r="E8" t="n">
         <v>0.01277560070983339</v>
@@ -4334,22 +4334,22 @@
         <v>0.01277560070983339</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01338420255340504</v>
+        <v>0.01338420255340505</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03191991406148725</v>
+        <v>0.03191991406148726</v>
       </c>
       <c r="I8" t="n">
         <v>0.01277560070983339</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01920142583412653</v>
+        <v>0.01920142583412651</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01712232768857952</v>
+        <v>0.01712232768857955</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02118246476235975</v>
+        <v>0.02118246476235976</v>
       </c>
     </row>
     <row r="9">
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01183860291745992</v>
+        <v>0.01183860291745991</v>
       </c>
       <c r="C9" t="n">
         <v>0.004159248910090277</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03145779438525694</v>
+        <v>0.03145779438525696</v>
       </c>
       <c r="E9" t="n">
         <v>0.01263051723176428</v>
@@ -4377,16 +4377,16 @@
         <v>0.01320507905794775</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03145465045726809</v>
+        <v>0.03145465045726807</v>
       </c>
       <c r="I9" t="n">
         <v>0.01263051723176428</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01898142523616542</v>
+        <v>0.01898142523616543</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0168762011684403</v>
+        <v>0.01687620116844031</v>
       </c>
       <c r="L9" t="n">
         <v>0.02087366898383702</v>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004927105700420281</v>
+        <v>0.004927105700420284</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004990399476253692</v>
+        <v>0.004990399476253677</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005883198021152705</v>
+        <v>0.005883198021152711</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00662317905422208</v>
+        <v>0.006623179054222079</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00662317905422208</v>
+        <v>0.006623179054222079</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005840995567802982</v>
+        <v>0.005840995567802906</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006879947514365171</v>
+        <v>0.006879947514365177</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00662317905422208</v>
+        <v>0.006623179054222079</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009120230598555587</v>
+        <v>0.009120230598555597</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005356066019896502</v>
+        <v>0.005356066019896506</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006221929178749621</v>
+        <v>0.00622192917874962</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001692398078956095</v>
+        <v>0.001692398078956099</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001546963105914304</v>
+        <v>0.001546963105914289</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001692398078956095</v>
+        <v>0.001692398078956099</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001714372924653483</v>
+        <v>0.001714372924653488</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001714372924653481</v>
+        <v>0.001714372924653488</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00168999787174595</v>
+        <v>0.001689997871745952</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001692398078956095</v>
+        <v>0.001692398078956099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001677097129221195</v>
+        <v>0.0016770971292212</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001692398078956095</v>
+        <v>0.001692398078956099</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001692398078956095</v>
+        <v>0.001692398078956099</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001692398078956095</v>
+        <v>0.001692398078956099</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00423650745825771</v>
+        <v>0.002628971228534984</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002593016331446069</v>
+        <v>0.002593016331446116</v>
       </c>
       <c r="D4" t="n">
         <v>0.002618949308496892</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002484790585373177</v>
+        <v>0.002484790585373181</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002619517333004792</v>
+        <v>0.002619517333004789</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004234107251047564</v>
+        <v>0.004234107251047563</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004361080974350311</v>
+        <v>0.004361080974350314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002613670278800085</v>
+        <v>0.004221206508522808</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004253098410881674</v>
+        <v>0.002728521009699269</v>
       </c>
       <c r="K4" t="n">
         <v>0.002632222907516663</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002617750444001798</v>
+        <v>0.002617750444001636</v>
       </c>
     </row>
     <row r="5">
@@ -4598,25 +4598,25 @@
         <v>0.003108881628687052</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003107142245510641</v>
+        <v>0.003107142245510632</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003108755939527986</v>
+        <v>0.003108755939527985</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003092285227884301</v>
+        <v>0.003092285227884302</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003092285227884301</v>
+        <v>0.003092285227884302</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003106481421476906</v>
+        <v>0.003106481421476903</v>
       </c>
       <c r="H5" t="n">
         <v>0.003108881628687052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00309358067895215</v>
+        <v>0.003093580678952149</v>
       </c>
       <c r="J5" t="n">
         <v>0.003108881628687052</v>
@@ -4635,34 +4635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004892427061848087</v>
+        <v>0.004892427061848096</v>
       </c>
       <c r="C6" t="n">
         <v>0.007417626772045919</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00794405434647911</v>
+        <v>0.007944054346479115</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006712842646065446</v>
+        <v>0.006712842646065463</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004956547027072147</v>
+        <v>0.004956547027072154</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007417554762585037</v>
+        <v>0.007417554762585043</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007419954969800914</v>
+        <v>0.00741995496980092</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007404654020060281</v>
+        <v>0.007404654020060284</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007420451696824299</v>
+        <v>0.007420451696824306</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004845476933778663</v>
+        <v>0.004845476933778668</v>
       </c>
       <c r="L6" t="n">
         <v>0.01006016921369581</v>
@@ -4678,34 +4678,34 @@
         <v>0.005957009240330934</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00734980013559576</v>
+        <v>0.007349800135595749</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007351540358933563</v>
+        <v>0.007351540358933561</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008945497436500107</v>
+        <v>0.0089454974365001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00733623835741473</v>
+        <v>0.007336238357414719</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007349139311562025</v>
+        <v>0.007349139311562017</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007351539518772176</v>
+        <v>0.007351539518772167</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007336238569037266</v>
+        <v>0.007336238569037263</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007351539518772176</v>
+        <v>0.007351539518772167</v>
       </c>
       <c r="K7" t="n">
         <v>0.006510762100961611</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007351539518772176</v>
+        <v>0.007351539518772167</v>
       </c>
     </row>
     <row r="8">
@@ -4715,13 +4715,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009702809561004493</v>
+        <v>0.009702809561004479</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004160801085830475</v>
+        <v>0.004160801085830472</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03189091433418981</v>
+        <v>0.03189091433418982</v>
       </c>
       <c r="E8" t="n">
         <v>0.01256548660904037</v>
@@ -4730,22 +4730,22 @@
         <v>0.01256548660904037</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01306533004994507</v>
+        <v>0.01306533004994506</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03188239471852943</v>
+        <v>0.03188239471852944</v>
       </c>
       <c r="I8" t="n">
         <v>0.01256548660904037</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01845234049273591</v>
+        <v>0.01845234049273592</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01718563700937783</v>
+        <v>0.0171856370093778</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02109653736828772</v>
+        <v>0.02109653736828771</v>
       </c>
     </row>
     <row r="9">
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009556428582742253</v>
+        <v>0.009556428582742242</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004102740534816542</v>
+        <v>0.004102740534816538</v>
       </c>
       <c r="D9" t="n">
         <v>0.03141272615405624</v>
@@ -4773,7 +4773,7 @@
         <v>0.01287937777365115</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03140935256431913</v>
+        <v>0.03140935256431914</v>
       </c>
       <c r="I9" t="n">
         <v>0.01239959742360737</v>
@@ -4782,10 +4782,10 @@
         <v>0.0182246550857356</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01692998984241011</v>
+        <v>0.01692998984241007</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02078290374354556</v>
+        <v>0.02078290374354555</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06345077488167616</v>
+        <v>0.06345077488167605</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03062198606440338</v>
+        <v>0.03062198606440342</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08602154121344371</v>
+        <v>0.08602154121344377</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03062198606440338</v>
+        <v>0.03062198606440342</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03062198606440338</v>
+        <v>0.03062198606440342</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08876207502400633</v>
+        <v>0.0887620750240064</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1894244824514291</v>
+        <v>0.1894244824514295</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03062198606440338</v>
+        <v>0.03062198606440342</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1467683547870897</v>
+        <v>0.1467683547870894</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04459054553269363</v>
+        <v>0.04459054553269378</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08832201248110502</v>
+        <v>0.0883220124811049</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00217009390104079</v>
+        <v>0.002170093901040789</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001935232285084632</v>
+        <v>0.001935232285084626</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00217009390104079</v>
+        <v>0.002170093901040789</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001991390055907655</v>
+        <v>0.001991390055907651</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001991390055907654</v>
+        <v>0.00199139005590765</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002166018069272856</v>
+        <v>0.002166018069272851</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00217009390104079</v>
+        <v>0.002170093901040789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002144238959910436</v>
+        <v>0.002144238959910435</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00217009390104079</v>
+        <v>0.002170093901040789</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00217009390104079</v>
+        <v>0.002170093901040789</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00217009390104079</v>
+        <v>0.002170093901040789</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005556787065599603</v>
+        <v>0.005556787065599601</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003178603055135469</v>
+        <v>0.003178603055135453</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00336597774593559</v>
+        <v>0.003365977745935551</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003043491833797411</v>
+        <v>0.003043491833797405</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003282443230742125</v>
+        <v>0.003282443230742115</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003317499601150635</v>
+        <v>0.005552711233831663</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003366190155164873</v>
+        <v>0.005710944429718896</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005530932124469258</v>
+        <v>0.005530932124469248</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005600600637604355</v>
+        <v>0.005600600637604351</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003261636885275815</v>
+        <v>0.003261636885275809</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003410101416176474</v>
+        <v>0.003410101416176468</v>
       </c>
     </row>
     <row r="5">
@@ -4994,25 +4994,25 @@
         <v>0.00420807690536049</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004182221964230144</v>
+        <v>0.004182221964230138</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004207931291394409</v>
+        <v>0.00420793129139441</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004179509206616712</v>
+        <v>0.004179509206616704</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004179509206616712</v>
+        <v>0.004179509206616704</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004204001073592558</v>
+        <v>0.004204001073592555</v>
       </c>
       <c r="H5" t="n">
         <v>0.00420807690536049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004182221964230144</v>
+        <v>0.004182221964230138</v>
       </c>
       <c r="J5" t="n">
         <v>0.00420807690536049</v>
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006479413638493403</v>
+        <v>0.006479413638493401</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009825376073157376</v>
+        <v>0.009825376073157388</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01055251833295685</v>
+        <v>0.01055251833295686</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008902888607986726</v>
+        <v>0.008902888607986737</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006558964312738243</v>
+        <v>0.006558964312738251</v>
       </c>
       <c r="G6" t="n">
         <v>0.009848910273755326</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009852986105523313</v>
+        <v>0.009852986105523338</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009827131164392893</v>
+        <v>0.009827131164392901</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009853649104057876</v>
+        <v>0.009853649104057886</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006416747798431155</v>
+        <v>0.006416747798431167</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01337696463598974</v>
+        <v>0.01337696463598976</v>
       </c>
     </row>
     <row r="7">
@@ -5071,28 +5071,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00986478787380538</v>
+        <v>0.009864787873805384</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01224353397023169</v>
+        <v>0.01224353397023167</v>
       </c>
       <c r="D7" t="n">
-        <v>0.012269389721638</v>
+        <v>0.01226938972163801</v>
       </c>
       <c r="E7" t="n">
         <v>0.01501838982746909</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01224353118079367</v>
+        <v>0.01224353118079366</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01226531307959411</v>
+        <v>0.01226531307959412</v>
       </c>
       <c r="H7" t="n">
         <v>0.01226938891136206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01224353397023169</v>
+        <v>0.01224353397023167</v>
       </c>
       <c r="J7" t="n">
         <v>0.01226938891136206</v>
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01376848166752649</v>
+        <v>0.01376848166752648</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01450630603016531</v>
+        <v>0.01450630603016532</v>
       </c>
       <c r="D8" t="n">
         <v>0.01328260862908422</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01450630603016531</v>
+        <v>0.01450630603016532</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01450630603016531</v>
+        <v>0.01450630603016532</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01325575599586364</v>
+        <v>0.01325575599586365</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01139946380649833</v>
+        <v>0.01139946380649831</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01450630603016531</v>
+        <v>0.01450630603016532</v>
       </c>
       <c r="J8" t="n">
         <v>0.0120861142660371</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01424345551709599</v>
+        <v>0.01424345551709597</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008998909278625558</v>
+        <v>0.01344921196437923</v>
       </c>
     </row>
     <row r="9">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01435530456491292</v>
+        <v>0.01435530456491293</v>
       </c>
       <c r="C9" t="n">
         <v>0.01463421795542815</v>
@@ -5166,10 +5166,10 @@
         <v>0.01463421795542815</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01413994161166289</v>
+        <v>0.01413994161166287</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01339397286429209</v>
+        <v>0.01339397286429207</v>
       </c>
       <c r="I9" t="n">
         <v>0.01463421795542815</v>
@@ -5178,10 +5178,10 @@
         <v>0.01367128156947471</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01454880991374688</v>
+        <v>0.01454880991374687</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01241739823118824</v>
+        <v>0.01422658760723173</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04716744173565754</v>
+        <v>0.04716744173565753</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03181714127897251</v>
+        <v>0.03181714127897255</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07644331850867436</v>
+        <v>0.07644331850867397</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03181714127897251</v>
+        <v>0.03181714127897255</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03181714127897251</v>
+        <v>0.03181714127897255</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07771250518033236</v>
+        <v>0.0777125051803325</v>
       </c>
       <c r="H2" t="n">
         <v>0.1496936545698072</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03181714127897251</v>
+        <v>0.03181714127897255</v>
       </c>
       <c r="J2" t="n">
         <v>0.1146841342519505</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03928774731611948</v>
+        <v>0.03928774731611951</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2768967459556695</v>
+        <v>0.0939676100718371</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002084733527045306</v>
+        <v>0.002084733527045311</v>
       </c>
       <c r="C3" t="n">
         <v>0.001910405473985352</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002084733527045306</v>
+        <v>0.002084733527045312</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001959900121430819</v>
+        <v>0.00195990012143082</v>
       </c>
       <c r="F3" t="n">
         <v>0.00195990012143082</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002081221945685407</v>
+        <v>0.002081221945685409</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002084733527045306</v>
+        <v>0.002084733527045312</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002062526986593512</v>
+        <v>0.00206252698659351</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002084733527045306</v>
+        <v>0.002084733527045312</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002084733527045306</v>
+        <v>0.002084733527045312</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002084733527045306</v>
+        <v>0.002084733527045312</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003218977675976309</v>
+        <v>0.005277471443619916</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003104833051947403</v>
+        <v>0.00310483305194741</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003258596597518997</v>
+        <v>0.003258596597519062</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002973546422661814</v>
+        <v>0.002973546422661816</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003188001349013992</v>
+        <v>0.003188001349013991</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003215466094616411</v>
+        <v>0.005273959862260016</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005398290820687351</v>
+        <v>0.005398290820687345</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003196771135524511</v>
+        <v>0.005255264903168118</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003359745719516587</v>
+        <v>0.005308444682383293</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003182301876143905</v>
+        <v>0.003182301876143903</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003296432207658346</v>
+        <v>0.003296432207658358</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003915955671111856</v>
+        <v>0.003915955671111861</v>
       </c>
       <c r="C5" t="n">
         <v>0.003893749130660066</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003915819882532598</v>
+        <v>0.003915819882532603</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00389074422868889</v>
+        <v>0.003890744228688891</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00389074422868889</v>
+        <v>0.003890744228688891</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003912444089751965</v>
+        <v>0.003912444089751966</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003915955671111856</v>
+        <v>0.003915955671111863</v>
       </c>
       <c r="I5" t="n">
         <v>0.003893749130660066</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003915955671111856</v>
+        <v>0.003915955671111863</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003915955671111856</v>
+        <v>0.003915955671111863</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003915955671111856</v>
+        <v>0.003915955671111863</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005972611184495672</v>
+        <v>0.005972611184495654</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008995108451332437</v>
+        <v>0.008995108451351715</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00965120368925463</v>
+        <v>0.009651203689254612</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008162027055324339</v>
+        <v>0.008162027055324336</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006045272427317926</v>
+        <v>0.006045272427317916</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009015915072520378</v>
+        <v>0.009015915072520361</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009019426653880683</v>
+        <v>0.009019426653880658</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008997220113428484</v>
+        <v>0.008997220113428475</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009020025435656368</v>
+        <v>0.009020025435656354</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005916015023388761</v>
+        <v>0.005916015023388752</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01220208017766774</v>
+        <v>0.01220208017766772</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008578356252666893</v>
+        <v>0.008578356252666888</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01060291807092261</v>
+        <v>0.01060291807092259</v>
       </c>
       <c r="D7" t="n">
         <v>0.01062512555081364</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0129648434721285</v>
+        <v>0.01296484347212846</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01060291588254148</v>
+        <v>0.01060291588254145</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0106216130300145</v>
+        <v>0.01062161303001449</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0106251246113744</v>
+        <v>0.01062512461137439</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01060291807092261</v>
+        <v>0.01060291807092259</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0106251246113744</v>
+        <v>0.01062512461137439</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008047877657419421</v>
+        <v>0.008047877657419407</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0106251246113744</v>
+        <v>0.01062512461137439</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01405457538354191</v>
+        <v>0.01405457538354192</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0143657563219953</v>
+        <v>0.01436575632199531</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01330768150307004</v>
+        <v>0.01330768150307006</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0143657563219953</v>
+        <v>0.01436575632199531</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0143657563219953</v>
+        <v>0.01436575632199531</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01331726262547946</v>
+        <v>0.01331726262547948</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01195527697759337</v>
+        <v>0.01195527697759339</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0143657563219953</v>
+        <v>0.01436575632199531</v>
       </c>
       <c r="J8" t="n">
         <v>0.01256314835626183</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01420729055345841</v>
+        <v>0.01420729055345842</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009417902138102952</v>
+        <v>0.01313411884692599</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01444910481608178</v>
+        <v>0.01444910481608179</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0145501157254392</v>
+        <v>0.01455011572543921</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01414494931567264</v>
+        <v>0.01414494931567266</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0145501157254392</v>
+        <v>0.01455011572543921</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0145501157254392</v>
+        <v>0.01455011572543921</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01414317818898565</v>
+        <v>0.01414317818898566</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01359707402616028</v>
+        <v>0.01359707402616029</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0145501157254392</v>
+        <v>0.01455011572543921</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01384265360072246</v>
+        <v>0.01384265360072248</v>
       </c>
       <c r="K9" t="n">
         <v>0.0145113560833835</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01407573409626906</v>
+        <v>0.01407573409626907</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04000340417198571</v>
+        <v>0.04000340417198552</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04042864123740614</v>
+        <v>0.04042864123740598</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06265018209929722</v>
+        <v>0.06265018209929718</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04042864123740614</v>
+        <v>0.04042864123740598</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04042864123740614</v>
+        <v>0.04042864123740598</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0679406888615796</v>
+        <v>0.06794068886157931</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1084064685278094</v>
+        <v>0.1084064685278096</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04042864123740614</v>
+        <v>0.04042864123740598</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0971489639139887</v>
+        <v>0.09714896391398865</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03206996890929887</v>
+        <v>0.03206996890929868</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2461506130700978</v>
+        <v>0.2461506130700979</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002094904626450456</v>
+        <v>0.00209490462645045</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001953298113603372</v>
+        <v>0.001953298113603363</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002094904626450456</v>
+        <v>0.00209490462645045</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002001200337374849</v>
+        <v>0.002001200337374846</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00200120033737485</v>
+        <v>0.002001200337374845</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002092009988635557</v>
+        <v>0.002092009988635555</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002094904626450456</v>
+        <v>0.00209490462645045</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002076619530926604</v>
+        <v>0.002076619530926597</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002094904626450456</v>
+        <v>0.00209490462645045</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002094904626450456</v>
+        <v>0.00209490462645045</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002094904626450456</v>
+        <v>0.00209490462645045</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003246901093511718</v>
+        <v>0.00324690109351172</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003172679923459384</v>
+        <v>0.003172679923459372</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00528994957157188</v>
+        <v>0.005289949571571857</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003039348465328681</v>
+        <v>0.003039348465328672</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003229716399945273</v>
+        <v>0.003229716399945268</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00324400645569683</v>
+        <v>0.003244006455696829</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00537617244481764</v>
+        <v>0.005376172444817626</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005242948796878234</v>
+        <v>0.00524294879687822</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005293293274244148</v>
+        <v>0.003387136775872861</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003215055686269432</v>
+        <v>0.003215055686269427</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003314982070317373</v>
+        <v>0.003314982070317374</v>
       </c>
     </row>
     <row r="5">
@@ -5786,34 +5786,34 @@
         <v>0.003881219593419521</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003862934497895677</v>
+        <v>0.003862934497895664</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003881083201104089</v>
+        <v>0.00388108320110408</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00385979688950708</v>
+        <v>0.003859796889507075</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00385979688950708</v>
+        <v>0.003859796889507075</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003878324955604628</v>
+        <v>0.003878324955604619</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003881219593419521</v>
+        <v>0.003881219593419518</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003862934497895677</v>
+        <v>0.003862934497895664</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003881219593419521</v>
+        <v>0.003881219593419518</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003881219593419521</v>
+        <v>0.003881219593419518</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003881219593419521</v>
+        <v>0.003881219593419518</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005888004157988363</v>
+        <v>0.005888004157988362</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008843791493069774</v>
+        <v>0.008843791493069755</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009481487194195228</v>
+        <v>0.009481487194195209</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008030002785332618</v>
+        <v>0.008030002785332599</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005962273539566577</v>
+        <v>0.005962273539566563</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008861432581111937</v>
+        <v>0.008861432581111918</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008864327218927416</v>
+        <v>0.008864327218927399</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008846042123402974</v>
+        <v>0.008846042123402951</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008864912146942258</v>
+        <v>0.008864912146942247</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005832717429557817</v>
+        <v>0.005832717429557806</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01197334552762971</v>
+        <v>0.01197334552762968</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007973519996472856</v>
+        <v>0.007973519996472859</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009827449025311906</v>
+        <v>0.009827449025311899</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009845735188555549</v>
+        <v>0.009845735188555544</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01198794334233199</v>
+        <v>0.01198794334233197</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009827447385040659</v>
+        <v>0.009827447385040631</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009842839483020855</v>
+        <v>0.009842839483020872</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00984573412083576</v>
+        <v>0.009845734120835756</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009827449025311906</v>
+        <v>0.009827449025311899</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00984573412083576</v>
+        <v>0.009845734120835756</v>
       </c>
       <c r="K7" t="n">
         <v>0.008760966353506473</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00984573412083576</v>
+        <v>0.009845734120835756</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01400312997691056</v>
+        <v>0.01400312997691058</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01382861280926613</v>
+        <v>0.01382861280926615</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01340318838130058</v>
+        <v>0.0134031883813006</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01382861280926613</v>
+        <v>0.01382861280926615</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01382861280926613</v>
+        <v>0.01382861280926615</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01331902825434069</v>
+        <v>0.01331902825434068</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01255468364081863</v>
+        <v>0.01255468364081865</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01382861280926613</v>
+        <v>0.01382861280926615</v>
       </c>
       <c r="J8" t="n">
         <v>0.01277246679474018</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01415540899886471</v>
+        <v>0.01415540899886474</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009782681274645263</v>
+        <v>0.009782681274645289</v>
       </c>
     </row>
     <row r="9">
@@ -5943,13 +5943,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0143111343713207</v>
+        <v>0.01431113437132072</v>
       </c>
       <c r="C9" t="n">
         <v>0.01415936862409189</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01406682369117939</v>
+        <v>0.01406682369117942</v>
       </c>
       <c r="E9" t="n">
         <v>0.01415936862409189</v>
@@ -5958,22 +5958,22 @@
         <v>0.01415936862409189</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01402879363589934</v>
+        <v>0.01402879363589935</v>
       </c>
       <c r="H9" t="n">
-        <v>0.013723444788181</v>
+        <v>0.01372344478818101</v>
       </c>
       <c r="I9" t="n">
         <v>0.01415936862409189</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01381073343994898</v>
+        <v>0.013810733439949</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01437320002228127</v>
+        <v>0.01437320002228129</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01259610561286679</v>
+        <v>0.0125961056128668</v>
       </c>
     </row>
   </sheetData>
@@ -6062,34 +6062,34 @@
         <v>0.01692840543914713</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01703099416577253</v>
+        <v>0.01703099416577252</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02770981305022332</v>
+        <v>0.02770981305022329</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01703099416577253</v>
+        <v>0.01703099416577252</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01703099416577253</v>
+        <v>0.01703099416577252</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03530061210928093</v>
+        <v>0.03530061210928091</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06149649393146363</v>
+        <v>0.06149649393146359</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01703099416577253</v>
+        <v>0.01703099416577252</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1132814022720287</v>
+        <v>0.1132814022720285</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02792724091914477</v>
+        <v>0.02792724091914473</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04238597139379288</v>
+        <v>0.1059854792317579</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001974645400646826</v>
+        <v>0.001974645400646814</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001771887005257497</v>
+        <v>0.001771887005257494</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001974645400646826</v>
+        <v>0.001974645400646814</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001824924116847694</v>
+        <v>0.00182492411684769</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001824924116847693</v>
+        <v>0.00182492411684769</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001971911005841358</v>
+        <v>0.001971911005841352</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001974645400646826</v>
+        <v>0.001974645400646814</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001957329104235279</v>
+        <v>0.001957329104235274</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001974645400646826</v>
+        <v>0.001974645400646814</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001974645400646826</v>
+        <v>0.001974645400646814</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001974645400646826</v>
+        <v>0.001974645400646814</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00300588583530256</v>
+        <v>0.003005885835302554</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002921403947351687</v>
+        <v>0.002921403947351694</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003007752898302698</v>
+        <v>0.004931427316455939</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002792805383255413</v>
+        <v>0.002792805383255402</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002977076762954871</v>
+        <v>0.002977076762954865</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004874709335267161</v>
+        <v>0.00300315144049709</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005019216036659252</v>
+        <v>0.005019216036659234</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004860127433661081</v>
+        <v>0.002988569538891018</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004929047652955588</v>
+        <v>0.004929047652955575</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002987515662220251</v>
+        <v>0.002987515662220248</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003033442754111244</v>
+        <v>0.003033442754111235</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003709970776608645</v>
+        <v>0.003709970776608641</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003692654480197101</v>
+        <v>0.003692654480197104</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003709829204362342</v>
+        <v>0.00370982920436234</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003689687045745509</v>
+        <v>0.003689687045745506</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003689687045745509</v>
+        <v>0.003689687045745506</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00370723638180318</v>
+        <v>0.003707236381803172</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003709970776608645</v>
+        <v>0.003709970776608641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003692654480197101</v>
+        <v>0.003692654480197104</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003709970776608645</v>
+        <v>0.003709970776608641</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003709970776608645</v>
+        <v>0.003709970776608641</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003709970776608645</v>
+        <v>0.003709970776608641</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005720688715288278</v>
+        <v>0.00572068871528828</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008656807810185248</v>
+        <v>0.008656807810164875</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009289056159292897</v>
+        <v>0.009289056159292899</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00784868943250611</v>
+        <v>0.00784868943250612</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005795372107694891</v>
+        <v>0.005795372107694888</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008673475247268976</v>
+        <v>0.008673475247268986</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008676209642074554</v>
+        <v>0.008676209642074563</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008658893345662897</v>
+        <v>0.008658893345662909</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0086767904816142</v>
+        <v>0.008676790481614204</v>
       </c>
       <c r="K6" t="n">
         <v>0.005665788397202515</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0117634983819612</v>
+        <v>0.01176349838196122</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008308493121966146</v>
+        <v>0.00830849312196613</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01029324735094841</v>
+        <v>0.0102932473509484</v>
       </c>
       <c r="D7" t="n">
         <v>0.01031056456464722</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01260359375425681</v>
+        <v>0.0126035937542568</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01029324626178687</v>
+        <v>0.01029324626178686</v>
       </c>
       <c r="G7" t="n">
         <v>0.01030782925255448</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01031056364735996</v>
+        <v>0.01031056364735995</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01029324735094841</v>
+        <v>0.0102932473509484</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01031056364735996</v>
+        <v>0.01031056364735995</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007789599249823318</v>
+        <v>0.00915055650801652</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01031056364735996</v>
+        <v>0.01031056364735995</v>
       </c>
     </row>
     <row r="8">
@@ -6305,7 +6305,7 @@
         <v>0.01459154643657614</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01432238831311552</v>
+        <v>0.01432238831311551</v>
       </c>
       <c r="E8" t="n">
         <v>0.01459154643657614</v>
@@ -6314,7 +6314,7 @@
         <v>0.01459154643657614</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01416583220142604</v>
+        <v>0.01416583220142603</v>
       </c>
       <c r="H8" t="n">
         <v>0.01362415368271174</v>
@@ -6323,13 +6323,13 @@
         <v>0.01459154643657614</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0125474764964494</v>
+        <v>0.01254747649644939</v>
       </c>
       <c r="K8" t="n">
         <v>0.01432987000532755</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01283660665005451</v>
+        <v>0.01411903714638003</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0145464791376655</v>
+        <v>0.01454647913766549</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01453026142463235</v>
+        <v>0.01453026142463234</v>
       </c>
       <c r="D9" t="n">
         <v>0.01442978248529703</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01453026142463235</v>
+        <v>0.01453026142463234</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01453026142463235</v>
+        <v>0.01453026142463234</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01436290231684392</v>
+        <v>0.01436290231684391</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01414662034522334</v>
+        <v>0.01414662034522333</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01453026142463235</v>
+        <v>0.01453026142463234</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01370777477657558</v>
+        <v>0.01370777477657557</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01443284607940907</v>
+        <v>0.01443284607940906</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01434756774748398</v>
+        <v>0.01382622262818833</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01281549512995012</v>
+        <v>0.01281549512995013</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01943911558305757</v>
+        <v>0.01943911558305755</v>
       </c>
       <c r="D2" t="n">
         <v>0.01655882266821837</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01943911558305757</v>
+        <v>0.01943911558305755</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01943911558305757</v>
+        <v>0.01943911558305755</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02339379686725725</v>
+        <v>0.02339379686725706</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01247214275224732</v>
+        <v>0.01247214275224734</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01943911558305757</v>
+        <v>0.01943911558305755</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06636150179752119</v>
+        <v>0.06636150179752118</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02485687648570944</v>
+        <v>0.02485687648570948</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01473287029905924</v>
+        <v>0.01473287029905925</v>
       </c>
     </row>
     <row r="3">
@@ -6495,13 +6495,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001881170598699892</v>
+        <v>0.001881170598699902</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001746835441367613</v>
+        <v>0.001746835441367609</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001881170598699892</v>
+        <v>0.001881170598699902</v>
       </c>
       <c r="E3" t="n">
         <v>0.001792359925374819</v>
@@ -6510,22 +6510,22 @@
         <v>0.00179235992537482</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001879214900365996</v>
+        <v>0.00187921490036599</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001881170598699892</v>
+        <v>0.001881170598699902</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001868861144859145</v>
+        <v>0.001868861144859142</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001881170598699892</v>
+        <v>0.001881170598699902</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001881170598699892</v>
+        <v>0.001881170598699902</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001881170598699892</v>
+        <v>0.001881170598699902</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002885633924182456</v>
+        <v>0.004560750890752798</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00283786945619428</v>
+        <v>0.002837869456194273</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002878232590194333</v>
+        <v>0.002878221014572502</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002713769022016569</v>
+        <v>0.002713769022016564</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002868102567960108</v>
+        <v>0.002868102567960106</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00288367822584855</v>
+        <v>0.002883678225848561</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004655535530328862</v>
+        <v>0.002873990561297635</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002873324470341708</v>
+        <v>0.002873324470341703</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003002583936680148</v>
+        <v>0.004593023636947695</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002893020759761676</v>
+        <v>0.002893020759761691</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002885096522996146</v>
+        <v>0.002885096522996144</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003403971790811918</v>
+        <v>0.003403971790811919</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00339166233697117</v>
+        <v>0.003391662336971166</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003403838851243146</v>
+        <v>0.003403838851243142</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003389379366769582</v>
+        <v>0.003389379366769578</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003389379366769582</v>
+        <v>0.003389379366769578</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003402016092478011</v>
+        <v>0.003402016092478019</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003403971790811918</v>
+        <v>0.003403971790811919</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00339166233697117</v>
+        <v>0.003391662336971166</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003403971790811918</v>
+        <v>0.003403971790811919</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003403971790811918</v>
+        <v>0.003403971790811919</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003403971790811918</v>
+        <v>0.003403971790811919</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00518510888695484</v>
+        <v>0.005185108886954851</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007784332759136555</v>
+        <v>0.007784332759136553</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00833998355960293</v>
+        <v>0.00833998355960292</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00706982069669956</v>
+        <v>0.007069820696699557</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005254346271420661</v>
+        <v>0.005254346271420654</v>
       </c>
       <c r="G6" t="n">
         <v>0.007796196341479957</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007798152039813495</v>
+        <v>0.007798152039813488</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007785842585973109</v>
+        <v>0.007785842585973105</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007798665573053062</v>
+        <v>0.007798665573053053</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00513657026931142</v>
+        <v>0.005136570269311429</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01052769410768051</v>
+        <v>0.0105276941076805</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007107126121122032</v>
+        <v>0.007107126121122034</v>
       </c>
       <c r="C7" t="n">
         <v>0.008763695421386782</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008776006071880343</v>
+        <v>0.008776006071880326</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0106895468841502</v>
+        <v>0.01068954688415018</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008763695169164793</v>
+        <v>0.008763695169164787</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008774049176893627</v>
+        <v>0.008774049176893631</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008776004875227538</v>
+        <v>0.008776004875227518</v>
       </c>
       <c r="I7" t="n">
         <v>0.008763695421386782</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008776004875227538</v>
+        <v>0.008776004875227518</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007769819864168535</v>
+        <v>0.007769819864168533</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008776004875227538</v>
+        <v>0.008776004875227518</v>
       </c>
     </row>
     <row r="8">
@@ -6713,7 +6713,7 @@
         <v>0.01433138531604506</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01464683613533155</v>
+        <v>0.01464683613533156</v>
       </c>
       <c r="I8" t="n">
         <v>0.01441378428614695</v>
@@ -6725,7 +6725,7 @@
         <v>0.01428356624008107</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01477425491084583</v>
+        <v>0.01477425491084584</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6741,7 @@
         <v>0.01441442357171332</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01446122339489752</v>
+        <v>0.01446122339489753</v>
       </c>
       <c r="E9" t="n">
         <v>0.01441442357171332</v>
@@ -6750,7 +6750,7 @@
         <v>0.01441442357171332</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01439096466332225</v>
+        <v>0.01439096466332224</v>
       </c>
       <c r="H9" t="n">
         <v>0.01452124978481549</v>
@@ -6765,7 +6765,7 @@
         <v>0.01437310077761888</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01450065312875552</v>
+        <v>0.01457300843327495</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0180767823715752</v>
+        <v>0.01807678237157516</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02247941734236918</v>
+        <v>0.02247941734236922</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01315581408096562</v>
+        <v>0.01315581408096561</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02247941734236918</v>
+        <v>0.02247941734236922</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02247941734236918</v>
+        <v>0.02247941734236922</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0210936224652351</v>
+        <v>0.02109362246523527</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01285662718898649</v>
+        <v>0.01285662718898651</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02247941734236918</v>
+        <v>0.02247941734236922</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05548379729993803</v>
+        <v>0.05548379729993795</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02082842343180168</v>
+        <v>0.02082842343180173</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0175358798478602</v>
+        <v>0.01228723025126886</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001882531329955687</v>
+        <v>0.001882531329955665</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001770934422755464</v>
+        <v>0.001770934422755468</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001882531329955687</v>
+        <v>0.001882531329955665</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001815110067441862</v>
+        <v>0.001815110067441868</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001815110067441863</v>
+        <v>0.001815110067441867</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001880699479128601</v>
+        <v>0.001880699479128635</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001882531329955687</v>
+        <v>0.001882531329955665</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001870985370198751</v>
+        <v>0.001870985370198757</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001882531329955687</v>
+        <v>0.001882531329955665</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001882531329955687</v>
+        <v>0.001882531329955665</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001882531329955687</v>
+        <v>0.001882531329955665</v>
       </c>
     </row>
     <row r="4">
@@ -6931,34 +6931,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002905887348348829</v>
+        <v>0.002905887348348736</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002869904906933821</v>
+        <v>0.002869904906933846</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004599826556475201</v>
+        <v>0.002880430178370254</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002744131074977741</v>
+        <v>0.002744131074977735</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002890831879118642</v>
+        <v>0.002890831879118648</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002904055497521688</v>
+        <v>0.004582888678674703</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004664746167741336</v>
+        <v>0.004664746167741368</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002894341388591844</v>
+        <v>0.002894341388591865</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003020118932723472</v>
+        <v>0.004604693708229028</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002912667775259496</v>
+        <v>0.002912667775259439</v>
       </c>
       <c r="L4" t="n">
         <v>0.002901417332679375</v>
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003380784782380288</v>
+        <v>0.003380784782380353</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00336923882262344</v>
+        <v>0.003369238822623448</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003380651270156302</v>
+        <v>0.00338065127015631</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003367105615704884</v>
+        <v>0.00336710561570489</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003367105615704884</v>
+        <v>0.00336710561570489</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003378952931553356</v>
+        <v>0.003378952931553327</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003380784782380288</v>
+        <v>0.003380784782380353</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00336923882262344</v>
+        <v>0.003369238822623448</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003380784782380288</v>
+        <v>0.003380784782380353</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003380784782380288</v>
+        <v>0.003380784782380353</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003380784782380288</v>
+        <v>0.003380784782380353</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005136671762496429</v>
+        <v>0.005136671762496392</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007699728447496256</v>
+        <v>0.007699728447512607</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008246791699433138</v>
+        <v>0.008246791699433121</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006995338545598012</v>
+        <v>0.006995338545598015</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00520558731368286</v>
+        <v>0.005205587313682864</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007710814696420315</v>
+        <v>0.007710814696420261</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007712646547246787</v>
+        <v>0.007712646547246797</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007701100587490373</v>
+        <v>0.00770110058749039</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007713152795517168</v>
+        <v>0.00771315279551706</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00508882170881933</v>
+        <v>0.005088821708819268</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01040346760504368</v>
+        <v>0.01040346760504365</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006675630537640416</v>
+        <v>0.006675630537640412</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008210892578670203</v>
+        <v>0.008210892578670219</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008222439587796063</v>
+        <v>0.008222439587796065</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009995876868372767</v>
+        <v>0.009995876868372777</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008210892343322175</v>
+        <v>0.008210892343322188</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008220606687600081</v>
+        <v>0.008220606687600093</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008222438538427143</v>
+        <v>0.00822243853842713</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008210892578670203</v>
+        <v>0.008210892578670219</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008222438538427143</v>
+        <v>0.00822243853842713</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007326212349347955</v>
+        <v>0.007289851278179657</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008222438538427143</v>
+        <v>0.00822243853842713</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01429689502816454</v>
+        <v>0.01429689502816451</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01403444473939898</v>
+        <v>0.01403444473939897</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01441972419457996</v>
+        <v>0.01441972419457993</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01403444473939898</v>
+        <v>0.01403444473939897</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01403444473939898</v>
+        <v>0.01403444473939897</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01422092182280376</v>
+        <v>0.01422092182280372</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01446155358805666</v>
+        <v>0.01446155358805665</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01403444473939898</v>
+        <v>0.01403444473939897</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01340786654430864</v>
+        <v>0.01340786654430863</v>
       </c>
       <c r="K8" t="n">
         <v>0.0141983501647251</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01434909867166177</v>
+        <v>0.01434909867166175</v>
       </c>
     </row>
     <row r="9">
@@ -7134,34 +7134,34 @@
         <v>0.01427221433081604</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01408294540589234</v>
+        <v>0.01408294540589233</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01432224938432184</v>
+        <v>0.0143222493843218</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01408294540589234</v>
+        <v>0.01408294540589233</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01408294540589234</v>
+        <v>0.01408294540589233</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01424034087349885</v>
+        <v>0.01424034087349883</v>
       </c>
       <c r="H9" t="n">
         <v>0.01433950316233661</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01408294540589234</v>
+        <v>0.01408294540589233</v>
       </c>
       <c r="J9" t="n">
         <v>0.01391061266905719</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01423210432026637</v>
+        <v>0.01423210432026633</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01429374042897345</v>
+        <v>0.01434894469454066</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04203748101057059</v>
+        <v>0.0420374810105706</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0276270116219297</v>
+        <v>0.02762701162192966</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07899608625087826</v>
+        <v>0.0789960862508783</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0276270116219297</v>
+        <v>0.02762701162192966</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0276270116219297</v>
+        <v>0.02762701162192966</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0758018586213387</v>
+        <v>0.07580185862133856</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1702843807430717</v>
+        <v>0.1702843807430719</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0276270116219297</v>
+        <v>0.02762701162192966</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1157355039183063</v>
+        <v>0.1157355039183065</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04148189954110496</v>
+        <v>0.04148189954110506</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2757102088812725</v>
+        <v>0.2757102088812727</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002113360091671463</v>
+        <v>0.002113360091671464</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001884492281738844</v>
+        <v>0.001884492281738849</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002113360091671463</v>
+        <v>0.002113360091671464</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001939968680863803</v>
+        <v>0.001939968680863806</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001939968680863802</v>
+        <v>0.001939968680863806</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002109548616160939</v>
+        <v>0.002109548616160942</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002113360091671463</v>
+        <v>0.002113360091671464</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002089181654001942</v>
+        <v>0.002089181654001947</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002113360091671463</v>
+        <v>0.002113360091671464</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002113360091671463</v>
+        <v>0.002113360091671464</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002113360091671463</v>
+        <v>0.002113360091671464</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003234933687007753</v>
+        <v>0.003234933687007754</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003105171554694674</v>
+        <v>0.003105171554694678</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003288159746947811</v>
+        <v>0.003288159746947815</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002972736756947768</v>
+        <v>0.002972736756947761</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003198794479828968</v>
+        <v>0.003198794479828965</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005377841998331103</v>
+        <v>0.005377841998331108</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00555138741293874</v>
+        <v>0.005551387412938744</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00321075524933823</v>
+        <v>0.005357475036172107</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00543942655049992</v>
+        <v>0.005439426550499925</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003187018535465815</v>
+        <v>0.003187018535465818</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003312085526329998</v>
+        <v>0.00331208552633</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004043112418161144</v>
+        <v>0.00404311241816115</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004018933980491623</v>
+        <v>0.00401893398049163</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004042968365744565</v>
+        <v>0.004042968365744568</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004016019033991259</v>
+        <v>0.004016019033991266</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004016019033991259</v>
+        <v>0.004016019033991266</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004039300942650622</v>
+        <v>0.004039300942650625</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004043112418161144</v>
+        <v>0.00404311241816115</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004018933980491623</v>
+        <v>0.00401893398049163</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004043112418161144</v>
+        <v>0.00404311241816115</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004043112418161144</v>
+        <v>0.00404311241816115</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004043112418161144</v>
+        <v>0.00404311241816115</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006224507236069054</v>
+        <v>0.00622450723606906</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009425305273834412</v>
+        <v>0.009425305273856795</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01012059310870644</v>
+        <v>0.01012059310870645</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008542940286282804</v>
+        <v>0.008542940286282817</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006300965338649001</v>
+        <v>0.006300965338649019</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009447651366937518</v>
+        <v>0.009447651366937529</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009451462842448277</v>
+        <v>0.009451462842448279</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009427284404778516</v>
+        <v>0.009427284404778535</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009452097026583572</v>
+        <v>0.009452097026583589</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006164564879464917</v>
+        <v>0.006164564879464923</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01282228780207685</v>
+        <v>0.01282228780207687</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009490603641436472</v>
+        <v>0.009490603641436477</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01177422410307763</v>
+        <v>0.01177422410307765</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01179840308970458</v>
+        <v>0.0117984030897046</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01443737224321573</v>
+        <v>0.01443737224321574</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01177422142094051</v>
+        <v>0.01177422142094054</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01179459106523663</v>
+        <v>0.01179459106523664</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01179840254074715</v>
+        <v>0.01179840254074717</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01177422410307763</v>
+        <v>0.01177422410307765</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01179840254074715</v>
+        <v>0.01179840254074717</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01040700523993289</v>
+        <v>0.01046125502595028</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01179840254074715</v>
+        <v>0.01179840254074717</v>
       </c>
     </row>
     <row r="8">
@@ -7487,13 +7487,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0141842202966626</v>
+        <v>0.01418422029666262</v>
       </c>
       <c r="C8" t="n">
         <v>0.01448611223581118</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01327797073576357</v>
+        <v>0.01327797073576358</v>
       </c>
       <c r="E8" t="n">
         <v>0.01448611223581118</v>
@@ -7502,22 +7502,22 @@
         <v>0.01448611223581118</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01341339293362306</v>
+        <v>0.01341339293362305</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0113988771618187</v>
+        <v>0.01139887716181871</v>
       </c>
       <c r="I8" t="n">
         <v>0.01448611223581118</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01266977983198151</v>
+        <v>0.01266977983198152</v>
       </c>
       <c r="K8" t="n">
         <v>0.01420578699998428</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01385654365832585</v>
+        <v>0.009744361121897803</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01447394391123593</v>
+        <v>0.01447394391123594</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01457386404478042</v>
+        <v>0.01457386404478041</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01410488337122711</v>
+        <v>0.01410488337122712</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01457386404478042</v>
+        <v>0.01457386404478041</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01457386404478042</v>
+        <v>0.01457386404478041</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01415416992929759</v>
+        <v>0.0141541699292976</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01334296485252369</v>
+        <v>0.01334296485252368</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01457386404478042</v>
+        <v>0.01457386404478041</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01385806049851168</v>
+        <v>0.01385806049851169</v>
       </c>
       <c r="K9" t="n">
         <v>0.01448277678502842</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01434143366752508</v>
+        <v>0.0126696968753318</v>
       </c>
     </row>
   </sheetData>
@@ -7643,13 +7643,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.009188512898505695</v>
+        <v>0.009188512898505698</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02048889300219784</v>
+        <v>0.02048889300219783</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0635281814105695</v>
+        <v>0.0635281814105696</v>
       </c>
       <c r="E2" t="n">
         <v>0.02048889300219783</v>
@@ -7658,22 +7658,22 @@
         <v>0.02048889300219783</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04520113836556627</v>
+        <v>0.04520113836556628</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0248797649387894</v>
+        <v>0.02487976493878937</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02048889300219784</v>
+        <v>0.02048889300219783</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08581134961966205</v>
+        <v>0.08581134961966193</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02005578084967431</v>
+        <v>0.02005578084967429</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3267509925288082</v>
+        <v>0.01998563484285111</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001955118401023408</v>
+        <v>0.001955118401023398</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001799868961973642</v>
+        <v>0.001799868961973638</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001955118401023408</v>
+        <v>0.001955118401023398</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001847171953687357</v>
+        <v>0.001847171953687354</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001847171953687357</v>
+        <v>0.001847171953687354</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001952339072408255</v>
+        <v>0.001952339072408242</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0019551184010234</v>
+        <v>0.001955118401023398</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001937564460421405</v>
+        <v>0.001937564460421401</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001955118401023408</v>
+        <v>0.001955118401023398</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001955118401023408</v>
+        <v>0.001955118401023398</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001955118401023408</v>
+        <v>0.001955118401023398</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003000192241341701</v>
+        <v>0.004899217635033853</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002918772733563267</v>
+        <v>0.002918772733563263</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003070383636639198</v>
+        <v>0.003070383636639015</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002792381277128601</v>
+        <v>0.002792381277128568</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002976026345865688</v>
+        <v>0.002976026345865683</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004896438306418715</v>
+        <v>0.002997412912726543</v>
       </c>
       <c r="H4" t="n">
         <v>0.005001523342358993</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004881663694431867</v>
+        <v>0.004881663694431858</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00493479610400208</v>
+        <v>0.003127819650757217</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002970816600334043</v>
+        <v>0.00297081660033405</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003099248024232899</v>
+        <v>0.0030992480242329</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003598635495627315</v>
+        <v>0.003598635495627312</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00358108155502532</v>
+        <v>0.003581081555025321</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003598501685420915</v>
+        <v>0.003598501685420909</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003578521510397824</v>
+        <v>0.003578521510397827</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003578521510397824</v>
+        <v>0.003578521510397827</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003595856167012167</v>
+        <v>0.003595856167012162</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003598635495627315</v>
+        <v>0.003598635495627312</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00358108155502532</v>
+        <v>0.003581081555025321</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003598635495627315</v>
+        <v>0.003598635495627312</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003598635495627315</v>
+        <v>0.003598635495627312</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003598635495627315</v>
+        <v>0.003598635495627312</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005504846951502569</v>
+        <v>0.005504846951502574</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008280509196156173</v>
+        <v>0.008280509196174159</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008879353091078365</v>
+        <v>0.008879353091078341</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007516270184794167</v>
+        <v>0.007516270184794163</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00557444137903778</v>
+        <v>0.005574441379037767</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008297021805598055</v>
+        <v>0.008297021805598048</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008299801134213062</v>
+        <v>0.008299801134213053</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008282247193611206</v>
+        <v>0.008282247193611201</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008300350418116243</v>
+        <v>0.008300350418116239</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005452929243093189</v>
+        <v>0.005452929243093185</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01121936448385551</v>
+        <v>0.0112193644838555</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007705232525672971</v>
+        <v>0.00770523252567296</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009512718677210227</v>
+        <v>0.00951271867721022</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009530274076900932</v>
+        <v>0.009530274076900935</v>
       </c>
       <c r="E7" t="n">
         <v>0.01161877662440077</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009512717924392115</v>
+        <v>0.00951271792439211</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00952749328919705</v>
+        <v>0.00952749328919706</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009530272617812245</v>
+        <v>0.009530272617812221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009512718677210227</v>
+        <v>0.00951271867721022</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009530272617812245</v>
+        <v>0.009530272617812221</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008472837834628237</v>
+        <v>0.007232220995140318</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009530272617812245</v>
+        <v>0.009530272617812221</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0148202807766966</v>
+        <v>0.01482028077669661</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01448934213897889</v>
+        <v>0.01448934213897887</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01333779239966727</v>
+        <v>0.01333779239966728</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01448934213897889</v>
+        <v>0.01448934213897887</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01448934213897889</v>
+        <v>0.01448934213897887</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01388684118347725</v>
+        <v>0.01388684118347726</v>
       </c>
       <c r="H8" t="n">
         <v>0.01446099009315957</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01448934213897889</v>
+        <v>0.01448934213897887</v>
       </c>
       <c r="J8" t="n">
         <v>0.01304812269222056</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01452576448350047</v>
+        <v>0.01452576448350048</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01459209490733429</v>
+        <v>0.007958575260530776</v>
       </c>
     </row>
     <row r="9">
@@ -7926,34 +7926,34 @@
         <v>0.01465423650909406</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01450093171719499</v>
+        <v>0.01450093171719498</v>
       </c>
       <c r="D9" t="n">
         <v>0.01405047237462659</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01450093171719499</v>
+        <v>0.01450093171719498</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01450093171719499</v>
+        <v>0.01450093171719498</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01427027349679419</v>
+        <v>0.0142702734967942</v>
       </c>
       <c r="H9" t="n">
         <v>0.01450839609382841</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01450093171719499</v>
+        <v>0.01450093171719498</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01393319025933201</v>
+        <v>0.013933190259332</v>
       </c>
       <c r="K9" t="n">
         <v>0.01453430668254622</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0145615979742084</v>
+        <v>0.01186483686189393</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen photochemical ozone formation results.xlsx
+++ b/Results/Hydrogen/hydrogen photochemical ozone formation results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08525123755515017</v>
+        <v>0.08525123755515052</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05191630204564382</v>
+        <v>0.05191630204564383</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1694755403253592</v>
+        <v>0.1694755403253596</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05191630204564382</v>
+        <v>0.05191630204564383</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05191630204564382</v>
+        <v>0.05191630204564383</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1214463725586996</v>
+        <v>0.1214463725586993</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2389036818016615</v>
+        <v>0.2389036818016614</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05191630204564382</v>
+        <v>0.05191630204564383</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1520831843674304</v>
+        <v>0.152083184367431</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05958216583016948</v>
+        <v>0.0595821658301695</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09804254212428259</v>
+        <v>0.3681314073785206</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00244747266180591</v>
+        <v>0.002447472661805912</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002295295294137587</v>
+        <v>0.002295295294137584</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00244747266180591</v>
+        <v>0.002447472661805912</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002356448963090838</v>
+        <v>0.002356448963090834</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002356448963090836</v>
+        <v>0.002356448963090834</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002444069538033234</v>
+        <v>0.002444069538033254</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00244747266180591</v>
+        <v>0.002447472661805912</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002426250318469695</v>
+        <v>0.0024262503184697</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00244747266180591</v>
+        <v>0.002447472661805912</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00244747266180591</v>
+        <v>0.002447472661805912</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00244747266180591</v>
+        <v>0.002447472661805912</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003803844908782871</v>
+        <v>0.003803844908782865</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003668397372595511</v>
+        <v>0.003668397372595475</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003959501764127141</v>
+        <v>0.003959518277380236</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003513999018221125</v>
+        <v>0.003513999018221127</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003779583833363699</v>
+        <v>0.003779583833363694</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006425933612238218</v>
+        <v>0.006425933612238215</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006608690727069787</v>
+        <v>0.006608690727069804</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003782622565446658</v>
+        <v>0.006408114392674662</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003968679755440626</v>
+        <v>0.006456333933543074</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003738987196650061</v>
+        <v>0.003738987196650057</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003903423395847117</v>
+        <v>0.003903423395847118</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004825237718683751</v>
+        <v>0.004825237718683754</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004804015375347551</v>
+        <v>0.004804015375347544</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004825076009250697</v>
+        <v>0.004825076009250692</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004801504756458286</v>
+        <v>0.004801504756458279</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004801504756458286</v>
+        <v>0.004801504756458279</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004821834594911101</v>
+        <v>0.004821834594911097</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004825237718683751</v>
+        <v>0.004825237718683754</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004804015375347551</v>
+        <v>0.004804015375347544</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004825237718683751</v>
+        <v>0.004825237718683754</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004825237718683751</v>
+        <v>0.004825237718683754</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004825237718683751</v>
+        <v>0.004825237718683754</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007433306720444851</v>
+        <v>0.007433306720444855</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01130232911454433</v>
+        <v>0.01130232911457029</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01213195659095294</v>
+        <v>0.0121319565909529</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01023810457216025</v>
+        <v>0.01023810457216024</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007534043511422076</v>
+        <v>0.00753404351142205</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01132158746544298</v>
+        <v>0.011321587465443</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01132499058921582</v>
+        <v>0.01132499058921573</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01130376824587941</v>
+        <v>0.01130376824587943</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01132575541110205</v>
+        <v>0.01132575541110202</v>
       </c>
       <c r="K6" t="n">
         <v>0.007361016695134253</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01539017980220264</v>
+        <v>0.01539017980220269</v>
       </c>
     </row>
     <row r="7">
@@ -718,34 +718,34 @@
         <v>0.01299911338313663</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0162110112499887</v>
+        <v>0.01621101124998869</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01623223471884064</v>
+        <v>0.01623223471884062</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01994196022014042</v>
+        <v>0.01994196022014041</v>
       </c>
       <c r="F7" t="n">
         <v>0.01621100787668795</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01622883046955226</v>
+        <v>0.01622883046955223</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01623223359332492</v>
+        <v>0.0162322335933249</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0162110112499887</v>
+        <v>0.01621101124998869</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01623223359332492</v>
+        <v>0.0162322335933249</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01435895151948652</v>
+        <v>0.01216115784707213</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01623223359332492</v>
+        <v>0.0162322335933249</v>
       </c>
     </row>
     <row r="8">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01360352976596097</v>
+        <v>0.01360352976596094</v>
       </c>
       <c r="C8" t="n">
         <v>0.01439248842073947</v>
@@ -770,19 +770,19 @@
         <v>0.01439248842073947</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01292592901904736</v>
+        <v>0.01292592901904737</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01093814382495993</v>
+        <v>0.01093814382495994</v>
       </c>
       <c r="I8" t="n">
         <v>0.01439248842073947</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01239314532046432</v>
+        <v>0.01239314532046431</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01420542153658416</v>
+        <v>0.01420542153658418</v>
       </c>
       <c r="L8" t="n">
         <v>0.01358922871371968</v>
@@ -801,7 +801,7 @@
         <v>0.01475280475580074</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01369450146315278</v>
+        <v>0.01369450146315277</v>
       </c>
       <c r="E9" t="n">
         <v>0.01475280475580074</v>
@@ -810,7 +810,7 @@
         <v>0.01475280475580074</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01412649040456141</v>
+        <v>0.0141264904045614</v>
       </c>
       <c r="H9" t="n">
         <v>0.01332792668297189</v>
@@ -819,13 +819,13 @@
         <v>0.01475280475580074</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01391751894552565</v>
+        <v>0.01391751894552566</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01465455528967272</v>
+        <v>0.01465455528967271</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01440488965310744</v>
+        <v>0.01242129964235726</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007908069937214622</v>
+        <v>0.007908069937214634</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02183012290606761</v>
+        <v>0.02183012290606764</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01625440881031481</v>
+        <v>0.0162544088103148</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02183012290606761</v>
+        <v>0.02183012290606764</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02183012290606761</v>
+        <v>0.02183012290606764</v>
       </c>
       <c r="G2" t="n">
         <v>0.02461823126793045</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01625376362460502</v>
+        <v>0.01625376362460506</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02183012290606761</v>
+        <v>0.02183012290606764</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06394229831931381</v>
+        <v>0.06394229831931382</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01930124217881787</v>
+        <v>0.01930124217881785</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01356804827290346</v>
+        <v>0.01356804827290345</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001901277892631337</v>
+        <v>0.001901277892631335</v>
       </c>
       <c r="C3" t="n">
         <v>0.001785357883627884</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001901277892631337</v>
+        <v>0.001901277892631335</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001830024318261652</v>
+        <v>0.001830024318261655</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001830024318261652</v>
+        <v>0.001830024318261654</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001899313657202712</v>
+        <v>0.001899313657202708</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001901277892631337</v>
+        <v>0.001901277892631335</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001888896264506861</v>
+        <v>0.001888896264506864</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001901277892631337</v>
+        <v>0.001901277892631335</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001901277892631337</v>
+        <v>0.001901277892631335</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001901277892631337</v>
+        <v>0.001901277892631335</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004604037442183369</v>
+        <v>0.002922953406917474</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002886061585157213</v>
+        <v>0.002886061585157244</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004642483195929393</v>
+        <v>0.004642483195929381</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002759529601853771</v>
+        <v>0.002759529601853756</v>
       </c>
       <c r="F4" t="n">
         <v>0.002911460271440275</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002920989171488856</v>
+        <v>0.004602073206754755</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004714557885389615</v>
+        <v>0.004714557885389624</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002910571778793</v>
+        <v>0.002910571778793002</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004647338311370386</v>
+        <v>0.003045498745636588</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002928626416012615</v>
+        <v>0.002928626416012578</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002924052132511706</v>
+        <v>0.002924052132511711</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003448262357610072</v>
+        <v>0.003448262357610084</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0034358807294856</v>
+        <v>0.003435880729485601</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003448128376123624</v>
+        <v>0.003448128376123637</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003433621171084113</v>
+        <v>0.003433621171084116</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003433621171084113</v>
+        <v>0.003433621171084116</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00344629812218145</v>
+        <v>0.003446298122181452</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003448262357610072</v>
+        <v>0.003448262357610084</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0034358807294856</v>
+        <v>0.003435880729485601</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003448262357610072</v>
+        <v>0.003448262357610084</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003448262357610072</v>
+        <v>0.003448262357610084</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003448262357610072</v>
+        <v>0.003448262357610084</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005250001058071073</v>
+        <v>0.005250001058071072</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007882072845136784</v>
+        <v>0.007882072845153463</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00844458433290605</v>
+        <v>0.008444584332906071</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007158561448354307</v>
+        <v>0.007158561448354317</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005320223382761057</v>
+        <v>0.005320223382761067</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007893968854398284</v>
+        <v>0.007893968854398312</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007895933089826982</v>
+        <v>0.007895933089826997</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007883551461702436</v>
+        <v>0.007883551461702457</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00789645308667271</v>
+        <v>0.007896453086672715</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005200851512617828</v>
+        <v>0.005200851512617844</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01065983034182299</v>
+        <v>0.01065983034182301</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006788592891581333</v>
+        <v>0.006788592891581334</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008353366823332584</v>
+        <v>0.008353366823332589</v>
       </c>
       <c r="D7" t="n">
         <v>0.008365749602778231</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01017337156806546</v>
+        <v>0.01017337156806548</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008353366526505444</v>
+        <v>0.008353366526505429</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008363784216028434</v>
+        <v>0.008363784216028444</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008365748451457067</v>
+        <v>0.008365748451457078</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008353366823332584</v>
+        <v>0.008353366823332589</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008365748451457067</v>
+        <v>0.008365748451457078</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007451938810338396</v>
+        <v>0.007451938810338403</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008365748451457067</v>
+        <v>0.008365748451457078</v>
       </c>
     </row>
     <row r="8">
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01459579870677108</v>
+        <v>0.01459579870677107</v>
       </c>
       <c r="C8" t="n">
         <v>0.0140928348814209</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01437476373271489</v>
+        <v>0.0143747637327149</v>
       </c>
       <c r="E8" t="n">
         <v>0.0140928348814209</v>
@@ -1166,22 +1166,22 @@
         <v>0.0140928348814209</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01417143938663255</v>
+        <v>0.01417143938663253</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01442287270658022</v>
+        <v>0.01442287270658019</v>
       </c>
       <c r="I8" t="n">
         <v>0.0140928348814209</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01329049151180535</v>
+        <v>0.01329049151180536</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01427803548980267</v>
+        <v>0.01427803548980265</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01449694056989674</v>
+        <v>0.0144969405698967</v>
       </c>
     </row>
     <row r="9">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01441554654791105</v>
+        <v>0.01441554654791104</v>
       </c>
       <c r="C9" t="n">
         <v>0.01413130185005036</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01432553010228408</v>
+        <v>0.01432553010228407</v>
       </c>
       <c r="E9" t="n">
         <v>0.01413130185005036</v>
@@ -1206,10 +1206,10 @@
         <v>0.01413130185005036</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01424135160433578</v>
+        <v>0.01424135160433576</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0143454099812163</v>
+        <v>0.01434540998121628</v>
       </c>
       <c r="I9" t="n">
         <v>0.01413130185005036</v>
@@ -1218,10 +1218,10 @@
         <v>0.01388445618876643</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01428614804722494</v>
+        <v>0.01428614804722493</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01435143359609451</v>
+        <v>0.01437546619568197</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02017937845475284</v>
+        <v>0.02017937845475282</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03667394993898707</v>
+        <v>0.03667394993898705</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05533204121894646</v>
+        <v>0.05533204121894651</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02869525037621015</v>
+        <v>0.02869525037621012</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02869525037621015</v>
+        <v>0.02869525037621012</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0506768823622061</v>
+        <v>0.05067688236220611</v>
       </c>
       <c r="H2" t="n">
         <v>0.1011655714639694</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02869525037621015</v>
+        <v>0.02869525037621012</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09703422757538765</v>
+        <v>0.0970342275753875</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03056654682833806</v>
+        <v>0.03056654682833797</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08279759165610616</v>
+        <v>0.08279759165610612</v>
       </c>
     </row>
     <row r="3">
@@ -1347,31 +1347,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002012644970363203</v>
+        <v>0.002012644970363204</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001785576736107039</v>
+        <v>0.001785576736107037</v>
       </c>
       <c r="D3" t="n">
         <v>0.002012644970363203</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001909039259144128</v>
+        <v>0.001909039259144132</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001909039259144129</v>
+        <v>0.001909039259144132</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002008401807504666</v>
+        <v>0.002008401807504675</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002012644970363203</v>
+        <v>0.002012644970363205</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00198535197953261</v>
+        <v>0.001985351979532612</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002012644970363203</v>
+        <v>0.002012644970363205</v>
       </c>
       <c r="K3" t="n">
         <v>0.002012644970363203</v>
@@ -1387,34 +1387,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003038528291032711</v>
+        <v>0.005010039419114084</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002979706148378686</v>
+        <v>0.002979706148378688</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003069356272315258</v>
+        <v>0.003069370145652039</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002826356149524532</v>
+        <v>0.002826356149524529</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003008070306203202</v>
+        <v>0.003008070306203199</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005005796256255545</v>
+        <v>0.003034285128174173</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00519975486707717</v>
+        <v>0.005199754867077168</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004982746428283496</v>
+        <v>0.003011235300202118</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005053444591619027</v>
+        <v>0.005053444591619032</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002999972742191872</v>
+        <v>0.002999972742191874</v>
       </c>
       <c r="L4" t="n">
         <v>0.003051520541824138</v>
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003918566515788882</v>
+        <v>0.003918566515788884</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003915757157897678</v>
+        <v>0.003915757157897682</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003918432204494803</v>
+        <v>0.003918432204494801</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003887658126519122</v>
+        <v>0.003887658126519123</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003887658126519122</v>
+        <v>0.003887658126519123</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003914323352930347</v>
+        <v>0.003914323352930348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003918566515788882</v>
+        <v>0.003918566515788884</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003891273524958289</v>
+        <v>0.003891273524958292</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003918566515788882</v>
+        <v>0.003918566515788884</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003918566515788882</v>
+        <v>0.003918566515788884</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003918566515788882</v>
+        <v>0.003918566515788884</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006078540350645985</v>
+        <v>0.006078540350645998</v>
       </c>
       <c r="C6" t="n">
         <v>0.009268555230104981</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009936634555679525</v>
+        <v>0.009936634555679547</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008370385330207553</v>
+        <v>0.008370385330207567</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006150462785790659</v>
+        <v>0.00615046278579067</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009269785976225606</v>
+        <v>0.009269785976225613</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009274029139088525</v>
+        <v>0.009274029139088539</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009246736148253545</v>
+        <v>0.009246736148253559</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009274657139239214</v>
+        <v>0.009274657139239237</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006019182506322544</v>
+        <v>0.006019182506322551</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01261198437632388</v>
+        <v>0.01261198437632391</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008585366257043734</v>
+        <v>0.008585366257043731</v>
       </c>
       <c r="C7" t="n">
         <v>0.01066667923497316</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01066948954978979</v>
+        <v>0.0106694895497898</v>
       </c>
       <c r="E7" t="n">
         <v>0.01304722769512771</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01064219419647245</v>
+        <v>0.01064219419647244</v>
       </c>
       <c r="G7" t="n">
         <v>0.01066524543000582</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01066948859286436</v>
+        <v>0.01066948859286437</v>
       </c>
       <c r="I7" t="n">
         <v>0.01064219560203376</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01066948859286436</v>
+        <v>0.01066948859286437</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009461940328988993</v>
+        <v>0.009461940328988996</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01066948859286436</v>
+        <v>0.01066948859286437</v>
       </c>
     </row>
     <row r="8">
@@ -1550,7 +1550,7 @@
         <v>0.01303044872696621</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003781841388241002</v>
+        <v>0.003781841388241001</v>
       </c>
       <c r="D8" t="n">
         <v>0.03113757327166265</v>
@@ -1562,19 +1562,19 @@
         <v>0.01262266919288654</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01278784280584175</v>
+        <v>0.01278784280584176</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0303501003043647</v>
+        <v>0.03035010030436469</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01262266919288654</v>
+        <v>0.01262266919288653</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01763412868052224</v>
+        <v>0.01763412868052223</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01701578953077497</v>
+        <v>0.01701578953077498</v>
       </c>
       <c r="L8" t="n">
         <v>0.02050973764433904</v>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01302502993078951</v>
+        <v>0.01302502993078952</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004136309827476033</v>
+        <v>0.004136309827476035</v>
       </c>
       <c r="D9" t="n">
         <v>0.03132523069330777</v>
@@ -1605,13 +1605,13 @@
         <v>0.013181572756307</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03100634608542753</v>
+        <v>0.03100634608542752</v>
       </c>
       <c r="I9" t="n">
         <v>0.0127413315580604</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01852565944286498</v>
+        <v>0.01852565944286497</v>
       </c>
       <c r="K9" t="n">
         <v>0.01709261818618094</v>
@@ -1706,34 +1706,34 @@
         <v>0.01150106357520047</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02501378776389319</v>
+        <v>0.02501378776389328</v>
       </c>
       <c r="D2" t="n">
         <v>0.03803109370171219</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01784971344082617</v>
+        <v>0.01784971344082622</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01784971344082617</v>
+        <v>0.01784971344082622</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0321059543169782</v>
+        <v>0.03210595431697846</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05244000961871276</v>
+        <v>0.05244000961871281</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01784971344082617</v>
+        <v>0.01784971344082622</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06532979888783927</v>
+        <v>0.0653297988878393</v>
       </c>
       <c r="K2" t="n">
         <v>0.01664020731105277</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03330052889549228</v>
+        <v>0.0333005288954923</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001880076817890242</v>
+        <v>0.001880076817890256</v>
       </c>
       <c r="C3" t="n">
         <v>0.001709940213403883</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001880076817890242</v>
+        <v>0.001880076817890256</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001906983319205205</v>
+        <v>0.001906983319205214</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001906983319205211</v>
+        <v>0.001906983319205214</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001876406328541559</v>
+        <v>0.00187640632854157</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001880076817890242</v>
+        <v>0.001880076817890256</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00185649270529201</v>
+        <v>0.001856492705292008</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001880076817890241</v>
+        <v>0.001880076817890256</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001880076817890242</v>
+        <v>0.001880076817890256</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001880076817890242</v>
+        <v>0.001880076817890256</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004643165569899018</v>
+        <v>0.00464316556989903</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002819648132401369</v>
+        <v>0.00281964813240133</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004670205257941746</v>
+        <v>0.004670205257941778</v>
       </c>
       <c r="E4" t="n">
         <v>0.002690183747137601</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002846242241834356</v>
+        <v>0.002846242241834363</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002859128201048171</v>
+        <v>0.004639495080550343</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004801418038413156</v>
+        <v>0.004801418038413157</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002839214577798611</v>
+        <v>0.002839214577798615</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002983442229743633</v>
+        <v>0.002983442229743631</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002842155469164762</v>
+        <v>0.002842155469164772</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002859553858727997</v>
+        <v>0.002859553858728001</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003579249873729446</v>
+        <v>0.003579249873729451</v>
       </c>
       <c r="C5" t="n">
         <v>0.00357685141884406</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003579122236192866</v>
+        <v>0.003579122236192855</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003553149367682013</v>
+        <v>0.003553149367682021</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003553149367682013</v>
+        <v>0.003553149367682021</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003575579384380765</v>
+        <v>0.00357557938438076</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003579249873729446</v>
+        <v>0.003579249873729451</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003555665761131203</v>
+        <v>0.003555665761131204</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003579249873729446</v>
+        <v>0.003579249873729451</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003579249873729446</v>
+        <v>0.003579249873729451</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003579249873729446</v>
+        <v>0.003579249873729451</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005560112600593357</v>
+        <v>0.005560112600593381</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008449911095207558</v>
+        <v>0.008449911095183759</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009054056466183529</v>
+        <v>0.009054056466183534</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007637424993152885</v>
+        <v>0.0076374249931529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005626834983157082</v>
+        <v>0.005626834983157088</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008450321279724402</v>
+        <v>0.008450321279724405</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008453991769080548</v>
+        <v>0.008453991769080576</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008430407656474825</v>
+        <v>0.008430407656474839</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008454560494587919</v>
+        <v>0.008454560494587926</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005506357309777947</v>
+        <v>0.005506357309777961</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0114768905383678</v>
+        <v>0.01147689053836783</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007225837037737225</v>
+        <v>0.007225837037737244</v>
       </c>
       <c r="C7" t="n">
         <v>0.008943673303064883</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008946072789159041</v>
+        <v>0.008946072789159057</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01090760198602964</v>
+        <v>0.01090760198602966</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008922486858335082</v>
+        <v>0.008922486858335105</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008942401268601579</v>
+        <v>0.008942401268601581</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00894607175795026</v>
+        <v>0.008946071757950279</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008922487645352022</v>
+        <v>0.00892248764535203</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00894607175795026</v>
+        <v>0.008946071757950279</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007949361438898163</v>
+        <v>0.007949361438898168</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00894607175795026</v>
+        <v>0.008946071757950279</v>
       </c>
     </row>
     <row r="8">
@@ -1943,34 +1943,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01314572082114871</v>
+        <v>0.01314572082114872</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003913787417192319</v>
+        <v>0.00391378741719232</v>
       </c>
       <c r="D8" t="n">
         <v>0.03137360797477601</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01275270811944803</v>
+        <v>0.01275270811944802</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01275270811944803</v>
+        <v>0.01275270811944802</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01308022395466229</v>
+        <v>0.01308022395466228</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03116878930581577</v>
+        <v>0.03116878930581578</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01275270811944803</v>
+        <v>0.01275270811944802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0181991827236559</v>
+        <v>0.01819918272365592</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01721536624281847</v>
+        <v>0.01721536624281848</v>
       </c>
       <c r="L8" t="n">
         <v>0.02078927510190936</v>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01303452949330743</v>
+        <v>0.01303452949330741</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004133037772227439</v>
+        <v>0.004133037772227436</v>
       </c>
       <c r="D9" t="n">
         <v>0.03135518464994279</v>
@@ -2001,19 +2001,19 @@
         <v>0.01325216225025391</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0312727509203223</v>
+        <v>0.03127275092032231</v>
       </c>
       <c r="I9" t="n">
         <v>0.01273939356800504</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01872641483669772</v>
+        <v>0.01872641483669773</v>
       </c>
       <c r="K9" t="n">
         <v>0.01711650056800174</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0208097174876529</v>
+        <v>0.02080971748765291</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006317282618925005</v>
+        <v>0.006317282618925006</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01850849819421504</v>
+        <v>0.01850849819421502</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0250149314188725</v>
+        <v>0.02501493141887246</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008255769111006402</v>
+        <v>0.0082557691110064</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008255769111006402</v>
+        <v>0.0082557691110064</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02028341995975397</v>
+        <v>0.02028341995975402</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02814118649697358</v>
+        <v>0.02814118649697357</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008255769111006402</v>
+        <v>0.0082557691110064</v>
       </c>
       <c r="J2" t="n">
         <v>0.03756974007875735</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00937103607020145</v>
+        <v>0.009371036070201419</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0151032335931656</v>
+        <v>0.01510323359316559</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001804573889659526</v>
+        <v>0.001804573889659523</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001660257834835548</v>
+        <v>0.001660257834835546</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001804573889659526</v>
+        <v>0.001804573889659523</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00180934669148644</v>
+        <v>0.001809346691486439</v>
       </c>
       <c r="F3" t="n">
         <v>0.00180934669148644</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00180152834555022</v>
+        <v>0.001801528345550222</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001804573889659526</v>
+        <v>0.001804573889659523</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001785120299744236</v>
+        <v>0.001785120299744238</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001804573889659526</v>
+        <v>0.001804573889659523</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001804573889659526</v>
+        <v>0.001804573889659523</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001804573889659526</v>
+        <v>0.001804573889659523</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002761257913489919</v>
+        <v>0.002761257913489909</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002730517235123053</v>
+        <v>0.002730517235123062</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002770651306004955</v>
+        <v>0.002770636818871302</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002590899613561105</v>
+        <v>0.002590899613561091</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002745564868942008</v>
+        <v>0.002745564868942003</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004471252569905063</v>
+        <v>0.004471252569905062</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004615790281404479</v>
+        <v>0.004615790281404472</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004454844524099079</v>
+        <v>0.004454844524099077</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004497648341420711</v>
+        <v>0.004497648341420707</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002752819996364723</v>
+        <v>0.002752819996364624</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002752360384828006</v>
+        <v>0.002752360384827829</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003424328745116838</v>
+        <v>0.003424328745116835</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003422281266917215</v>
+        <v>0.003422281266917219</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003424201081514569</v>
+        <v>0.003424201081514565</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003402070175125488</v>
+        <v>0.003402070175125486</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003402070175125488</v>
+        <v>0.003402070175125486</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003421283201007533</v>
+        <v>0.003421283201007534</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003424328745116838</v>
+        <v>0.003424328745116835</v>
       </c>
       <c r="I5" t="n">
         <v>0.003404875155201552</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003424328745116838</v>
+        <v>0.003424328745116835</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003424328745116838</v>
+        <v>0.003424328745116835</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003424328745116838</v>
+        <v>0.003424328745116835</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005351058077064662</v>
+        <v>0.005351058077064663</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008137412681704074</v>
+        <v>0.008137412681727657</v>
       </c>
       <c r="D6" t="n">
         <v>0.008720040708066238</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007357042547622488</v>
+        <v>0.007357042547622485</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005418458056015299</v>
+        <v>0.005418458056015291</v>
       </c>
       <c r="G6" t="n">
         <v>0.008138391837805126</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008141437381921687</v>
+        <v>0.008141437381921697</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00812198379199913</v>
+        <v>0.008121983791999134</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008141985766825741</v>
+        <v>0.008141985766825736</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005299225349344408</v>
+        <v>0.005299225349344405</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01105622188921168</v>
+        <v>0.01105622188921167</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006461936229051304</v>
+        <v>0.006461936229051311</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007981629278335073</v>
+        <v>0.007981629278335074</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007983677739699923</v>
+        <v>0.007983677739699924</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009720279654942416</v>
+        <v>0.009720279654942418</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007964222604185686</v>
+        <v>0.007964222604185684</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007980631212425393</v>
+        <v>0.007980631212425383</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007983676756534695</v>
+        <v>0.007983676756534698</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007964223166619409</v>
+        <v>0.007964223166619407</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007983676756534695</v>
+        <v>0.007983676756534698</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006067533547894487</v>
+        <v>0.007066202927313678</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007983676756534695</v>
+        <v>0.007983676756534698</v>
       </c>
     </row>
     <row r="8">
@@ -2339,13 +2339,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01321442097115584</v>
+        <v>0.01321442097115583</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003973469957205045</v>
+        <v>0.003973469957205044</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03158550570000035</v>
+        <v>0.03158550570000034</v>
       </c>
       <c r="E8" t="n">
         <v>0.01268634282182651</v>
@@ -2354,22 +2354,22 @@
         <v>0.01268634282182651</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01318137390588795</v>
+        <v>0.01318137390588794</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03158611522285859</v>
+        <v>0.03158611522285858</v>
       </c>
       <c r="I8" t="n">
         <v>0.01268634282182651</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01801283402822754</v>
+        <v>0.01801283402822753</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01733040891645334</v>
+        <v>0.01733040891645332</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02105067518007834</v>
+        <v>0.02105067518007835</v>
       </c>
     </row>
     <row r="9">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01303174530828393</v>
+        <v>0.01303174530828394</v>
       </c>
       <c r="C9" t="n">
         <v>0.004103028441628763</v>
@@ -2388,28 +2388,28 @@
         <v>0.03138089396196921</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01254069352182794</v>
+        <v>0.01254069352182793</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01254069352182794</v>
+        <v>0.01254069352182793</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01319047266448171</v>
+        <v>0.01319047266448172</v>
       </c>
       <c r="H9" t="n">
         <v>0.0313816518727442</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01254069352182794</v>
+        <v>0.01254069352182793</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01817202710165415</v>
+        <v>0.01817202710165416</v>
       </c>
       <c r="K9" t="n">
         <v>0.01712821200148185</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02084553529335621</v>
+        <v>0.02084553529335622</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008388538039507036</v>
+        <v>0.008388538039507034</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006137795201643195</v>
+        <v>0.006137795201643188</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03134147627226712</v>
+        <v>0.03134147627226708</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01528411396059481</v>
+        <v>0.01528411396059477</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01528411396059481</v>
+        <v>0.01528411396059477</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03339442840766498</v>
+        <v>0.03339442840766522</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07933456951320431</v>
+        <v>0.07933456951320426</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01528411396059481</v>
+        <v>0.01528411396059477</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08962499778150901</v>
+        <v>0.08962499778150905</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02172253553758004</v>
+        <v>0.02172253553758008</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07232629067457073</v>
+        <v>0.07232629067457066</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001886809246219494</v>
+        <v>0.001886809246219496</v>
       </c>
       <c r="C3" t="n">
         <v>0.001648299554604904</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001886809246219494</v>
+        <v>0.001886809246219496</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00179081784792881</v>
+        <v>0.001790817847928813</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00179081784792881</v>
+        <v>0.001790817847928813</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00188271537607006</v>
+        <v>0.001882715376070062</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001886809246219494</v>
+        <v>0.001886809246219496</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001860457238970533</v>
+        <v>0.001860457238970535</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001886809246219494</v>
+        <v>0.001886809246219496</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001886809246219494</v>
+        <v>0.001886809246219496</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001886809246219494</v>
+        <v>0.001886809246219496</v>
       </c>
     </row>
     <row r="4">
@@ -2575,31 +2575,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002841669375381188</v>
+        <v>0.002841669375381187</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002753579018363816</v>
+        <v>0.002753579018363774</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002854409322470075</v>
+        <v>0.002854394960189425</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002639821923523765</v>
+        <v>0.002639821923523751</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002812360300715146</v>
+        <v>0.002812360300715144</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002837575505231753</v>
+        <v>0.002837575505231755</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00488206898596043</v>
+        <v>0.004882068985960431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002815317368132226</v>
+        <v>0.00467586936110018</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004740643537151651</v>
+        <v>0.002966882624871534</v>
       </c>
       <c r="K4" t="n">
         <v>0.002815375813007793</v>
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003677748585037997</v>
+        <v>0.003677748585038001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003674744582635017</v>
+        <v>0.003674744582635022</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003677616607705859</v>
+        <v>0.003677616607705861</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00364917143292277</v>
+        <v>0.003649171432922771</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00364917143292277</v>
+        <v>0.003649171432922771</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003673654714888568</v>
+        <v>0.003673654714888571</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003677748585037997</v>
+        <v>0.003677748585038001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003651396577789039</v>
+        <v>0.00365139657778904</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003677748585037997</v>
+        <v>0.003677748585038001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003677748585037997</v>
+        <v>0.003677748585038001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003677748585037997</v>
+        <v>0.003677748585038001</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005765691605476726</v>
+        <v>0.005765691605476737</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008813260737671795</v>
+        <v>0.00881326073769583</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00945047213175286</v>
+        <v>0.009450472131752865</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007955349721173503</v>
+        <v>0.007955349721173517</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005834832733933193</v>
+        <v>0.005834832733933202</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008813538469241577</v>
+        <v>0.008813538469241589</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00881763233939472</v>
+        <v>0.008817632339394744</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008791280332142045</v>
+        <v>0.008791280332142064</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008818232128258418</v>
+        <v>0.008818232128258425</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005709000239961952</v>
+        <v>0.005709000239961961</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01200563963040365</v>
+        <v>0.01200563963040368</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007951241525159955</v>
+        <v>0.007951241525159946</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009881029632084769</v>
+        <v>0.009881029632084759</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009884034511382126</v>
+        <v>0.009884034511382115</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01208808216605156</v>
+        <v>0.01208808216605154</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009857680534252556</v>
+        <v>0.009857680534252551</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009879939764338323</v>
+        <v>0.009879939764338321</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009884033634487751</v>
+        <v>0.009884033634487758</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009857681627238775</v>
+        <v>0.009857681627238773</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009884033634487751</v>
+        <v>0.009884033634487754</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007450303139400719</v>
+        <v>0.008764166664501211</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009884033634487751</v>
+        <v>0.009884033634487754</v>
       </c>
     </row>
     <row r="8">
@@ -2735,31 +2735,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01297647063303007</v>
+        <v>0.01297647063303008</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00432133230662683</v>
+        <v>0.004321332306626831</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03154135758051137</v>
+        <v>0.03154135758051139</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01280499326453413</v>
+        <v>0.01280499326453414</v>
       </c>
       <c r="F8" t="n">
         <v>0.01280499326453414</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01304427234481764</v>
+        <v>0.01304427234481765</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03064465934144672</v>
+        <v>0.03064465934144673</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01280499326453413</v>
+        <v>0.01280499326453414</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01768145314740405</v>
+        <v>0.01768145314740404</v>
       </c>
       <c r="K8" t="n">
         <v>0.01708647292303034</v>
@@ -2790,7 +2790,7 @@
         <v>0.01274470477401195</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01321111924810602</v>
+        <v>0.01321111924810603</v>
       </c>
       <c r="H9" t="n">
         <v>0.03103993077029079</v>
@@ -2799,10 +2799,10 @@
         <v>0.01274470477401195</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01847926407473055</v>
+        <v>0.01847926407473056</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01704568839691959</v>
+        <v>0.01704568839691958</v>
       </c>
       <c r="L9" t="n">
         <v>0.02107513776456153</v>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005198466382038588</v>
+        <v>0.005198466382038585</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005127845214557044</v>
+        <v>0.005127845214557051</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00711250352679292</v>
+        <v>0.007112503526792922</v>
       </c>
       <c r="E2" t="n">
-        <v>0.009081793582635845</v>
+        <v>0.0090817935826358</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009081793582635845</v>
+        <v>0.0090817935826358</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009517418256800671</v>
+        <v>0.009517418256800532</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01047196825025021</v>
+        <v>0.01047196825025019</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009081793582635845</v>
+        <v>0.0090817935826358</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03248225024539838</v>
+        <v>0.03248225024539839</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007080222848930499</v>
+        <v>0.007080222848930491</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01447913099938981</v>
+        <v>0.01447913099938982</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001754669938296525</v>
+        <v>0.001754669938296523</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001583517109753739</v>
+        <v>0.001583517109753743</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001754669938296525</v>
+        <v>0.001754669938296523</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00179696435656099</v>
+        <v>0.001796964356560991</v>
       </c>
       <c r="F3" t="n">
         <v>0.00179696435656099</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001751525319613145</v>
+        <v>0.00175152531961315</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001754669938296525</v>
+        <v>0.001754669938296523</v>
       </c>
       <c r="I3" t="n">
         <v>0.001734429856190042</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001754669938296525</v>
+        <v>0.001754669938296523</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001754669938296525</v>
+        <v>0.001754669938296523</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001754669938296525</v>
+        <v>0.001754669938296523</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002672961301823669</v>
+        <v>0.00267296130182368</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002626612840408738</v>
+        <v>0.002626612840408717</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002669955821201308</v>
+        <v>0.004340880291037994</v>
       </c>
       <c r="E4" t="n">
         <v>0.002527037261642961</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002661118796918107</v>
+        <v>0.002661118796918112</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004320491282586176</v>
+        <v>0.002669816683140303</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004462816965655172</v>
+        <v>0.004462816965655168</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004303395819163073</v>
+        <v>0.004303395819163075</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002778857106846744</v>
+        <v>0.004343026123457692</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002666931222593022</v>
+        <v>0.002666931222593026</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002666080672504581</v>
+        <v>0.00266608067250458</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00329105714919862</v>
+        <v>0.003291057149198619</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003289065050191362</v>
+        <v>0.003289065050191364</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003290932262879975</v>
+        <v>0.003290932262879971</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003269534039581222</v>
+        <v>0.003269534039581218</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003269534039581222</v>
+        <v>0.003269534039581218</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003287912530515249</v>
+        <v>0.003287912530515247</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00329105714919862</v>
+        <v>0.003291057149198619</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003270817067092143</v>
+        <v>0.003270817067092147</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00329105714919862</v>
+        <v>0.003291057149198619</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00329105714919862</v>
+        <v>0.003291057149198619</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00329105714919862</v>
+        <v>0.003291057149198619</v>
       </c>
     </row>
     <row r="6">
@@ -3051,34 +3051,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005161504581047077</v>
+        <v>0.005161504581047074</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007845751202898276</v>
+        <v>0.007845751202875765</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008405414219182674</v>
+        <v>0.008405414219182681</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007092722057283985</v>
+        <v>0.007092722057283983</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005225740609654746</v>
+        <v>0.00522574060965474</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007845146839153537</v>
+        <v>0.007845146839153539</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007848291457842549</v>
+        <v>0.007848291457842538</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007828051375730432</v>
+        <v>0.007828051375730427</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007848819483759895</v>
+        <v>0.007848819483759897</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005111596135872939</v>
+        <v>0.005111596135872943</v>
       </c>
       <c r="L6" t="n">
         <v>0.01065486501166152</v>
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006535427414977753</v>
+        <v>0.006535427414977757</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008082833249957257</v>
+        <v>0.008082833249957249</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008084826294991481</v>
+        <v>0.008084826294991476</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009852558173167408</v>
+        <v>0.00985255817316741</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008064585017132706</v>
+        <v>0.008064585017132709</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008081680730281133</v>
+        <v>0.008081680730281135</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008084825348964503</v>
+        <v>0.0080848253489645</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00806458526685803</v>
+        <v>0.008064585266858031</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008084825348964503</v>
+        <v>0.0080848253489645</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006133856538332408</v>
+        <v>0.007187098498952584</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008084825348964503</v>
+        <v>0.0080848253489645</v>
       </c>
     </row>
     <row r="8">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01287524622692727</v>
+        <v>0.01287524622692726</v>
       </c>
       <c r="C8" t="n">
         <v>0.004245569685165849</v>
@@ -3155,10 +3155,10 @@
         <v>0.01281992243581753</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01877521331686112</v>
+        <v>0.01877521331686114</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01726249802772419</v>
+        <v>0.01726249802772416</v>
       </c>
       <c r="L8" t="n">
         <v>0.02106109238040337</v>
@@ -3171,13 +3171,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0126828169379913</v>
+        <v>0.01268281693799131</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004188023420486172</v>
+        <v>0.004188023420486175</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03150035813141605</v>
+        <v>0.03150035813141604</v>
       </c>
       <c r="E9" t="n">
         <v>0.01268422928757309</v>
@@ -3195,10 +3195,10 @@
         <v>0.01268422928757309</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01885482905251635</v>
+        <v>0.01885482905251636</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01702967172765275</v>
+        <v>0.01702967172765272</v>
       </c>
       <c r="L9" t="n">
         <v>0.02084855014082519</v>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004787601138402727</v>
+        <v>0.004787601138402704</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005026994911117034</v>
+        <v>0.005026994911117036</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006280820107376111</v>
+        <v>0.006280820107376094</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007059053534686497</v>
+        <v>0.00705905353468651</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007059053534686497</v>
+        <v>0.00705905353468651</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006272650339458353</v>
+        <v>0.006272650339458395</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007278489898038309</v>
+        <v>0.007278489898038296</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007059053534686497</v>
+        <v>0.00705905353468651</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01065386674301336</v>
+        <v>0.01065386674301335</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004726061164590055</v>
+        <v>0.004726061164590024</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006341881474188891</v>
+        <v>0.006341881474188886</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001715260004036619</v>
+        <v>0.001715260004036587</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001567164163008961</v>
+        <v>0.001567164163008963</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001715260004036619</v>
+        <v>0.001715260004036587</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00173537491582884</v>
+        <v>0.001735374915828841</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00173537491582884</v>
+        <v>0.001735374915828841</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001712698551005935</v>
+        <v>0.001712698551005803</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001715260004036619</v>
+        <v>0.001715260004036587</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001698887514830149</v>
+        <v>0.001698887514830004</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001715260004036619</v>
+        <v>0.001715260004036587</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001715260004036619</v>
+        <v>0.001715260004036587</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001715260004036619</v>
+        <v>0.001715260004036587</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004268627390457136</v>
+        <v>0.004268627390457121</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002610500526610462</v>
+        <v>0.002610500526610423</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002637706488720838</v>
+        <v>0.002637706488720824</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002501700226981079</v>
+        <v>0.002501700226981076</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00263695829184658</v>
+        <v>0.002636958291846589</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004266065937426369</v>
+        <v>0.004266065937426365</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00439533306294336</v>
+        <v>0.00263931102245253</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00263096493710115</v>
+        <v>0.004252254901250523</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004286838261771842</v>
+        <v>0.002748418093804572</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002648745385733776</v>
+        <v>0.002648745385733796</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002636162290615634</v>
+        <v>0.002636162290615605</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003183400990814461</v>
+        <v>0.003183400990814457</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003181624251000152</v>
+        <v>0.003181624251000153</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003183275443933316</v>
+        <v>0.003183275443933307</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003165521453556894</v>
+        <v>0.003165521453556899</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003165521453556894</v>
+        <v>0.003165521453556899</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003180839537783694</v>
+        <v>0.00318083953778368</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003183400990814461</v>
+        <v>0.003183400990814457</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003167028501607847</v>
+        <v>0.003167028501607856</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003183400990814461</v>
+        <v>0.003183400990814457</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003183400990814461</v>
+        <v>0.003183400990814457</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003183400990814461</v>
+        <v>0.003183400990814457</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005009888663704419</v>
+        <v>0.005009888663704411</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007606034390875907</v>
+        <v>0.007606034390898212</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008147446270319983</v>
+        <v>0.008147446270319972</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006880771545345486</v>
+        <v>0.006880771545345494</v>
       </c>
       <c r="F6" t="n">
         <v>0.005075066828264366</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007606027403659813</v>
+        <v>0.007606027403659823</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007608588856696104</v>
+        <v>0.007608588856696102</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007592216367483973</v>
+        <v>0.007592216367483974</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007609099571085791</v>
+        <v>0.007609099571085762</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004961616473902795</v>
+        <v>0.004961616473902781</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0103231485036184</v>
+        <v>0.01032314850361841</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006031524560798187</v>
+        <v>0.006031524560798186</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007443379053544841</v>
+        <v>0.007443379053544851</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007445156657496268</v>
+        <v>0.007445156657496279</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009060084258291317</v>
+        <v>0.009060084258291327</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007428783067693085</v>
+        <v>0.007428783067693092</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007442594340328376</v>
+        <v>0.00744259434032838</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007445155793359142</v>
+        <v>0.007445155793359128</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007428783304152529</v>
+        <v>0.007428783304152535</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007445155793359142</v>
+        <v>0.007445155793359128</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006592862208258009</v>
+        <v>0.006626092668907794</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007445155793359142</v>
+        <v>0.007445155793359128</v>
       </c>
     </row>
     <row r="8">
@@ -3530,10 +3530,10 @@
         <v>0.01269249558780865</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004184656732816539</v>
+        <v>0.004184656732816542</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0319222429505335</v>
+        <v>0.03192224295053349</v>
       </c>
       <c r="E8" t="n">
         <v>0.01260147207500169</v>
@@ -3545,7 +3545,7 @@
         <v>0.0133607977355599</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03191482320120554</v>
+        <v>0.03191482320120553</v>
       </c>
       <c r="I8" t="n">
         <v>0.01260147207500169</v>
@@ -3554,7 +3554,7 @@
         <v>0.01847400408178218</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01730800078548638</v>
+        <v>0.01730800078548639</v>
       </c>
       <c r="L8" t="n">
         <v>0.0211286983124853</v>
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01249735257578451</v>
+        <v>0.01249735257578452</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004126695335222626</v>
+        <v>0.004126695335222629</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03144906707839094</v>
+        <v>0.03144906707839096</v>
       </c>
       <c r="E9" t="n">
         <v>0.01244101569445684</v>
@@ -3591,13 +3591,13 @@
         <v>0.01244101569445684</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01826640385518086</v>
+        <v>0.01826640385518087</v>
       </c>
       <c r="K9" t="n">
         <v>0.01704150898927293</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02081594406070841</v>
+        <v>0.02081594406070838</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007103434848175331</v>
+        <v>0.007103434848175363</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00553228792793691</v>
+        <v>0.005532287927936906</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01142022564100612</v>
+        <v>0.01142022564100619</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01225451085715709</v>
+        <v>0.01225451085715714</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01225451085715709</v>
+        <v>0.01225451085715714</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01815712033422169</v>
+        <v>0.01815712033422158</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06630544994135412</v>
+        <v>0.06630544994135425</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01225451085715709</v>
+        <v>0.01225451085715714</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02868434113430157</v>
+        <v>0.02868434113430156</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01292335779125222</v>
+        <v>0.01292335779125231</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0583850476110012</v>
+        <v>0.05838504761100134</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00183504693238802</v>
+        <v>0.001835046932388057</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001607930547774585</v>
+        <v>0.001607930547774586</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00183504693238802</v>
+        <v>0.001835046932388057</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001750123958038376</v>
+        <v>0.001750123958038375</v>
       </c>
       <c r="F3" t="n">
         <v>0.001750123958038376</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001831376945112622</v>
+        <v>0.00183137694511261</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00183504693238802</v>
+        <v>0.001835046932388057</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001811388639970366</v>
+        <v>0.001811388639970369</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00183504693238802</v>
+        <v>0.001835046932388057</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00183504693238802</v>
+        <v>0.001835046932388057</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00183504693238802</v>
+        <v>0.001835046932388057</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002741923681192476</v>
+        <v>0.00274192368119252</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002676149818165979</v>
+        <v>0.002676149818165934</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00273565820461568</v>
+        <v>0.002735658204615726</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002563433306903295</v>
+        <v>0.002563433306903294</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002716560433817557</v>
+        <v>0.002716560433817553</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004533976288793722</v>
+        <v>0.002738253693917093</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004711932119390429</v>
+        <v>0.004711932119390473</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004513987983651503</v>
+        <v>0.002718265388774842</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004570817771892532</v>
+        <v>0.002843807945302514</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002718714568802271</v>
+        <v>0.002718714568802379</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002751903437710974</v>
+        <v>0.002751903437710997</v>
       </c>
     </row>
     <row r="5">
@@ -3803,13 +3803,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003530631108976231</v>
+        <v>0.003530631108976274</v>
       </c>
       <c r="C5" t="n">
         <v>0.003528272599642559</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003530499686440865</v>
+        <v>0.003530499686440916</v>
       </c>
       <c r="E5" t="n">
         <v>0.003505179885141848</v>
@@ -3818,22 +3818,22 @@
         <v>0.003505179885141848</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003526961121700788</v>
+        <v>0.003526961121700844</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003530631108976231</v>
+        <v>0.003530631108976274</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003506972816558556</v>
+        <v>0.003506972816558557</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003530631108976231</v>
+        <v>0.003530631108976274</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003530631108976231</v>
+        <v>0.003530631108976274</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003530631108976231</v>
+        <v>0.003530631108976274</v>
       </c>
     </row>
     <row r="6">
@@ -3843,13 +3843,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005553806513798553</v>
+        <v>0.00555380651379861</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008481471662992662</v>
+        <v>0.008481471662969049</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009092571244205665</v>
+        <v>0.009092571244205719</v>
       </c>
       <c r="E6" t="n">
         <v>0.007658643185182562</v>
@@ -3858,22 +3858,22 @@
         <v>0.00562206530107049</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008481138834936048</v>
+        <v>0.008481138834936128</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008484808822215167</v>
+        <v>0.008484808822215164</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008461150529793812</v>
+        <v>0.008461150529793814</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008485384843225408</v>
+        <v>0.00848538484322545</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005499361641626096</v>
+        <v>0.005499361641626119</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01154648581509289</v>
+        <v>0.01154648581509294</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007513877490128536</v>
+        <v>0.007513877490128573</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009329315218013468</v>
+        <v>0.009329315218013456</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009331674249963257</v>
+        <v>0.009331674249963298</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01140571298639455</v>
+        <v>0.01140571298639453</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009308014446759274</v>
+        <v>0.009308014446759267</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009328003740071703</v>
+        <v>0.009328003740071731</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00933167372734714</v>
+        <v>0.009331673727347164</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009308015434929465</v>
+        <v>0.009308015434929448</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00933167372734714</v>
+        <v>0.009331673727347164</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008278435668276274</v>
+        <v>0.00827843566827628</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009331673727347141</v>
+        <v>0.009331673727347164</v>
       </c>
     </row>
     <row r="8">
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01288060869667596</v>
+        <v>0.012880608696676</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004291681786235068</v>
+        <v>0.004291681786235066</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03193255233863058</v>
+        <v>0.03193255233863061</v>
       </c>
       <c r="E8" t="n">
         <v>0.01280677093188643</v>
@@ -3938,10 +3938,10 @@
         <v>0.01280677093188643</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01330466873369813</v>
+        <v>0.01330466873369814</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0308411001905714</v>
+        <v>0.03084110019057143</v>
       </c>
       <c r="I8" t="n">
         <v>0.01280677093188643</v>
@@ -3950,10 +3950,10 @@
         <v>0.01888759825989961</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01717626247295969</v>
+        <v>0.01717626247295973</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0208426463157801</v>
+        <v>0.02084264631578013</v>
       </c>
     </row>
     <row r="9">
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01270931833035491</v>
+        <v>0.01270931833035496</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004235167133906717</v>
+        <v>0.004235167133906716</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03152328788603363</v>
+        <v>0.03152328788603367</v>
       </c>
       <c r="E9" t="n">
         <v>0.01270670841145483</v>
@@ -3981,19 +3981,19 @@
         <v>0.01327033424234771</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03107996001259</v>
+        <v>0.03107996001259004</v>
       </c>
       <c r="I9" t="n">
         <v>0.01270670841145483</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01889462190420478</v>
+        <v>0.0188946219042048</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01701740316711428</v>
+        <v>0.01701740316711429</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02113124768423742</v>
+        <v>0.02113124768423744</v>
       </c>
     </row>
   </sheetData>
@@ -4079,34 +4079,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005354084426659737</v>
+        <v>0.00535408442665974</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005172352947111832</v>
+        <v>0.00517235294711183</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006501485706427696</v>
+        <v>0.006501485706427678</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008350195041873353</v>
+        <v>0.008350195041873364</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008350195041873353</v>
+        <v>0.008350195041873364</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006707667015885079</v>
+        <v>0.006707667015884857</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00755417375335835</v>
+        <v>0.007554173753358338</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008350195041873353</v>
+        <v>0.008350195041873364</v>
       </c>
       <c r="J2" t="n">
         <v>0.01057396227069986</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005967534082374193</v>
+        <v>0.005967534082374179</v>
       </c>
       <c r="L2" t="n">
         <v>0.006730537782381709</v>
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00172594612465803</v>
+        <v>0.001725946124658029</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001559300971515475</v>
+        <v>0.001559300971515469</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00172594612465803</v>
+        <v>0.001725946124658029</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001772047360134172</v>
+        <v>0.001772047360134173</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001772047360134172</v>
+        <v>0.001772047360134173</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001722914569032447</v>
+        <v>0.001722914569032446</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00172594612465803</v>
+        <v>0.001725946124658029</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001706431343308604</v>
+        <v>0.001706431343308607</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00172594612465803</v>
+        <v>0.001725946124658029</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00172594612465803</v>
+        <v>0.001725946124658029</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00172594612465803</v>
+        <v>0.001725946124658029</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002637685308026777</v>
+        <v>0.00426692555197127</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002595980857572902</v>
+        <v>0.002595980857572844</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002637157652887501</v>
+        <v>0.002637172202506244</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002496893742078492</v>
+        <v>0.002496893742078495</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002626680198691953</v>
+        <v>0.002626680198691946</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002634653752401192</v>
+        <v>0.002634653752401187</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004402230362985155</v>
+        <v>0.004402230362985153</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004247410770621858</v>
+        <v>0.004247410770621846</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004283989771770829</v>
+        <v>0.002734974356471034</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002633082506303082</v>
+        <v>0.002633082506303072</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002628500010218414</v>
+        <v>0.002628500010218411</v>
       </c>
     </row>
     <row r="5">
@@ -4202,25 +4202,25 @@
         <v>0.00319922332020143</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003197375124349464</v>
+        <v>0.003197375124349455</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003199098327213353</v>
+        <v>0.003199098327213346</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003178934963023404</v>
+        <v>0.003178934963023399</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003178934963023404</v>
+        <v>0.003178934963023399</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003196191764575849</v>
+        <v>0.003196191764575841</v>
       </c>
       <c r="H5" t="n">
         <v>0.00319922332020143</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003179708538852008</v>
+        <v>0.003179708538852003</v>
       </c>
       <c r="J5" t="n">
         <v>0.00319922332020143</v>
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005022010809132922</v>
+        <v>0.005022010809132915</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00762288874301345</v>
+        <v>0.007622888743013432</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008164522406374856</v>
+        <v>0.00816452240637483</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006893359591802238</v>
+        <v>0.006893359591802231</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005084613967108605</v>
+        <v>0.005084613967108603</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007621782617816182</v>
+        <v>0.007621782617816179</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007624814173447454</v>
+        <v>0.00762481417344743</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007605299392092355</v>
+        <v>0.007605299392092339</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007625325694220673</v>
+        <v>0.007625325694220648</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004973662400818494</v>
+        <v>0.004973662400818486</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01034365992591163</v>
+        <v>0.01034365992591161</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006407180663522125</v>
+        <v>0.006407180663522114</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007921286765654628</v>
+        <v>0.007921286765654612</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007923135841584026</v>
+        <v>0.007923135841584</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009652999838470198</v>
+        <v>0.009652999838470185</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007903619977189963</v>
+        <v>0.00790361997718996</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007920103405881005</v>
+        <v>0.007920103405880992</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007923134961506593</v>
+        <v>0.007923134961506578</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007903620180157164</v>
+        <v>0.007903620180157158</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007923134961506593</v>
+        <v>0.007923134961506578</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007044785457799557</v>
+        <v>0.006014277675361981</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007923134961506593</v>
+        <v>0.007923134961506578</v>
       </c>
     </row>
     <row r="8">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01201542540907251</v>
+        <v>0.01201542540907252</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004215689634909165</v>
+        <v>0.004215689634909166</v>
       </c>
       <c r="D8" t="n">
         <v>0.03192790107988223</v>
@@ -4337,7 +4337,7 @@
         <v>0.01338420255340505</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03191991406148726</v>
+        <v>0.03191991406148725</v>
       </c>
       <c r="I8" t="n">
         <v>0.01277560070983339</v>
@@ -4346,10 +4346,10 @@
         <v>0.01920142583412651</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01712232768857955</v>
+        <v>0.01712232768857952</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02118246476235976</v>
+        <v>0.02118246476235975</v>
       </c>
     </row>
     <row r="9">
@@ -4383,10 +4383,10 @@
         <v>0.01263051723176428</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01898142523616543</v>
+        <v>0.01898142523616541</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01687620116844031</v>
+        <v>0.0168762011684403</v>
       </c>
       <c r="L9" t="n">
         <v>0.02087366898383702</v>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004927105700420284</v>
+        <v>0.004927105700420282</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004990399476253677</v>
+        <v>0.004990399476253659</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005883198021152711</v>
+        <v>0.005883198021152699</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006623179054222079</v>
+        <v>0.00662317905422206</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006623179054222079</v>
+        <v>0.00662317905422206</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005840995567802906</v>
+        <v>0.005840995567802894</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006879947514365177</v>
+        <v>0.006879947514365162</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006623179054222079</v>
+        <v>0.00662317905422206</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009120230598555597</v>
+        <v>0.009120230598555584</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005356066019896506</v>
+        <v>0.005356066019896508</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00622192917874962</v>
+        <v>0.006221929178749623</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001692398078956099</v>
+        <v>0.001692398078956098</v>
       </c>
       <c r="C3" t="n">
         <v>0.001546963105914289</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001692398078956099</v>
+        <v>0.001692398078956098</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001714372924653488</v>
+        <v>0.001714372924653482</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001714372924653488</v>
+        <v>0.001714372924653482</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001689997871745952</v>
+        <v>0.001689997871745951</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001692398078956099</v>
+        <v>0.001692398078956098</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0016770971292212</v>
+        <v>0.001677097129221193</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001692398078956099</v>
+        <v>0.001692398078956098</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001692398078956099</v>
+        <v>0.001692398078956098</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001692398078956099</v>
+        <v>0.001692398078956098</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002628971228534984</v>
+        <v>0.004236507458257716</v>
       </c>
       <c r="C4" t="n">
         <v>0.002593016331446116</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002618949308496892</v>
+        <v>0.00261893437314459</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002484790585373181</v>
+        <v>0.002484790585373179</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002619517333004789</v>
+        <v>0.002619517333004792</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004234107251047563</v>
+        <v>0.002626571021324839</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004361080974350314</v>
+        <v>0.004361080974350312</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004221206508522808</v>
+        <v>0.002613670278800083</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002728521009699269</v>
+        <v>0.004253098410881679</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002632222907516663</v>
+        <v>0.00263222290751666</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002617750444001636</v>
+        <v>0.002617750444001794</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003108881628687052</v>
+        <v>0.003108881628687049</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003107142245510632</v>
+        <v>0.003107142245510629</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003108755939527985</v>
+        <v>0.003108755939527991</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003092285227884302</v>
+        <v>0.003092285227884298</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003092285227884302</v>
+        <v>0.003092285227884298</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003106481421476903</v>
+        <v>0.003106481421476908</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003108881628687052</v>
+        <v>0.003108881628687049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003093580678952149</v>
+        <v>0.003093580678952145</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003108881628687052</v>
+        <v>0.003108881628687049</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003108881628687052</v>
+        <v>0.003108881628687049</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003108881628687052</v>
+        <v>0.003108881628687049</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004892427061848096</v>
+        <v>0.004892427061848089</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007417626772045919</v>
+        <v>0.007417626772023726</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007944054346479115</v>
+        <v>0.007944054346479103</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006712842646065463</v>
+        <v>0.006712842646065438</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004956547027072154</v>
+        <v>0.004956547027072142</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007417554762585043</v>
+        <v>0.007417554762585041</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00741995496980092</v>
+        <v>0.007419954969800909</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007404654020060284</v>
+        <v>0.007404654020060271</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007420451696824306</v>
+        <v>0.007420451696824291</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004845476933778668</v>
+        <v>0.004845476933778659</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01006016921369581</v>
+        <v>0.0100601692136958</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005957009240330934</v>
+        <v>0.005957009240330923</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007349800135595749</v>
+        <v>0.00734980013559574</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007351540358933561</v>
+        <v>0.007351540358933551</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0089454974365001</v>
+        <v>0.008945497436500081</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007336238357414719</v>
+        <v>0.007336238357414715</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007349139311562017</v>
+        <v>0.007349139311562005</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007351539518772167</v>
+        <v>0.007351539518772162</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007336238569037263</v>
+        <v>0.007336238569037242</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007351539518772167</v>
+        <v>0.007351539518772162</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006510762100961611</v>
+        <v>0.006510762100961613</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007351539518772167</v>
+        <v>0.007351539518772162</v>
       </c>
     </row>
     <row r="8">
@@ -4715,34 +4715,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009702809561004479</v>
+        <v>0.009702809561004493</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004160801085830472</v>
+        <v>0.004160801085830471</v>
       </c>
       <c r="D8" t="n">
         <v>0.03189091433418982</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01256548660904037</v>
+        <v>0.01256548660904036</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01256548660904037</v>
+        <v>0.01256548660904036</v>
       </c>
       <c r="G8" t="n">
         <v>0.01306533004994506</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03188239471852944</v>
+        <v>0.03188239471852945</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01256548660904037</v>
+        <v>0.01256548660904036</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01845234049273592</v>
+        <v>0.01845234049273591</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0171856370093778</v>
+        <v>0.01718563700937781</v>
       </c>
       <c r="L8" t="n">
         <v>0.02109653736828771</v>
@@ -4755,13 +4755,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009556428582742242</v>
+        <v>0.009556428582742247</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004102740534816538</v>
+        <v>0.00410274053481654</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03141272615405624</v>
+        <v>0.03141272615405625</v>
       </c>
       <c r="E9" t="n">
         <v>0.01239959742360737</v>
@@ -4782,7 +4782,7 @@
         <v>0.0182246550857356</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01692998984241007</v>
+        <v>0.01692998984241006</v>
       </c>
       <c r="L9" t="n">
         <v>0.02078290374354555</v>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06345077488167605</v>
+        <v>0.06345077488167671</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03062198606440342</v>
+        <v>0.03062198606440332</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08602154121344377</v>
+        <v>0.08602154121344371</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03062198606440342</v>
+        <v>0.03062198606440332</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03062198606440342</v>
+        <v>0.03062198606440332</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0887620750240064</v>
+        <v>0.08876207502400651</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1894244824514295</v>
+        <v>0.1894244824514291</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03062198606440342</v>
+        <v>0.03062198606440332</v>
       </c>
       <c r="J2" t="n">
         <v>0.1467683547870894</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04459054553269378</v>
+        <v>0.0445905455326939</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0883220124811049</v>
+        <v>0.08832201248110491</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002170093901040789</v>
+        <v>0.002170093901040796</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001935232285084626</v>
+        <v>0.001935232285084627</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002170093901040789</v>
+        <v>0.002170093901040796</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001991390055907651</v>
+        <v>0.001991390055907653</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00199139005590765</v>
+        <v>0.001991390055907652</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002166018069272851</v>
+        <v>0.002166018069272854</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002170093901040789</v>
+        <v>0.002170093901040796</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002144238959910435</v>
+        <v>0.002144238959910436</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002170093901040789</v>
+        <v>0.002170093901040796</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002170093901040789</v>
+        <v>0.002170093901040796</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002170093901040789</v>
+        <v>0.002170093901040796</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005556787065599601</v>
+        <v>0.003321575432918575</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003178603055135453</v>
+        <v>0.003178603055135465</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003365977745935551</v>
+        <v>0.00336598833102498</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003043491833797405</v>
+        <v>0.003043491833797404</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003282443230742115</v>
+        <v>0.003282443230742118</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005552711233831663</v>
+        <v>0.003317499601150635</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005710944429718896</v>
+        <v>0.005710944429718903</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005530932124469248</v>
+        <v>0.005530932124469257</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005600600637604351</v>
+        <v>0.003474133724602417</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003261636885275809</v>
+        <v>0.003261636885275806</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003410101416176468</v>
+        <v>0.003410101416176479</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00420807690536049</v>
+        <v>0.004208076905360483</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004182221964230138</v>
+        <v>0.004182221964230141</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00420793129139441</v>
+        <v>0.004207931291394417</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004179509206616704</v>
+        <v>0.004179509206616706</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004179509206616704</v>
+        <v>0.004179509206616706</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004204001073592555</v>
+        <v>0.004204001073592556</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00420807690536049</v>
+        <v>0.004208076905360483</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004182221964230138</v>
+        <v>0.004182221964230141</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00420807690536049</v>
+        <v>0.004208076905360483</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00420807690536049</v>
+        <v>0.004208076905360483</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00420807690536049</v>
+        <v>0.004208076905360483</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006479413638493401</v>
+        <v>0.006479413638493399</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009825376073157388</v>
+        <v>0.00982537607318055</v>
       </c>
       <c r="D6" t="n">
         <v>0.01055251833295686</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008902888607986737</v>
+        <v>0.008902888607986733</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006558964312738251</v>
+        <v>0.006558964312738243</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009848910273755326</v>
+        <v>0.009848910273755325</v>
       </c>
       <c r="H6" t="n">
         <v>0.009852986105523338</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009827131164392901</v>
+        <v>0.009827131164392893</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009853649104057886</v>
+        <v>0.009853649104057879</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006416747798431167</v>
+        <v>0.006416747798431161</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01337696463598976</v>
+        <v>0.01337696463598973</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009864787873805384</v>
+        <v>0.009864787873805372</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01224353397023167</v>
+        <v>0.01224353397023169</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01226938972163801</v>
+        <v>0.01226938972163802</v>
       </c>
       <c r="E7" t="n">
         <v>0.01501838982746909</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01224353118079366</v>
+        <v>0.01224353118079367</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01226531307959412</v>
+        <v>0.01226531307959411</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01226938891136206</v>
+        <v>0.01226938891136205</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01224353397023167</v>
+        <v>0.01224353397023169</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01226938891136206</v>
+        <v>0.01226938891136205</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01087615396740368</v>
+        <v>0.01087615396740369</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01226938891136206</v>
+        <v>0.01226938891136205</v>
       </c>
     </row>
     <row r="8">
@@ -5111,13 +5111,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01376848166752648</v>
+        <v>0.0137684816675265</v>
       </c>
       <c r="C8" t="n">
         <v>0.01450630603016532</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01328260862908422</v>
+        <v>0.01328260862908424</v>
       </c>
       <c r="E8" t="n">
         <v>0.01450630603016532</v>
@@ -5129,7 +5129,7 @@
         <v>0.01325575599586365</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01139946380649831</v>
+        <v>0.01139946380649833</v>
       </c>
       <c r="I8" t="n">
         <v>0.01450630603016532</v>
@@ -5138,10 +5138,10 @@
         <v>0.0120861142660371</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01424345551709597</v>
+        <v>0.014243455517096</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01344921196437923</v>
+        <v>0.01344921196437925</v>
       </c>
     </row>
     <row r="9">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01435530456491293</v>
+        <v>0.01435530456491292</v>
       </c>
       <c r="C9" t="n">
         <v>0.01463421795542815</v>
@@ -5166,22 +5166,22 @@
         <v>0.01463421795542815</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01413994161166287</v>
+        <v>0.01413994161166288</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01339397286429207</v>
+        <v>0.01339397286429208</v>
       </c>
       <c r="I9" t="n">
         <v>0.01463421795542815</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01367128156947471</v>
+        <v>0.01367128156947472</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01454880991374687</v>
+        <v>0.01454880991374688</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01422658760723173</v>
+        <v>0.01241739823118823</v>
       </c>
     </row>
   </sheetData>
@@ -5267,34 +5267,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04716744173565753</v>
+        <v>0.04716744173565754</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03181714127897255</v>
+        <v>0.03181714127897251</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07644331850867397</v>
+        <v>0.07644331850867428</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03181714127897255</v>
+        <v>0.03181714127897251</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03181714127897255</v>
+        <v>0.03181714127897251</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0777125051803325</v>
+        <v>0.07771250518033285</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1496936545698072</v>
+        <v>0.1496936545698069</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03181714127897255</v>
+        <v>0.03181714127897251</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1146841342519505</v>
+        <v>0.1146841342519506</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03928774731611951</v>
+        <v>0.0392877473161195</v>
       </c>
       <c r="L2" t="n">
         <v>0.0939676100718371</v>
@@ -5310,34 +5310,34 @@
         <v>0.002084733527045311</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001910405473985352</v>
+        <v>0.001910405473985353</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002084733527045312</v>
+        <v>0.002084733527045309</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00195990012143082</v>
+        <v>0.001959900121430819</v>
       </c>
       <c r="F3" t="n">
         <v>0.00195990012143082</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002081221945685409</v>
+        <v>0.002081221945685417</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002084733527045312</v>
+        <v>0.002084733527045309</v>
       </c>
       <c r="I3" t="n">
         <v>0.00206252698659351</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002084733527045312</v>
+        <v>0.002084733527045309</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002084733527045312</v>
+        <v>0.002084733527045309</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002084733527045312</v>
+        <v>0.002084733527045309</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005277471443619916</v>
+        <v>0.003218977675976315</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00310483305194741</v>
+        <v>0.003104833051947395</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003258596597519062</v>
+        <v>0.003258596597518999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002973546422661816</v>
+        <v>0.002973546422661817</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003188001349013991</v>
+        <v>0.003188001349013997</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005273959862260016</v>
+        <v>0.003215466094616407</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005398290820687345</v>
+        <v>0.005398290820687346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005255264903168118</v>
+        <v>0.005255264903168116</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005308444682383293</v>
+        <v>0.003359745719516503</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003182301876143903</v>
+        <v>0.003182301876143909</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003296432207658358</v>
+        <v>0.003296432207658354</v>
       </c>
     </row>
     <row r="5">
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003915955671111861</v>
+        <v>0.003915955671111878</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003893749130660066</v>
+        <v>0.003893749130660065</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003915819882532603</v>
+        <v>0.003915819882532602</v>
       </c>
       <c r="E5" t="n">
         <v>0.003890744228688891</v>
@@ -5402,22 +5402,22 @@
         <v>0.003890744228688891</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003912444089751966</v>
+        <v>0.003912444089751964</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003915955671111863</v>
+        <v>0.003915955671111878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003893749130660066</v>
+        <v>0.003893749130660065</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003915955671111863</v>
+        <v>0.003915955671111878</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003915955671111863</v>
+        <v>0.003915955671111878</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003915955671111863</v>
+        <v>0.003915955671111878</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005972611184495654</v>
+        <v>0.005972611184495669</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008995108451351715</v>
+        <v>0.008995108451351728</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009651203689254612</v>
+        <v>0.009651203689254628</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008162027055324336</v>
+        <v>0.008162027055324345</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006045272427317916</v>
+        <v>0.006045272427317931</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009015915072520361</v>
+        <v>0.009015915072520374</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009019426653880658</v>
+        <v>0.009019426653880669</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008997220113428475</v>
+        <v>0.008997220113428479</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009020025435656354</v>
+        <v>0.009020025435656378</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005916015023388752</v>
+        <v>0.005916015023388761</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01220208017766772</v>
+        <v>0.01220208017766773</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008578356252666888</v>
+        <v>0.0085783562526669</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01060291807092259</v>
+        <v>0.01060291807092261</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01062512555081364</v>
+        <v>0.01062512555081365</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01296484347212846</v>
+        <v>0.01296484347212849</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01060291588254145</v>
+        <v>0.01060291588254147</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01062161303001449</v>
+        <v>0.0106216130300145</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01062512461137439</v>
+        <v>0.01062512461137441</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01060291807092259</v>
+        <v>0.01060291807092261</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01062512461137439</v>
+        <v>0.01062512461137441</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008047877657419407</v>
+        <v>0.009439219381184185</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01062512461137439</v>
+        <v>0.01062512461137441</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01405457538354192</v>
+        <v>0.01405457538354193</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01436575632199531</v>
+        <v>0.0143657563219953</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01330768150307006</v>
+        <v>0.01330768150307005</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01436575632199531</v>
+        <v>0.0143657563219953</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01436575632199531</v>
+        <v>0.0143657563219953</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01331726262547948</v>
+        <v>0.01331726262547946</v>
       </c>
       <c r="H8" t="n">
         <v>0.01195527697759339</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01436575632199531</v>
+        <v>0.0143657563219953</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01256314835626183</v>
+        <v>0.01256314835626184</v>
       </c>
       <c r="K8" t="n">
         <v>0.01420729055345842</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01313411884692599</v>
+        <v>0.01313411884692598</v>
       </c>
     </row>
     <row r="9">
@@ -5553,7 +5553,7 @@
         <v>0.01455011572543921</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01414494931567266</v>
+        <v>0.01414494931567265</v>
       </c>
       <c r="E9" t="n">
         <v>0.01455011572543921</v>
@@ -5562,7 +5562,7 @@
         <v>0.01455011572543921</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01414317818898566</v>
+        <v>0.01414317818898565</v>
       </c>
       <c r="H9" t="n">
         <v>0.01359707402616029</v>
@@ -5574,10 +5574,10 @@
         <v>0.01384265360072248</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0145113560833835</v>
+        <v>0.01451135608338352</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01407573409626907</v>
+        <v>0.01256498025921859</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04000340417198552</v>
+        <v>0.04000340417198566</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04042864123740598</v>
+        <v>0.04042864123740608</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06265018209929718</v>
+        <v>0.06265018209929724</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04042864123740598</v>
+        <v>0.04042864123740608</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04042864123740598</v>
+        <v>0.04042864123740608</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06794068886157931</v>
+        <v>0.06794068886157957</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1084064685278096</v>
+        <v>0.1084064685278095</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04042864123740598</v>
+        <v>0.04042864123740608</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09714896391398865</v>
+        <v>0.09714896391398872</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03206996890929868</v>
+        <v>0.03206996890929861</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2461506130700979</v>
+        <v>0.06293568166608257</v>
       </c>
     </row>
     <row r="3">
@@ -5703,13 +5703,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00209490462645045</v>
+        <v>0.002094904626450477</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001953298113603363</v>
+        <v>0.001953298113603367</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00209490462645045</v>
+        <v>0.002094904626450477</v>
       </c>
       <c r="E3" t="n">
         <v>0.002001200337374846</v>
@@ -5718,22 +5718,22 @@
         <v>0.002001200337374845</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002092009988635555</v>
+        <v>0.002092009988635556</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00209490462645045</v>
+        <v>0.002094904626450477</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002076619530926597</v>
+        <v>0.0020766195309266</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00209490462645045</v>
+        <v>0.002094904626450477</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00209490462645045</v>
+        <v>0.002094904626450477</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00209490462645045</v>
+        <v>0.002094904626450477</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00324690109351172</v>
+        <v>0.003246901093511738</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003172679923459372</v>
+        <v>0.003172679923459437</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005289949571571857</v>
+        <v>0.003261945322018143</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003039348465328672</v>
+        <v>0.003039348465328668</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003229716399945268</v>
+        <v>0.003229716399945267</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003244006455696829</v>
+        <v>0.005258339254587208</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005376172444817626</v>
+        <v>0.005376172444817642</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00524294879687822</v>
+        <v>0.003228615997987875</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003387136775872861</v>
+        <v>0.005293293274244153</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003215055686269427</v>
+        <v>0.00321505568626943</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003314982070317374</v>
+        <v>0.003314982070317382</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003881219593419521</v>
+        <v>0.003881219593419531</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003862934497895664</v>
+        <v>0.00386293449789567</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00388108320110408</v>
+        <v>0.003881083201104089</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003859796889507075</v>
+        <v>0.003859796889507078</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003859796889507075</v>
+        <v>0.003859796889507078</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003878324955604619</v>
+        <v>0.003878324955604626</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003881219593419518</v>
+        <v>0.003881219593419529</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003862934497895664</v>
+        <v>0.00386293449789567</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003881219593419518</v>
+        <v>0.003881219593419529</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003881219593419518</v>
+        <v>0.003881219593419529</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003881219593419518</v>
+        <v>0.003881219593419529</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005888004157988362</v>
+        <v>0.005888004157988376</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008843791493069755</v>
+        <v>0.008843791493069769</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009481487194195209</v>
+        <v>0.009481487194195223</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008030002785332599</v>
+        <v>0.008030002785332616</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005962273539566563</v>
+        <v>0.005962273539566571</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008861432581111918</v>
+        <v>0.008861432581111941</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008864327218927399</v>
+        <v>0.008864327218927425</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008846042123402951</v>
+        <v>0.00884604212340297</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008864912146942247</v>
+        <v>0.008864912146942282</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005832717429557806</v>
+        <v>0.005832717429557824</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01197334552762968</v>
+        <v>0.01197334552762971</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007973519996472859</v>
+        <v>0.007973519996472873</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009827449025311899</v>
+        <v>0.009827449025311914</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009845735188555544</v>
+        <v>0.009845735188555547</v>
       </c>
       <c r="E7" t="n">
         <v>0.01198794334233197</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009827447385040631</v>
+        <v>0.00982744738504065</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009842839483020872</v>
+        <v>0.009842839483020858</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009845734120835756</v>
+        <v>0.009845734120835755</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009827449025311899</v>
+        <v>0.009827449025311914</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009845734120835756</v>
+        <v>0.009845734120835755</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008760966353506473</v>
+        <v>0.008760966353506474</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009845734120835756</v>
+        <v>0.009845734120835755</v>
       </c>
     </row>
     <row r="8">
@@ -5903,19 +5903,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01400312997691058</v>
+        <v>0.01400312997691057</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01382861280926615</v>
+        <v>0.01382861280926614</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0134031883813006</v>
+        <v>0.01340318838130059</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01382861280926615</v>
+        <v>0.01382861280926614</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01382861280926615</v>
+        <v>0.01382861280926614</v>
       </c>
       <c r="G8" t="n">
         <v>0.01331902825434068</v>
@@ -5924,16 +5924,16 @@
         <v>0.01255468364081865</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01382861280926615</v>
+        <v>0.01382861280926614</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01277246679474018</v>
+        <v>0.01277246679474019</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01415540899886474</v>
+        <v>0.01415540899886473</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009782681274645289</v>
+        <v>0.009782681274645282</v>
       </c>
     </row>
     <row r="9">
@@ -5949,7 +5949,7 @@
         <v>0.01415936862409189</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01406682369117942</v>
+        <v>0.01406682369117941</v>
       </c>
       <c r="E9" t="n">
         <v>0.01415936862409189</v>
@@ -5958,7 +5958,7 @@
         <v>0.01415936862409189</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01402879363589935</v>
+        <v>0.01402879363589934</v>
       </c>
       <c r="H9" t="n">
         <v>0.01372344478818101</v>
@@ -5967,7 +5967,7 @@
         <v>0.01415936862409189</v>
       </c>
       <c r="J9" t="n">
-        <v>0.013810733439949</v>
+        <v>0.01381073343994899</v>
       </c>
       <c r="K9" t="n">
         <v>0.01437320002228129</v>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01692840543914713</v>
+        <v>0.01692840543914726</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01703099416577252</v>
+        <v>0.01703099416577251</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02770981305022329</v>
+        <v>0.0277098130502233</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01703099416577252</v>
+        <v>0.01703099416577251</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01703099416577252</v>
+        <v>0.01703099416577251</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03530061210928091</v>
+        <v>0.03530061210928086</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06149649393146359</v>
+        <v>0.06149649393146361</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01703099416577252</v>
+        <v>0.01703099416577251</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1132814022720285</v>
+        <v>0.1132814022720284</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02792724091914473</v>
+        <v>0.02792724091914478</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1059854792317579</v>
+        <v>0.105985479231758</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001974645400646814</v>
+        <v>0.001974645400646819</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001771887005257494</v>
+        <v>0.00177188700525749</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001974645400646814</v>
+        <v>0.001974645400646819</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00182492411684769</v>
+        <v>0.001824924116847684</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00182492411684769</v>
+        <v>0.001824924116847685</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001971911005841352</v>
+        <v>0.001971911005841353</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001974645400646814</v>
+        <v>0.001974645400646819</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001957329104235274</v>
+        <v>0.001957329104235275</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001974645400646814</v>
+        <v>0.001974645400646819</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001974645400646814</v>
+        <v>0.001974645400646819</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001974645400646814</v>
+        <v>0.001974645400646819</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003005885835302554</v>
+        <v>0.004877443730072614</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002921403947351694</v>
+        <v>0.002921403947351709</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004931427316455939</v>
+        <v>0.004931427316455935</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002792805383255402</v>
+        <v>0.002792805383255404</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002977076762954865</v>
+        <v>0.002977076762954861</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00300315144049709</v>
+        <v>0.004874709335267152</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005019216036659234</v>
+        <v>0.00301385159387108</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002988569538891018</v>
+        <v>0.004860127433661069</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004929047652955575</v>
+        <v>0.00492904765295557</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002987515662220248</v>
+        <v>0.002987515662220247</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003033442754111235</v>
+        <v>0.003033442754111236</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003709970776608641</v>
+        <v>0.003709970776608639</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003692654480197104</v>
+        <v>0.003692654480197097</v>
       </c>
       <c r="D5" t="n">
         <v>0.00370982920436234</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003689687045745506</v>
+        <v>0.0036896870457455</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003689687045745506</v>
+        <v>0.0036896870457455</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003707236381803172</v>
+        <v>0.003707236381803173</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003709970776608641</v>
+        <v>0.003709970776608639</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003692654480197104</v>
+        <v>0.003692654480197097</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003709970776608641</v>
+        <v>0.003709970776608639</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003709970776608641</v>
+        <v>0.003709970776608639</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003709970776608641</v>
+        <v>0.003709970776608639</v>
       </c>
     </row>
     <row r="6">
@@ -6219,34 +6219,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00572068871528828</v>
+        <v>0.005720688715288281</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008656807810164875</v>
+        <v>0.00865680781016488</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009289056159292899</v>
+        <v>0.009289056159292907</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00784868943250612</v>
+        <v>0.007848689432506124</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005795372107694888</v>
+        <v>0.005795372107694878</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008673475247268986</v>
+        <v>0.008673475247268985</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008676209642074563</v>
+        <v>0.008676209642074556</v>
       </c>
       <c r="I6" t="n">
         <v>0.008658893345662909</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008676790481614204</v>
+        <v>0.008676790481614193</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005665788397202515</v>
+        <v>0.005665788397202509</v>
       </c>
       <c r="L6" t="n">
         <v>0.01176349838196122</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00830849312196613</v>
+        <v>0.008308493121966139</v>
       </c>
       <c r="C7" t="n">
         <v>0.0102932473509484</v>
@@ -6286,7 +6286,7 @@
         <v>0.01031056364735995</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00915055650801652</v>
+        <v>0.009150556508016522</v>
       </c>
       <c r="L7" t="n">
         <v>0.01031056364735995</v>
@@ -6299,28 +6299,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01460894694521027</v>
+        <v>0.01460894694521026</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01459154643657614</v>
+        <v>0.01459154643657613</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01432238831311551</v>
+        <v>0.0143223883131155</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01459154643657614</v>
+        <v>0.01459154643657613</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01459154643657614</v>
+        <v>0.01459154643657613</v>
       </c>
       <c r="G8" t="n">
         <v>0.01416583220142603</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01362415368271174</v>
+        <v>0.01362415368271173</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01459154643657614</v>
+        <v>0.01459154643657613</v>
       </c>
       <c r="J8" t="n">
         <v>0.01254747649644939</v>
@@ -6329,7 +6329,7 @@
         <v>0.01432987000532755</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01411903714638003</v>
+        <v>0.0128366066500545</v>
       </c>
     </row>
     <row r="9">
@@ -6342,34 +6342,34 @@
         <v>0.01454647913766549</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01453026142463234</v>
+        <v>0.01453026142463235</v>
       </c>
       <c r="D9" t="n">
         <v>0.01442978248529703</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01453026142463234</v>
+        <v>0.01453026142463235</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01453026142463234</v>
+        <v>0.01453026142463235</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01436290231684391</v>
+        <v>0.01436290231684392</v>
       </c>
       <c r="H9" t="n">
         <v>0.01414662034522333</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01453026142463234</v>
+        <v>0.01453026142463235</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01370777477657557</v>
+        <v>0.01370777477657556</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01443284607940906</v>
+        <v>0.01443284607940905</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01382622262818833</v>
+        <v>0.01382622262818832</v>
       </c>
     </row>
   </sheetData>
@@ -6458,34 +6458,34 @@
         <v>0.01281549512995013</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01943911558305755</v>
+        <v>0.01943911558305756</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01655882266821837</v>
+        <v>0.01655882266821836</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01943911558305755</v>
+        <v>0.01943911558305756</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01943911558305755</v>
+        <v>0.01943911558305756</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02339379686725706</v>
+        <v>0.0233937968672574</v>
       </c>
       <c r="H2" t="n">
         <v>0.01247214275224734</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01943911558305755</v>
+        <v>0.01943911558305756</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06636150179752118</v>
+        <v>0.06636150179752122</v>
       </c>
       <c r="K2" t="n">
         <v>0.02485687648570948</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01473287029905925</v>
+        <v>0.01473287029905926</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001881170598699902</v>
+        <v>0.001881170598699895</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001746835441367609</v>
+        <v>0.001746835441367611</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001881170598699902</v>
+        <v>0.001881170598699895</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001792359925374819</v>
+        <v>0.001792359925374821</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00179235992537482</v>
+        <v>0.001792359925374822</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00187921490036599</v>
+        <v>0.001879214900365998</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001881170598699902</v>
+        <v>0.001881170598699895</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001868861144859142</v>
+        <v>0.001868861144859144</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001881170598699902</v>
+        <v>0.001881170598699895</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001881170598699902</v>
+        <v>0.001881170598699895</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001881170598699902</v>
+        <v>0.001881170598699895</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004560750890752798</v>
+        <v>0.004560750890752803</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002837869456194273</v>
+        <v>0.002837869456194276</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002878221014572502</v>
+        <v>0.002878232590194347</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002713769022016564</v>
+        <v>0.002713769022016568</v>
       </c>
       <c r="F4" t="n">
         <v>0.002868102567960106</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002883678225848561</v>
+        <v>0.004558795192418906</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002873990561297635</v>
+        <v>0.004655535530328882</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002873324470341703</v>
+        <v>0.004548441436912047</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004593023636947695</v>
+        <v>0.003002583936680151</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002893020759761691</v>
+        <v>0.00289302075976169</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002885096522996144</v>
+        <v>0.002885096522996145</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003403971790811919</v>
+        <v>0.003403971790811917</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003391662336971166</v>
+        <v>0.003391662336971167</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003403838851243142</v>
+        <v>0.00340383885124314</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003389379366769578</v>
+        <v>0.00338937936676958</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003389379366769578</v>
+        <v>0.00338937936676958</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003402016092478019</v>
+        <v>0.003402016092478018</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003403971790811919</v>
+        <v>0.003403971790811917</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003391662336971166</v>
+        <v>0.003391662336971167</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003403971790811919</v>
+        <v>0.003403971790811917</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003403971790811919</v>
+        <v>0.003403971790811917</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003403971790811919</v>
+        <v>0.003403971790811917</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005185108886954851</v>
+        <v>0.005185108886954845</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007784332759136553</v>
+        <v>0.007784332759136546</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00833998355960292</v>
+        <v>0.008339983559602929</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007069820696699557</v>
+        <v>0.007069820696699554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005254346271420654</v>
+        <v>0.005254346271420658</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007796196341479957</v>
+        <v>0.007796196341479953</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007798152039813488</v>
+        <v>0.007798152039813495</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007785842585973105</v>
+        <v>0.007785842585973097</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007798665573053053</v>
+        <v>0.007798665573053061</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005136570269311429</v>
+        <v>0.005136570269311432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0105276941076805</v>
+        <v>0.01052769410768051</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007107126121122034</v>
+        <v>0.007107126121122035</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008763695421386782</v>
+        <v>0.008763695421386785</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008776006071880326</v>
+        <v>0.008776006071880345</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01068954688415018</v>
+        <v>0.01068954688415019</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008763695169164787</v>
+        <v>0.00876369516916479</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008774049176893631</v>
+        <v>0.008774049176893645</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008776004875227518</v>
+        <v>0.008776004875227538</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008763695421386782</v>
+        <v>0.008763695421386785</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008776004875227518</v>
+        <v>0.008776004875227538</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007769819864168533</v>
+        <v>0.007809050474213671</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008776004875227518</v>
+        <v>0.008776004875227538</v>
       </c>
     </row>
     <row r="8">
@@ -6698,16 +6698,16 @@
         <v>0.01461823049588637</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01441378428614695</v>
+        <v>0.01441378428614696</v>
       </c>
       <c r="D8" t="n">
         <v>0.01449998077979052</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01441378428614695</v>
+        <v>0.01441378428614696</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01441378428614695</v>
+        <v>0.01441378428614696</v>
       </c>
       <c r="G8" t="n">
         <v>0.01433138531604506</v>
@@ -6716,7 +6716,7 @@
         <v>0.01464683613533156</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01441378428614695</v>
+        <v>0.01441378428614696</v>
       </c>
       <c r="J8" t="n">
         <v>0.01329676008672108</v>
@@ -6725,7 +6725,7 @@
         <v>0.01428356624008107</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01477425491084584</v>
+        <v>0.01459628269087219</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01450937548092534</v>
+        <v>0.01450937548092535</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01441442357171332</v>
+        <v>0.01441442357171333</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01446122339489753</v>
+        <v>0.01446122339489754</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01441442357171332</v>
+        <v>0.01441442357171333</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01441442357171332</v>
+        <v>0.01441442357171333</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01439096466332224</v>
+        <v>0.01439096466332225</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01452124978481549</v>
+        <v>0.01452124978481548</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01441442357171332</v>
+        <v>0.01441442357171333</v>
       </c>
       <c r="J9" t="n">
         <v>0.01397175562809879</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01437310077761888</v>
+        <v>0.01437310077761889</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01457300843327495</v>
+        <v>0.01450065312875553</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01807678237157516</v>
+        <v>0.01807678237157515</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02247941734236922</v>
+        <v>0.02247941734236921</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01315581408096561</v>
+        <v>0.0131558140809656</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02247941734236922</v>
+        <v>0.02247941734236921</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02247941734236922</v>
+        <v>0.02247941734236921</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02109362246523527</v>
+        <v>0.0210936224652352</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01285662718898651</v>
+        <v>0.01285662718898648</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02247941734236922</v>
+        <v>0.02247941734236921</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05548379729993795</v>
+        <v>0.05548379729993785</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02082842343180173</v>
+        <v>0.02082842343180167</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01228723025126886</v>
+        <v>0.01753587984786013</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001882531329955665</v>
+        <v>0.001882531329955662</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001770934422755468</v>
+        <v>0.001770934422755465</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001882531329955665</v>
+        <v>0.001882531329955662</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001815110067441868</v>
+        <v>0.001815110067441866</v>
       </c>
       <c r="F3" t="n">
         <v>0.001815110067441867</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001880699479128635</v>
+        <v>0.001880699479128632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001882531329955665</v>
+        <v>0.001882531329955662</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001870985370198757</v>
+        <v>0.001870985370198753</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001882531329955665</v>
+        <v>0.001882531329955662</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001882531329955665</v>
+        <v>0.001882531329955662</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001882531329955665</v>
+        <v>0.001882531329955662</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002905887348348736</v>
+        <v>0.002905887348348756</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002869904906933846</v>
+        <v>0.002869904906933804</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002880430178370254</v>
+        <v>0.002880430178370242</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002744131074977735</v>
+        <v>0.002744131074977734</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002890831879118648</v>
+        <v>0.002890831879118645</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004582888678674703</v>
+        <v>0.002904055497521728</v>
       </c>
       <c r="H4" t="n">
         <v>0.004664746167741368</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002894341388591865</v>
+        <v>0.002894341388591847</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004604693708229028</v>
+        <v>0.003020118932723448</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002912667775259439</v>
+        <v>0.002912667775259442</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002901417332679375</v>
+        <v>0.002901417332679372</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003380784782380353</v>
+        <v>0.003380784782380354</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003369238822623448</v>
+        <v>0.003369238822623442</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00338065127015631</v>
+        <v>0.003380651270156311</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00336710561570489</v>
+        <v>0.003367105615704886</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00336710561570489</v>
+        <v>0.003367105615704886</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003378952931553327</v>
+        <v>0.00337895293155332</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003380784782380353</v>
+        <v>0.003380784782380354</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003369238822623448</v>
+        <v>0.003369238822623442</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003380784782380353</v>
+        <v>0.003380784782380354</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003380784782380353</v>
+        <v>0.003380784782380354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003380784782380353</v>
+        <v>0.003380784782380354</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005136671762496392</v>
+        <v>0.005136671762496391</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007699728447512607</v>
+        <v>0.007699728447512611</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008246791699433121</v>
+        <v>0.008246791699433107</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006995338545598015</v>
+        <v>0.006995338545598018</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005205587313682864</v>
+        <v>0.005205587313682865</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007710814696420261</v>
+        <v>0.007710814696420259</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007712646547246797</v>
+        <v>0.007712646547246796</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00770110058749039</v>
+        <v>0.007701100587490382</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00771315279551706</v>
+        <v>0.00771315279551705</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005088821708819268</v>
+        <v>0.005088821708819267</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01040346760504365</v>
+        <v>0.01040346760504364</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006675630537640412</v>
+        <v>0.006675630537640402</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008210892578670219</v>
+        <v>0.008210892578670206</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008222439587796065</v>
+        <v>0.00822243958779606</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009995876868372777</v>
+        <v>0.009995876868372767</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008210892343322188</v>
+        <v>0.008210892343322174</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008220606687600093</v>
+        <v>0.008220606687600086</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00822243853842713</v>
+        <v>0.008222438538427114</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008210892578670219</v>
+        <v>0.008210892578670206</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00822243853842713</v>
+        <v>0.008222438538427114</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007289851278179657</v>
+        <v>0.007289851278179646</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00822243853842713</v>
+        <v>0.008222438538427114</v>
       </c>
     </row>
     <row r="8">
@@ -7118,10 +7118,10 @@
         <v>0.01340786654430863</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0141983501647251</v>
+        <v>0.01419835016472509</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01434909867166175</v>
+        <v>0.01448488094716845</v>
       </c>
     </row>
     <row r="9">
@@ -7146,7 +7146,7 @@
         <v>0.01408294540589233</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01424034087349883</v>
+        <v>0.01424034087349882</v>
       </c>
       <c r="H9" t="n">
         <v>0.01433950316233661</v>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0420374810105706</v>
+        <v>0.04203748101057057</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02762701162192966</v>
+        <v>0.02762701162192967</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0789960862508783</v>
+        <v>0.07899608625087821</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02762701162192966</v>
+        <v>0.02762701162192967</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02762701162192966</v>
+        <v>0.02762701162192967</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07580185862133856</v>
+        <v>0.07580185862133827</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1702843807430719</v>
+        <v>0.1702843807430717</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02762701162192966</v>
+        <v>0.02762701162192967</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1157355039183065</v>
+        <v>0.1157355039183064</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04148189954110506</v>
+        <v>0.04148189954110496</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2757102088812727</v>
+        <v>0.06423113576637009</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002113360091671464</v>
+        <v>0.002113360091671459</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001884492281738849</v>
+        <v>0.001884492281738846</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002113360091671464</v>
+        <v>0.002113360091671459</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001939968680863806</v>
+        <v>0.001939968680863803</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001939968680863806</v>
+        <v>0.001939968680863797</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002109548616160942</v>
+        <v>0.002109548616160937</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002113360091671464</v>
+        <v>0.002113360091671459</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002089181654001947</v>
+        <v>0.002089181654001942</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002113360091671464</v>
+        <v>0.002113360091671459</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002113360091671464</v>
+        <v>0.002113360091671459</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002113360091671464</v>
+        <v>0.002113360091671459</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003234933687007754</v>
+        <v>0.003234933687007746</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003105171554694678</v>
+        <v>0.003105171554694619</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003288159746947815</v>
+        <v>0.003288159746947841</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002972736756947761</v>
+        <v>0.00297273675694777</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003198794479828965</v>
+        <v>0.003198794479828963</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005377841998331108</v>
+        <v>0.005377841998331102</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005551387412938744</v>
+        <v>0.005551387412938718</v>
       </c>
       <c r="I4" t="n">
         <v>0.005357475036172107</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005439426550499925</v>
+        <v>0.005439426550499915</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003187018535465818</v>
+        <v>0.003187018535465832</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00331208552633</v>
+        <v>0.00331208552632999</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00404311241816115</v>
+        <v>0.004043112418161143</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00401893398049163</v>
+        <v>0.004018933980491625</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004042968365744568</v>
+        <v>0.004042968365744561</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004016019033991266</v>
+        <v>0.00401601903399125</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004016019033991266</v>
+        <v>0.00401601903399125</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004039300942650625</v>
+        <v>0.004039300942650616</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00404311241816115</v>
+        <v>0.004043112418161143</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00401893398049163</v>
+        <v>0.004018933980491625</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00404311241816115</v>
+        <v>0.004043112418161143</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00404311241816115</v>
+        <v>0.004043112418161143</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00404311241816115</v>
+        <v>0.004043112418161143</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00622450723606906</v>
+        <v>0.006224507236069045</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009425305273856795</v>
+        <v>0.009425305273834398</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01012059310870645</v>
+        <v>0.01012059310870639</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008542940286282817</v>
+        <v>0.008542940286282798</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006300965338649019</v>
+        <v>0.006300965338649</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009447651366937529</v>
+        <v>0.009447651366937508</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009451462842448279</v>
+        <v>0.009451462842448261</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009427284404778535</v>
+        <v>0.009427284404778493</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009452097026583589</v>
+        <v>0.009452097026583575</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006164564879464923</v>
+        <v>0.00616456487946491</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01282228780207687</v>
+        <v>0.01282228780207681</v>
       </c>
     </row>
     <row r="7">
@@ -7447,34 +7447,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009490603641436477</v>
+        <v>0.009490603641436453</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01177422410307765</v>
+        <v>0.01177422410307763</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0117984030897046</v>
+        <v>0.01179840308970457</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01443737224321574</v>
+        <v>0.01443737224321572</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01177422142094054</v>
+        <v>0.01177422142094051</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01179459106523664</v>
+        <v>0.0117945910652366</v>
       </c>
       <c r="H7" t="n">
         <v>0.01179840254074717</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01177422410307765</v>
+        <v>0.01177422410307763</v>
       </c>
       <c r="J7" t="n">
         <v>0.01179840254074717</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01046125502595028</v>
+        <v>0.01046125502595026</v>
       </c>
       <c r="L7" t="n">
         <v>0.01179840254074717</v>
@@ -7487,13 +7487,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01418422029666262</v>
+        <v>0.0141842202966626</v>
       </c>
       <c r="C8" t="n">
         <v>0.01448611223581118</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01327797073576358</v>
+        <v>0.01327797073576356</v>
       </c>
       <c r="E8" t="n">
         <v>0.01448611223581118</v>
@@ -7502,7 +7502,7 @@
         <v>0.01448611223581118</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01341339293362305</v>
+        <v>0.01341339293362306</v>
       </c>
       <c r="H8" t="n">
         <v>0.01139887716181871</v>
@@ -7511,13 +7511,13 @@
         <v>0.01448611223581118</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01266977983198152</v>
+        <v>0.01266977983198151</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01420578699998428</v>
+        <v>0.01420578699998429</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009744361121897803</v>
+        <v>0.009744361121897799</v>
       </c>
     </row>
     <row r="9">
@@ -7527,13 +7527,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01447394391123594</v>
+        <v>0.01447394391123593</v>
       </c>
       <c r="C9" t="n">
         <v>0.01457386404478041</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01410488337122712</v>
+        <v>0.0141048833712271</v>
       </c>
       <c r="E9" t="n">
         <v>0.01457386404478041</v>
@@ -7545,19 +7545,19 @@
         <v>0.0141541699292976</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01334296485252368</v>
+        <v>0.01334296485252367</v>
       </c>
       <c r="I9" t="n">
         <v>0.01457386404478041</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01385806049851169</v>
+        <v>0.01385806049851168</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01448277678502842</v>
+        <v>0.01448277678502841</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0126696968753318</v>
+        <v>0.01434143366752508</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.009188512898505698</v>
+        <v>0.009188512898505693</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02048889300219783</v>
+        <v>0.02048889300219785</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0635281814105696</v>
+        <v>0.06352818141056957</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02048889300219783</v>
+        <v>0.02048889300219785</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02048889300219783</v>
+        <v>0.02048889300219785</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04520113836556628</v>
+        <v>0.04520113836556618</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02487976493878937</v>
+        <v>0.02487976493878941</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02048889300219783</v>
+        <v>0.02048889300219785</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08581134961966193</v>
+        <v>0.085811349619662</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02005578084967429</v>
+        <v>0.02005578084967431</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01998563484285111</v>
+        <v>0.3267509925288084</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001955118401023398</v>
+        <v>0.001955118401023402</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001799868961973638</v>
+        <v>0.001799868961973639</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001955118401023398</v>
+        <v>0.001955118401023402</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001847171953687354</v>
+        <v>0.001847171953687356</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001847171953687354</v>
+        <v>0.001847171953687355</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001952339072408242</v>
+        <v>0.001952339072408244</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001955118401023398</v>
+        <v>0.001955118401023402</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001937564460421401</v>
+        <v>0.001937564460421403</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001955118401023398</v>
+        <v>0.001955118401023402</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001955118401023398</v>
+        <v>0.001955118401023402</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001955118401023398</v>
+        <v>0.001955118401023402</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004899217635033853</v>
+        <v>0.004899217635033856</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002918772733563263</v>
+        <v>0.002918772733563274</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003070383636639015</v>
+        <v>0.00307039512355556</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002792381277128568</v>
+        <v>0.002792381277128567</v>
       </c>
       <c r="F4" t="n">
         <v>0.002976026345865683</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002997412912726543</v>
+        <v>0.004896438306418703</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005001523342358993</v>
+        <v>0.00500152334235898</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004881663694431858</v>
+        <v>0.004881663694431862</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003127819650757217</v>
+        <v>0.00312781965075722</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00297081660033405</v>
+        <v>0.00297081660033404</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0030992480242329</v>
+        <v>0.003099248024232899</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003598635495627312</v>
+        <v>0.00359863549562731</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003581081555025321</v>
+        <v>0.003581081555025317</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003598501685420909</v>
+        <v>0.003598501685420911</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003578521510397827</v>
+        <v>0.00357852151039782</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003578521510397827</v>
+        <v>0.00357852151039782</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003595856167012162</v>
+        <v>0.003595856167012154</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003598635495627312</v>
+        <v>0.00359863549562731</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003581081555025321</v>
+        <v>0.003581081555025317</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003598635495627312</v>
+        <v>0.00359863549562731</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003598635495627312</v>
+        <v>0.00359863549562731</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003598635495627312</v>
+        <v>0.00359863549562731</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005504846951502574</v>
+        <v>0.005504846951502575</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008280509196174159</v>
+        <v>0.008280509196174148</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008879353091078341</v>
+        <v>0.008879353091078356</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007516270184794163</v>
+        <v>0.007516270184794154</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005574441379037767</v>
+        <v>0.005574441379037768</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008297021805598048</v>
+        <v>0.008297021805598034</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008299801134213053</v>
+        <v>0.008299801134213044</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008282247193611201</v>
+        <v>0.008282247193611196</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008300350418116239</v>
+        <v>0.008300350418116229</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005452929243093185</v>
+        <v>0.005452929243093175</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0112193644838555</v>
+        <v>0.01121936448385548</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00770523252567296</v>
+        <v>0.007705232525672965</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00951271867721022</v>
+        <v>0.009512718677210227</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009530274076900935</v>
+        <v>0.009530274076900939</v>
       </c>
       <c r="E7" t="n">
         <v>0.01161877662440077</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00951271792439211</v>
+        <v>0.009512717924392114</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00952749328919706</v>
+        <v>0.009527493289197055</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009530272617812221</v>
+        <v>0.009530272617812226</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00951271867721022</v>
+        <v>0.009512718677210227</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009530272617812221</v>
+        <v>0.009530272617812226</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007232220995140318</v>
+        <v>0.008472837834628212</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009530272617812221</v>
+        <v>0.009530272617812226</v>
       </c>
     </row>
     <row r="8">
@@ -7883,13 +7883,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01482028077669661</v>
+        <v>0.0148202807766966</v>
       </c>
       <c r="C8" t="n">
         <v>0.01448934213897887</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01333779239966728</v>
+        <v>0.01333779239966726</v>
       </c>
       <c r="E8" t="n">
         <v>0.01448934213897887</v>
@@ -7898,22 +7898,22 @@
         <v>0.01448934213897887</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01388684118347726</v>
+        <v>0.01388684118347725</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01446099009315957</v>
+        <v>0.01446099009315956</v>
       </c>
       <c r="I8" t="n">
         <v>0.01448934213897887</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01304812269222056</v>
+        <v>0.01304812269222055</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01452576448350048</v>
+        <v>0.01452576448350046</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007958575260530776</v>
+        <v>0.007958575260530761</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01465423650909406</v>
+        <v>0.01465423650909405</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01450093171719498</v>
+        <v>0.01450093171719497</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01405047237462659</v>
+        <v>0.01405047237462658</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01450093171719498</v>
+        <v>0.01450093171719497</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01450093171719498</v>
+        <v>0.01450093171719497</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0142702734967942</v>
+        <v>0.01427027349679419</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01450839609382841</v>
+        <v>0.0145083960938284</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01450093171719498</v>
+        <v>0.01450093171719497</v>
       </c>
       <c r="J9" t="n">
-        <v>0.013933190259332</v>
+        <v>0.01393319025933201</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01453430668254622</v>
+        <v>0.01453430668254621</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01186483686189393</v>
+        <v>0.01186483686189392</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen photochemical ozone formation results.xlsx
+++ b/Results/Hydrogen/hydrogen photochemical ozone formation results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,321 +511,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08525123755515052</v>
+        <v>0.01523705135944116</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05191630204564383</v>
+        <v>0.01523941131018243</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1694755403253596</v>
+        <v>0.01532089259771787</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05191630204564383</v>
+        <v>0.01523941131018243</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05191630204564383</v>
+        <v>0.01523941131018243</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1214463725586993</v>
+        <v>0.01525678294736159</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2389036818016614</v>
+        <v>0.01536839308023015</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05191630204564383</v>
+        <v>0.01523941131018243</v>
       </c>
       <c r="J2" t="n">
-        <v>0.152083184367431</v>
+        <v>0.01529595502551477</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0595821658301695</v>
+        <v>0.01520839991594569</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3681314073785206</v>
+        <v>0.01523910397747376</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002447472661805912</v>
+        <v>0.01542265394797631</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002295295294137584</v>
+        <v>0.01546194588496578</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002447472661805912</v>
+        <v>0.01542265394797631</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002356448963090834</v>
+        <v>0.01546194588496578</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002356448963090834</v>
+        <v>0.01546194588496578</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002444069538033254</v>
+        <v>0.0154100710548918</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002447472661805912</v>
+        <v>0.01542265394797631</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0024262503184697</v>
+        <v>0.01546194588496578</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002447472661805912</v>
+        <v>0.01542265394797631</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002447472661805912</v>
+        <v>0.01542265394797631</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002447472661805912</v>
+        <v>0.01542265394797631</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003803844908782865</v>
+        <v>0.08525123755515061</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003668397372595475</v>
+        <v>0.05191630204564394</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003959518277380236</v>
+        <v>0.1694755403253596</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003513999018221127</v>
+        <v>0.05191630204564394</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003779583833363694</v>
+        <v>0.05191630204564394</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006425933612238215</v>
+        <v>0.1214463725586992</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006608690727069804</v>
+        <v>0.2389036818016614</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006408114392674662</v>
+        <v>0.05191630204564394</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006456333933543074</v>
+        <v>0.152083184367431</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003738987196650057</v>
+        <v>0.05958216583016954</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003903423395847118</v>
+        <v>0.3681314073785215</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004825237718683754</v>
+        <v>0.00244747266180591</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004804015375347544</v>
+        <v>0.002295295294137586</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004825076009250692</v>
+        <v>0.00244747266180591</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004801504756458279</v>
+        <v>0.002356448963090833</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004801504756458279</v>
+        <v>0.002356448963090832</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004821834594911097</v>
+        <v>0.002444069538033254</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004825237718683754</v>
+        <v>0.00244747266180591</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004804015375347544</v>
+        <v>0.002426250318469699</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004825237718683754</v>
+        <v>0.00244747266180591</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004825237718683754</v>
+        <v>0.00244747266180591</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004825237718683754</v>
+        <v>0.00244747266180591</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007433306720444855</v>
+        <v>0.00380384490878287</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01130232911457029</v>
+        <v>0.003668397372595505</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0121319565909529</v>
+        <v>0.00395951827738024</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01023810457216024</v>
+        <v>0.00351399901822112</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00753404351142205</v>
+        <v>0.0037795838333637</v>
       </c>
       <c r="G6" t="n">
-        <v>0.011321587465443</v>
+        <v>0.006425933612238214</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01132499058921573</v>
+        <v>0.006608690727069808</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01130376824587943</v>
+        <v>0.006408114392674657</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01132575541110202</v>
+        <v>0.006456333933543079</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007361016695134253</v>
+        <v>0.003738987196650079</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01539017980220269</v>
+        <v>0.003903423395847117</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01299911338313663</v>
+        <v>0.004825237718683756</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01621101124998869</v>
+        <v>0.004804015375347541</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01623223471884062</v>
+        <v>0.00482507600925069</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01994196022014041</v>
+        <v>0.00480150475645828</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01621100787668795</v>
+        <v>0.00480150475645828</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01622883046955223</v>
+        <v>0.004821834594911097</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0162322335933249</v>
+        <v>0.004825237718683756</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01621101124998869</v>
+        <v>0.004804015375347541</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0162322335933249</v>
+        <v>0.004825237718683756</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01216115784707213</v>
+        <v>0.004825237718683756</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0162322335933249</v>
+        <v>0.004825237718683756</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01360352976596094</v>
+        <v>0.007433306720444855</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01439248842073947</v>
+        <v>0.01130232911457029</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01184819297339642</v>
+        <v>0.01213195659095291</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01439248842073947</v>
+        <v>0.01023810457216024</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01439248842073947</v>
+        <v>0.007534043511422046</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01292592901904737</v>
+        <v>0.011321587465443</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01093814382495994</v>
+        <v>0.01132499058921574</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01439248842073947</v>
+        <v>0.01130376824587944</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01239314532046431</v>
+        <v>0.01132575541110202</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01420542153658418</v>
+        <v>0.007361016695134249</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01358922871371968</v>
+        <v>0.0153901798022027</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01299911338313663</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0162110112499887</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01623223471884063</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0199419602201404</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01621100787668795</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01622883046955224</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01623223359332491</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0162110112499887</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01623223359332491</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01216115784707214</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01623223359332491</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01360352976596095</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01439248842073948</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01184819297339644</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01439248842073948</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01439248842073948</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01292592901904737</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01093814382495996</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01439248842073948</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01239314532046432</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01420542153658419</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0135892287137197</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>0.01440934405941936</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C11" t="n">
         <v>0.01475280475580074</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.01369450146315277</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.01369450146315278</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.01475280475580074</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01475280475580074</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.0141264904045614</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01332792668297189</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.01412649040456142</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0133279266829719</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.01475280475580074</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.01391751894552566</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01465455528967271</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01242129964235726</v>
+      <c r="J11" t="n">
+        <v>0.01391751894552567</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01465455528967272</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01242129964235727</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007908069937214634</v>
+        <v>0.01448012709777122</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02183012290606764</v>
+        <v>0.01436222108644773</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0162544088103148</v>
+        <v>0.01449068226973648</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02183012290606764</v>
+        <v>0.01436222108644773</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02183012290606764</v>
+        <v>0.01436222108644773</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02461823126793045</v>
+        <v>0.01449787366561056</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01625376362460506</v>
+        <v>0.01448867241224577</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02183012290606764</v>
+        <v>0.01436222108644773</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06394229831931382</v>
+        <v>0.01454295567210322</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01930124217881785</v>
+        <v>0.01449531187345701</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01356804827290345</v>
+        <v>0.01448788898381486</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001901277892631335</v>
+        <v>0.01473773298708415</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001785357883627884</v>
+        <v>0.01460034613209118</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001901277892631335</v>
+        <v>0.01473773298708415</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001830024318261655</v>
+        <v>0.01460034613209118</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001830024318261654</v>
+        <v>0.01460034613209118</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001899313657202708</v>
+        <v>0.01473522018797759</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001901277892631335</v>
+        <v>0.01473773298708415</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001888896264506864</v>
+        <v>0.01460034613209118</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001901277892631335</v>
+        <v>0.01473773298708415</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001901277892631335</v>
+        <v>0.01473773298708415</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001901277892631335</v>
+        <v>0.01473773298708415</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002922953406917474</v>
+        <v>0.007908069937214612</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002886061585157244</v>
+        <v>0.02183012290606766</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004642483195929381</v>
+        <v>0.0162544088103148</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002759529601853756</v>
+        <v>0.02183012290606766</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002911460271440275</v>
+        <v>0.02183012290606766</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004602073206754755</v>
+        <v>0.02461823126793053</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004714557885389624</v>
+        <v>0.01625376362460505</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002910571778793002</v>
+        <v>0.02183012290606766</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003045498745636588</v>
+        <v>0.06394229831931364</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002928626416012578</v>
+        <v>0.01930124217881785</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002924052132511711</v>
+        <v>0.01356804827290346</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003448262357610084</v>
+        <v>0.001901277892631335</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003435880729485601</v>
+        <v>0.001785357883627884</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003448128376123637</v>
+        <v>0.001901277892631335</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003433621171084116</v>
+        <v>0.001830024318261653</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003433621171084116</v>
+        <v>0.001830024318261653</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003446298122181452</v>
+        <v>0.00189931365720271</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003448262357610084</v>
+        <v>0.001901277892631335</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003435880729485601</v>
+        <v>0.001888896264506862</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003448262357610084</v>
+        <v>0.001901277892631335</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003448262357610084</v>
+        <v>0.001901277892631335</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003448262357610084</v>
+        <v>0.001901277892631335</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005250001058071072</v>
+        <v>0.002922953406917467</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007882072845153463</v>
+        <v>0.002886061585157218</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008444584332906071</v>
+        <v>0.004642483195929385</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007158561448354317</v>
+        <v>0.002759529601853774</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005320223382761067</v>
+        <v>0.002911460271440272</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007893968854398312</v>
+        <v>0.004602073206754733</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007895933089826997</v>
+        <v>0.004714557885389611</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007883551461702457</v>
+        <v>0.002910571778793002</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007896453086672715</v>
+        <v>0.003045498745636575</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005200851512617844</v>
+        <v>0.002928626416012575</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01065983034182301</v>
+        <v>0.0029240521325117</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006788592891581334</v>
+        <v>0.003448262357610073</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008353366823332589</v>
+        <v>0.003435880729485604</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008365749602778231</v>
+        <v>0.003448128376123626</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01017337156806548</v>
+        <v>0.003433621171084117</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008353366526505429</v>
+        <v>0.003433621171084117</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008363784216028444</v>
+        <v>0.003446298122181454</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008365748451457078</v>
+        <v>0.003448262357610073</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008353366823332589</v>
+        <v>0.003435880729485604</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008365748451457078</v>
+        <v>0.003448262357610073</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007451938810338403</v>
+        <v>0.003448262357610073</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008365748451457078</v>
+        <v>0.003448262357610073</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01459579870677107</v>
+        <v>0.005250001058071083</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0140928348814209</v>
+        <v>0.007882072845153465</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0143747637327149</v>
+        <v>0.008444584332906051</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0140928348814209</v>
+        <v>0.007158561448354318</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0140928348814209</v>
+        <v>0.005320223382761064</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01417143938663253</v>
+        <v>0.007893968854398291</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01442287270658019</v>
+        <v>0.007895933089826989</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0140928348814209</v>
+        <v>0.007883551461702455</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01329049151180536</v>
+        <v>0.007896453086672719</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01427803548980265</v>
+        <v>0.00520085151261783</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0144969405698967</v>
+        <v>0.01065983034182301</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.006788592891581327</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.008353366823332589</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.008365749602778231</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01017337156806547</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.008353366526505444</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.008363784216028439</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.008365748451457069</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.008353366823332589</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.008365748451457069</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.007451938810338394</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.008365748451457069</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01459579870677108</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0140928348814209</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01437476373271489</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0140928348814209</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0140928348814209</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01417143938663255</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01442287270658021</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0140928348814209</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01329049151180535</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01427803548980265</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01449694056989673</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01441554654791104</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01413130185005036</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.01432553010228407</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01413130185005036</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01413130185005036</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01424135160433576</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01434540998121628</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01413130185005036</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B11" t="n">
+        <v>0.01441554654791105</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01413130185005037</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01432553010228408</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01413130185005037</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01413130185005037</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01424135160433577</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01434540998121629</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01413130185005037</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.01388445618876643</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>0.01428614804722493</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.01437546619568197</v>
+      <c r="L11" t="n">
+        <v>0.01437546619568199</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,320 +1463,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02017937845475282</v>
+        <v>0.01320759869896247</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03667394993898705</v>
+        <v>0.004488294025847794</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05533204121894651</v>
+        <v>0.03188343203056998</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02869525037621012</v>
+        <v>0.01301682024085421</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02869525037621012</v>
+        <v>0.01301682024085421</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05067688236220611</v>
+        <v>0.0136756621079689</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1011655714639694</v>
+        <v>0.03192285013233773</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02869525037621012</v>
+        <v>0.01301682024085421</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0970342275753875</v>
+        <v>0.0194715562644803</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03056654682833797</v>
+        <v>0.01738912157088175</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08279759165610612</v>
+        <v>0.02181567580881841</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002012644970363204</v>
+        <v>0.01343169595657922</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001785576736107037</v>
+        <v>0.004555427614831616</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002012644970363203</v>
+        <v>0.03236438080497817</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001909039259144132</v>
+        <v>0.01322813458473288</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001909039259144132</v>
+        <v>0.01322813458473288</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002008401807504675</v>
+        <v>0.0138737458631916</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002012644970363205</v>
+        <v>0.03236438080497817</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001985351979532612</v>
+        <v>0.01322813458473288</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002012644970363205</v>
+        <v>0.01971300823353165</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002012644970363203</v>
+        <v>0.01766744075717406</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002012644970363203</v>
+        <v>0.0221168154784101</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005010039419114084</v>
+        <v>0.02017937845475283</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002979706148378688</v>
+        <v>0.03667394993898724</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003069370145652039</v>
+        <v>0.05533204121894655</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002826356149524529</v>
+        <v>0.02869525037621011</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003008070306203199</v>
+        <v>0.02869525037621011</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003034285128174173</v>
+        <v>0.0506768823622063</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005199754867077168</v>
+        <v>0.1011655714639696</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003011235300202118</v>
+        <v>0.02869525037621011</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005053444591619032</v>
+        <v>0.09703422757538745</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002999972742191874</v>
+        <v>0.03056654682833799</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003051520541824138</v>
+        <v>0.08279759165610615</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003918566515788884</v>
+        <v>0.002012644970363204</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003915757157897682</v>
+        <v>0.001785576736107044</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003918432204494801</v>
+        <v>0.002012644970363205</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003887658126519123</v>
+        <v>0.00190903925914413</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003887658126519123</v>
+        <v>0.001909039259144131</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003914323352930348</v>
+        <v>0.002008401807504667</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003918566515788884</v>
+        <v>0.002012644970363205</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003891273524958292</v>
+        <v>0.00198535197953261</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003918566515788884</v>
+        <v>0.002012644970363204</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003918566515788884</v>
+        <v>0.002012644970363205</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003918566515788884</v>
+        <v>0.002012644970363205</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006078540350645998</v>
+        <v>0.005010039419114092</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009268555230104981</v>
+        <v>0.002979706148378672</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009936634555679547</v>
+        <v>0.003069370145652042</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008370385330207567</v>
+        <v>0.002826356149524469</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00615046278579067</v>
+        <v>0.003008070306203204</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009269785976225613</v>
+        <v>0.003034285128174178</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009274029139088539</v>
+        <v>0.005199754867077177</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009246736148253559</v>
+        <v>0.003011235300202123</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009274657139239237</v>
+        <v>0.005053444591619027</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006019182506322551</v>
+        <v>0.002999972742191867</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01261198437632391</v>
+        <v>0.003051520541824143</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008585366257043731</v>
+        <v>0.003918566515788889</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01066667923497316</v>
+        <v>0.003915757157897682</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0106694895497898</v>
+        <v>0.003918432204494803</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01304722769512771</v>
+        <v>0.003887658126519125</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01064219419647244</v>
+        <v>0.003887658126519125</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01066524543000582</v>
+        <v>0.003914323352930348</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01066948859286437</v>
+        <v>0.003918566515788889</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01064219560203376</v>
+        <v>0.003891273524958292</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01066948859286437</v>
+        <v>0.003918566515788889</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009461940328988996</v>
+        <v>0.003918566515788889</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01066948859286437</v>
+        <v>0.003918566515788889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01303044872696621</v>
+        <v>0.006078540350645995</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003781841388241001</v>
+        <v>0.009268555230104992</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03113757327166265</v>
+        <v>0.00993663455567954</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01262266919288654</v>
+        <v>0.008370385330207558</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01262266919288654</v>
+        <v>0.00615046278579066</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01278784280584176</v>
+        <v>0.009269785976225615</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03035010030436469</v>
+        <v>0.009274029139088525</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01262266919288653</v>
+        <v>0.009246736148253562</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01763412868052223</v>
+        <v>0.009274657139239228</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01701578953077498</v>
+        <v>0.006019182506322553</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02050973764433904</v>
+        <v>0.01261198437632389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.008585366257043744</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01066667923497316</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01066948954978979</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01304722769512772</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01064219419647246</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01066524543000582</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01066948859286437</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01064219560203378</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01066948859286437</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.009461940328988998</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01066948859286437</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01303044872696623</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.003781841388241001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.03113757327166265</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01262266919288654</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01262266919288654</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01278784280584175</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.03035010030436469</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01262266919288654</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01763412868052225</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01701578953077498</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.02050973764433905</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>0.01302502993078952</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C11" t="n">
         <v>0.004136309827476035</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>0.03132523069330777</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.0127413315580604</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0127413315580604</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="E11" t="n">
+        <v>0.01274133155806041</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01274133155806041</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.013181572756307</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.03100634608542752</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0127413315580604</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01852565944286497</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01709261818618094</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="H11" t="n">
+        <v>0.03100634608542753</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01274133155806041</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01852565944286498</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01709261818618092</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.02108445027286289</v>
       </c>
     </row>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,320 +1939,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01150106357520047</v>
+        <v>0.01313523126848111</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02501378776389328</v>
+        <v>0.00438014786735842</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03803109370171219</v>
+        <v>0.03175389045928181</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01784971344082622</v>
+        <v>0.01291246274074505</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01784971344082622</v>
+        <v>0.01291246274074505</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03210595431697846</v>
+        <v>0.01357510838659575</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05244000961871281</v>
+        <v>0.03176464987675659</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01784971344082622</v>
+        <v>0.01291246274074505</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0653297988878393</v>
+        <v>0.01939231023864446</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01664020731105277</v>
+        <v>0.01727702387002054</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0333005288954923</v>
+        <v>0.02110802942668235</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001880076817890256</v>
+        <v>0.01336704185381996</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001709940213403883</v>
+        <v>0.004456882723541618</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001880076817890256</v>
+        <v>0.03224987834143766</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001906983319205214</v>
+        <v>0.01313307726356994</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001906983319205214</v>
+        <v>0.01313307726356994</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00187640632854157</v>
+        <v>0.01378999071169392</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001880076817890256</v>
+        <v>0.03224987834143766</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001856492705292008</v>
+        <v>0.01313307726356994</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001880076817890256</v>
+        <v>0.01966267885126315</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001880076817890256</v>
+        <v>0.01756816223781779</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001880076817890256</v>
+        <v>0.02144490114514719</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00464316556989903</v>
+        <v>0.01150106357520048</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00281964813240133</v>
+        <v>0.02501378776389328</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004670205257941778</v>
+        <v>0.03803109370171228</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002690183747137601</v>
+        <v>0.0178497134408262</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002846242241834363</v>
+        <v>0.0178497134408262</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004639495080550343</v>
+        <v>0.03210595431697828</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004801418038413157</v>
+        <v>0.05244000961871274</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002839214577798615</v>
+        <v>0.0178497134408262</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002983442229743631</v>
+        <v>0.06532979888783919</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002842155469164772</v>
+        <v>0.01664020731105279</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002859553858728001</v>
+        <v>0.03330052889549235</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003579249873729451</v>
+        <v>0.001880076817890243</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00357685141884406</v>
+        <v>0.001709940213403883</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003579122236192855</v>
+        <v>0.001880076817890243</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003553149367682021</v>
+        <v>0.001906983319205211</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003553149367682021</v>
+        <v>0.001906983319205209</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00357557938438076</v>
+        <v>0.001876406328541566</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003579249873729451</v>
+        <v>0.001880076817890243</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003555665761131204</v>
+        <v>0.001856492705292008</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003579249873729451</v>
+        <v>0.001880076817890243</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003579249873729451</v>
+        <v>0.001880076817890243</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003579249873729451</v>
+        <v>0.001880076817890243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005560112600593381</v>
+        <v>0.004643165569899033</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008449911095183759</v>
+        <v>0.002819648132401402</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009054056466183534</v>
+        <v>0.004670205257941773</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0076374249931529</v>
+        <v>0.002690183747137605</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005626834983157088</v>
+        <v>0.002846242241834366</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008450321279724405</v>
+        <v>0.00463949508055034</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008453991769080576</v>
+        <v>0.004801418038413144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008430407656474839</v>
+        <v>0.002839214577798617</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008454560494587926</v>
+        <v>0.002983442229743636</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005506357309777961</v>
+        <v>0.002842155469164775</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01147689053836783</v>
+        <v>0.002859553858728005</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007225837037737244</v>
+        <v>0.003579249873729447</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008943673303064883</v>
+        <v>0.003576851418844064</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008946072789159057</v>
+        <v>0.003579122236192854</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01090760198602966</v>
+        <v>0.003553149367682024</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008922486858335105</v>
+        <v>0.003553149367682024</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008942401268601581</v>
+        <v>0.003575579384380755</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008946071757950279</v>
+        <v>0.003579249873729447</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00892248764535203</v>
+        <v>0.003555665761131201</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008946071757950279</v>
+        <v>0.003579249873729447</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007949361438898168</v>
+        <v>0.003579249873729447</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008946071757950279</v>
+        <v>0.003579249873729447</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01314572082114872</v>
+        <v>0.005560112600593373</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00391378741719232</v>
+        <v>0.008449911095183716</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03137360797477601</v>
+        <v>0.009054056466183525</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01275270811944802</v>
+        <v>0.007637424993152905</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01275270811944802</v>
+        <v>0.005626834983157077</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01308022395466228</v>
+        <v>0.008450321279724386</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03116878930581578</v>
+        <v>0.008453991769080578</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01275270811944802</v>
+        <v>0.008430407656474841</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01819918272365592</v>
+        <v>0.008454560494587935</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01721536624281848</v>
+        <v>0.005506357309777956</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02078927510190936</v>
+        <v>0.0114768905383678</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.007225837037737234</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.00894367330306488</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.008946072789159034</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01090760198602965</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.008922486858335098</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.008942401268601564</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.008946071757950258</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.008922487645352029</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.008946071757950258</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.007949361438898154</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.008946071757950258</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01314572082114871</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.00391378741719232</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.031373607974776</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01275270811944802</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01275270811944802</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01308022395466229</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.03116878930581577</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01275270811944802</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01819918272365592</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01721536624281847</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.02078927510190937</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>0.01303452949330741</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.004133037772227436</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.03135518464994279</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="C11" t="n">
+        <v>0.004133037772227437</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.03135518464994278</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.01273939356800504</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01273939356800504</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G11" t="n">
         <v>0.01325216225025391</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>0.03127275092032231</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>0.01273939356800504</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>0.01872641483669773</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.01711650056800174</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="K11" t="n">
+        <v>0.01711650056800173</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.02080971748765291</v>
       </c>
     </row>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,321 +2415,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006317282618925006</v>
+        <v>0.01307736941604598</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01850849819421502</v>
+        <v>0.004280596249570992</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02501493141887246</v>
+        <v>0.03163583049677877</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0082557691110064</v>
+        <v>0.01260901940751404</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0082557691110064</v>
+        <v>0.01260901940751404</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02028341995975402</v>
+        <v>0.01338673423763699</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02814118649697357</v>
+        <v>0.03163631107271082</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0082557691110064</v>
+        <v>0.01260901940751404</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03756974007875735</v>
+        <v>0.0185460452346462</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009371036070201419</v>
+        <v>0.01720910442190183</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01510323359316559</v>
+        <v>0.02096986125820065</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001804573889659523</v>
+        <v>0.01331469303316452</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001660257834835546</v>
+        <v>0.004363726142412854</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001804573889659523</v>
+        <v>0.03214580185220181</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001809346691486439</v>
+        <v>0.01283650855179644</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00180934669148644</v>
+        <v>0.01283650855179644</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001801528345550222</v>
+        <v>0.01361271500160832</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001804573889659523</v>
+        <v>0.03214580185220181</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001785120299744238</v>
+        <v>0.01283650855179644</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001804573889659523</v>
+        <v>0.01883484614557888</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001804573889659523</v>
+        <v>0.01750819321064021</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001804573889659523</v>
+        <v>0.02132391714507609</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002761257913489909</v>
+        <v>0.006317282618925013</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002730517235123062</v>
+        <v>0.01850849819421504</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002770636818871302</v>
+        <v>0.02501493141887246</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002590899613561091</v>
+        <v>0.008255769111006398</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002745564868942003</v>
+        <v>0.008255769111006398</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004471252569905062</v>
+        <v>0.02028341995975393</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004615790281404472</v>
+        <v>0.02814118649697364</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004454844524099077</v>
+        <v>0.008255769111006398</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004497648341420707</v>
+        <v>0.03756974007875736</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002752819996364624</v>
+        <v>0.009371036070201434</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002752360384827829</v>
+        <v>0.0151032335931656</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003424328745116835</v>
+        <v>0.001804573889659523</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003422281266917219</v>
+        <v>0.001660257834835548</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003424201081514565</v>
+        <v>0.001804573889659523</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003402070175125486</v>
+        <v>0.001809346691486442</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003402070175125486</v>
+        <v>0.001809346691486443</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003421283201007534</v>
+        <v>0.001801528345550221</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003424328745116835</v>
+        <v>0.001804573889659523</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003404875155201552</v>
+        <v>0.001785120299744239</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003424328745116835</v>
+        <v>0.001804573889659523</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003424328745116835</v>
+        <v>0.001804573889659523</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003424328745116835</v>
+        <v>0.001804573889659523</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005351058077064663</v>
+        <v>0.002761257913489918</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008137412681727657</v>
+        <v>0.002730517235123067</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008720040708066238</v>
+        <v>0.002770636818871142</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007357042547622485</v>
+        <v>0.002590899613561098</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005418458056015291</v>
+        <v>0.002745564868942012</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008138391837805126</v>
+        <v>0.004471252569905062</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008141437381921697</v>
+        <v>0.00461579028140448</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008121983791999134</v>
+        <v>0.004454844524099083</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008141985766825736</v>
+        <v>0.004497648341420713</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005299225349344405</v>
+        <v>0.002752819996364651</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01105622188921167</v>
+        <v>0.002752360384827836</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006461936229051311</v>
+        <v>0.003424328745116839</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007981629278335074</v>
+        <v>0.003422281266917223</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007983677739699924</v>
+        <v>0.003424201081514569</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009720279654942418</v>
+        <v>0.003402070175125493</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007964222604185684</v>
+        <v>0.003402070175125493</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007980631212425383</v>
+        <v>0.003421283201007539</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007983676756534698</v>
+        <v>0.003424328745116839</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007964223166619407</v>
+        <v>0.003404875155201556</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007983676756534698</v>
+        <v>0.003424328745116839</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007066202927313678</v>
+        <v>0.003424328745116839</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007983676756534698</v>
+        <v>0.003424328745116839</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01321442097115583</v>
+        <v>0.005351058077064676</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003973469957205044</v>
+        <v>0.008137412681727657</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03158550570000034</v>
+        <v>0.008720040708066226</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01268634282182651</v>
+        <v>0.007357042547622488</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01268634282182651</v>
+        <v>0.005418458056015289</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01318137390588794</v>
+        <v>0.008138391837805119</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03158611522285858</v>
+        <v>0.008141437381921685</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01268634282182651</v>
+        <v>0.008121983791999136</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01801283402822753</v>
+        <v>0.008141985766825732</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01733040891645332</v>
+        <v>0.005299225349344409</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02105067518007835</v>
+        <v>0.01105622188921167</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.006461936229051307</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.007981629278335081</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.007983677739699933</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.009720279654942425</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.007964222604185694</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.007980631212425395</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0079836767565347</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.007964223166619412</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0079836767565347</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.007066202927313687</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0079836767565347</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01321442097115584</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.003973469957205042</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.03158550570000034</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01268634282182651</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01268634282182651</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01318137390588794</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.03158611522285858</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01268634282182651</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01801283402822755</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01733040891645334</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.02105067518007835</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01303174530828394</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.004103028441628763</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.01303174530828395</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.004103028441628764</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.03138089396196921</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.01254069352182793</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01254069352182793</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="E11" t="n">
+        <v>0.01254069352182794</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01254069352182794</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.01319047266448172</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.0313816518727442</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01254069352182793</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="H11" t="n">
+        <v>0.03138165187274421</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01254069352182794</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.01817202710165416</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.01712821200148185</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.02084553529335622</v>
+      <c r="K11" t="n">
+        <v>0.01712821200148187</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.02084553529335621</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,320 +2891,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008388538039507034</v>
+        <v>0.01288381121695</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006137795201643188</v>
+        <v>0.004312902102455623</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03134147627226708</v>
+        <v>0.03171080839276474</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01528411396059477</v>
+        <v>0.01288176173190535</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01528411396059477</v>
+        <v>0.01288176173190535</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03339442840766522</v>
+        <v>0.01352996171801512</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07933456951320426</v>
+        <v>0.03175503857247371</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01528411396059477</v>
+        <v>0.01288176173190535</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08962499778150905</v>
+        <v>0.01935231787238074</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02172253553758008</v>
+        <v>0.01725075527694056</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07232629067457066</v>
+        <v>0.02171221522628383</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001886809246219496</v>
+        <v>0.01311604747387853</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001648299554604904</v>
+        <v>0.00441108956527958</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001886809246219496</v>
+        <v>0.03221631383291319</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001790817847928813</v>
+        <v>0.01310621523806364</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001790817847928813</v>
+        <v>0.01310621523806364</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001882715376070062</v>
+        <v>0.0137450201179131</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001886809246219496</v>
+        <v>0.03221631383291319</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001860457238970535</v>
+        <v>0.01310621523806364</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001886809246219496</v>
+        <v>0.01960023926353954</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001886809246219496</v>
+        <v>0.0175371662059901</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001886809246219496</v>
+        <v>0.02202244718369803</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002841669375381187</v>
+        <v>0.008388538039507043</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002753579018363774</v>
+        <v>0.006137795201643207</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002854394960189425</v>
+        <v>0.03134147627226709</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002639821923523751</v>
+        <v>0.01528411396059491</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002812360300715144</v>
+        <v>0.01528411396059491</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002837575505231755</v>
+        <v>0.03339442840766513</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004882068985960431</v>
+        <v>0.07933456951320439</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00467586936110018</v>
+        <v>0.01528411396059491</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002966882624871534</v>
+        <v>0.08962499778150913</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002815375813007793</v>
+        <v>0.02172253553758007</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002855394401103266</v>
+        <v>0.07232629067457071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003677748585038001</v>
+        <v>0.001886809246219497</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003674744582635022</v>
+        <v>0.001648299554604903</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003677616607705861</v>
+        <v>0.001886809246219497</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003649171432922771</v>
+        <v>0.001790817847928812</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003649171432922771</v>
+        <v>0.001790817847928812</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003673654714888571</v>
+        <v>0.001882715376070063</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003677748585038001</v>
+        <v>0.001886809246219497</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00365139657778904</v>
+        <v>0.001860457238970535</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003677748585038001</v>
+        <v>0.001886809246219497</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003677748585038001</v>
+        <v>0.001886809246219497</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003677748585038001</v>
+        <v>0.001886809246219497</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005765691605476737</v>
+        <v>0.002841669375381193</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00881326073769583</v>
+        <v>0.002753579018363999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009450472131752865</v>
+        <v>0.002854394960189429</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007955349721173517</v>
+        <v>0.002639821923523765</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005834832733933202</v>
+        <v>0.002812360300715149</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008813538469241589</v>
+        <v>0.00283757550523176</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008817632339394744</v>
+        <v>0.004882068985960434</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008791280332142064</v>
+        <v>0.004675869361100186</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008818232128258425</v>
+        <v>0.002966882624871535</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005709000239961961</v>
+        <v>0.002815375813007797</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01200563963040368</v>
+        <v>0.002855394401103267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007951241525159946</v>
+        <v>0.003677748585038007</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009881029632084759</v>
+        <v>0.003674744582635029</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009884034511382115</v>
+        <v>0.003677616607705866</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01208808216605154</v>
+        <v>0.003649171432922781</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009857680534252551</v>
+        <v>0.003649171432922781</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009879939764338321</v>
+        <v>0.003673654714888576</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009884033634487758</v>
+        <v>0.003677748585038007</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009857681627238773</v>
+        <v>0.003651396577789044</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009884033634487754</v>
+        <v>0.003677748585038007</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008764166664501211</v>
+        <v>0.003677748585038007</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009884033634487754</v>
+        <v>0.003677748585038007</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01297647063303008</v>
+        <v>0.005765691605476739</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004321332306626831</v>
+        <v>0.008813260737695847</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03154135758051139</v>
+        <v>0.009450472131752884</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01280499326453414</v>
+        <v>0.007955349721173524</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01280499326453414</v>
+        <v>0.005834832733933206</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01304427234481765</v>
+        <v>0.008813538469241598</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03064465934144673</v>
+        <v>0.008817632339394752</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01280499326453414</v>
+        <v>0.008791280332142069</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01768145314740404</v>
+        <v>0.008818232128258436</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01708647292303034</v>
+        <v>0.005709000239961965</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02062228674485029</v>
+        <v>0.01200563963040369</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.007951241525159969</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.009881029632084785</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.009884034511382143</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01208808216605159</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.009857680534252572</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.009879939764338345</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.009884033634487775</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.009857681627238797</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.009884033634487775</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.008764166664501236</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.009884033634487775</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01297647063303008</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004321332306626831</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.03154135758051139</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01280499326453414</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01280499326453414</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01304427234481765</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.03064465934144673</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01280499326453414</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01768145314740407</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01708647292303037</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.02062228674485029</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>0.01282030330955895</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.00427206226372921</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C11" t="n">
+        <v>0.004272062263729212</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.03140370114696397</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.01274470477401195</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01274470477401195</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="E11" t="n">
+        <v>0.01274470477401196</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01274470477401196</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.01321111924810603</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.03103993077029079</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01274470477401195</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="H11" t="n">
+        <v>0.0310399307702908</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01274470477401196</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.01847926407473056</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.01704568839691958</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="K11" t="n">
+        <v>0.01704568839691961</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.02107513776456153</v>
       </c>
     </row>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,320 +3367,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005198466382038585</v>
+        <v>0.0127166927912298</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005127845214557051</v>
+        <v>0.004221599940338995</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007112503526792922</v>
+        <v>0.03155701130136027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0090817935826358</v>
+        <v>0.01276210188625229</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0090817935826358</v>
+        <v>0.01276210188625229</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009517418256800532</v>
+        <v>0.01338350593690095</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01047196825025019</v>
+        <v>0.03155984507081035</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0090817935826358</v>
+        <v>0.01276210188625229</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03248225024539839</v>
+        <v>0.01917567312312958</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007080222848930491</v>
+        <v>0.01708570251403352</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01447913099938982</v>
+        <v>0.02096730110994778</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001754669938296523</v>
+        <v>0.01294969813016763</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001583517109753743</v>
+        <v>0.004319363717441001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001754669938296523</v>
+        <v>0.03208702306877483</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001796964356560991</v>
+        <v>0.01299106980563046</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00179696435656099</v>
+        <v>0.01299106980563046</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00175152531961315</v>
+        <v>0.01362193510871606</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001754669938296523</v>
+        <v>0.03208702306877483</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001734429856190042</v>
+        <v>0.01299106980563046</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001754669938296523</v>
+        <v>0.01948036018157213</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001754669938296523</v>
+        <v>0.01738564175068033</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001754669938296523</v>
+        <v>0.02132208169336817</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00267296130182368</v>
+        <v>0.005198466382038571</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002626612840408717</v>
+        <v>0.005127845214557038</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004340880291037994</v>
+        <v>0.007112503526792904</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002527037261642961</v>
+        <v>0.009081793582635804</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002661118796918112</v>
+        <v>0.009081793582635804</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002669816683140303</v>
+        <v>0.009517418256800671</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004462816965655168</v>
+        <v>0.01047196825025017</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004303395819163075</v>
+        <v>0.009081793582635804</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004343026123457692</v>
+        <v>0.03248225024539835</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002666931222593026</v>
+        <v>0.00708022284893049</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00266608067250458</v>
+        <v>0.0144791309993898</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003291057149198619</v>
+        <v>0.001754669938296527</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003289065050191364</v>
+        <v>0.001583517109753738</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003290932262879971</v>
+        <v>0.001754669938296526</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003269534039581218</v>
+        <v>0.001796964356560991</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003269534039581218</v>
+        <v>0.001796964356560992</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003287912530515247</v>
+        <v>0.001751525319613137</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003291057149198619</v>
+        <v>0.001754669938296527</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003270817067092147</v>
+        <v>0.001734429856190046</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003291057149198619</v>
+        <v>0.001754669938296527</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003291057149198619</v>
+        <v>0.001754669938296527</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003291057149198619</v>
+        <v>0.001754669938296527</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005161504581047074</v>
+        <v>0.002672961301823665</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007845751202875765</v>
+        <v>0.002626612840408718</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008405414219182681</v>
+        <v>0.004340880291037969</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007092722057283983</v>
+        <v>0.002527037261642945</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00522574060965474</v>
+        <v>0.002661118796918111</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007845146839153539</v>
+        <v>0.002669816683140298</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007848291457842538</v>
+        <v>0.004462816965655141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007828051375730427</v>
+        <v>0.004303395819163079</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007848819483759897</v>
+        <v>0.004343026123457689</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005111596135872943</v>
+        <v>0.002666931222593115</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01065486501166152</v>
+        <v>0.002666080672504569</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006535427414977757</v>
+        <v>0.003291057149198619</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008082833249957249</v>
+        <v>0.00328906505019136</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008084826294991476</v>
+        <v>0.003290932262879968</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00985255817316741</v>
+        <v>0.003269534039581219</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008064585017132709</v>
+        <v>0.003269534039581219</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008081680730281135</v>
+        <v>0.003287912530515236</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0080848253489645</v>
+        <v>0.003291057149198619</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008064585266858031</v>
+        <v>0.003270817067092142</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0080848253489645</v>
+        <v>0.003291057149198619</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007187098498952584</v>
+        <v>0.003291057149198619</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0080848253489645</v>
+        <v>0.003291057149198619</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01287524622692726</v>
+        <v>0.005161504581047065</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004245569685165849</v>
+        <v>0.007845751202875768</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03196251147943562</v>
+        <v>0.008405414219182641</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01281992243581753</v>
+        <v>0.007092722057283984</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01281992243581753</v>
+        <v>0.005225740609654745</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01344455845152682</v>
+        <v>0.007845146839153515</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0319066131772968</v>
+        <v>0.007848291457842507</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01281992243581753</v>
+        <v>0.007828051375730428</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01877521331686114</v>
+        <v>0.007848819483759895</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01726249802772416</v>
+        <v>0.005111596135872924</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02106109238040337</v>
+        <v>0.01065486501166148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.006535427414977754</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.008082833249957261</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.008084826294991474</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.009852558173167412</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.008064585017132709</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.008081680730281144</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.008084825348964507</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.008064585266858037</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.008084825348964507</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.007187098498952593</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.008084825348964507</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01287524622692726</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004245569685165849</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.03196251147943563</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01281992243581753</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01281992243581753</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01344455845152681</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0319066131772968</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01281992243581753</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01877521331686112</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01726249802772416</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.02106109238040337</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01268281693799131</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.004188023420486175</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.0126828169379913</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.004188023420486172</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.03150035813141604</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>0.01268422928757309</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01268422928757309</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.01330279899261397</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.03147775799525565</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.01330279899261398</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.03147775799525564</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.01268422928757309</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.01885482905251636</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01702967172765272</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="J11" t="n">
+        <v>0.01885482905251635</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01702967172765271</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.02084855014082519</v>
       </c>
     </row>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004787601138402704</v>
+        <v>0.01252707715811236</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005026994911117036</v>
+        <v>0.004159435486853854</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006280820107376094</v>
+        <v>0.03149677653764446</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00705905353468651</v>
+        <v>0.01249690584719172</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00705905353468651</v>
+        <v>0.01249690584719172</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006272650339458395</v>
+        <v>0.01322205338609663</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007278489898038296</v>
+        <v>0.03149723442843536</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00705905353468651</v>
+        <v>0.01249690584719172</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01065386674301335</v>
+        <v>0.01835746472226389</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004726061164590024</v>
+        <v>0.01707180285625362</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006341881474188886</v>
+        <v>0.02085686435445723</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001715260004036587</v>
+        <v>0.0127578238826195</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001567164163008963</v>
+        <v>0.004256612606050521</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001715260004036587</v>
+        <v>0.03202709817053298</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001735374915828841</v>
+        <v>0.01272430671518655</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001735374915828841</v>
+        <v>0.01272430671518655</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001712698551005803</v>
+        <v>0.01346193925628207</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001715260004036587</v>
+        <v>0.03202709817053298</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001698887514830004</v>
+        <v>0.01272430671518655</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001715260004036587</v>
+        <v>0.01867413645386787</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001715260004036587</v>
+        <v>0.01737458024659525</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001715260004036587</v>
+        <v>0.02121863239412464</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004268627390457121</v>
+        <v>0.004787601138402737</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002610500526610423</v>
+        <v>0.005026994911117038</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002637706488720824</v>
+        <v>0.00628082010737612</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002501700226981076</v>
+        <v>0.007059053534686516</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002636958291846589</v>
+        <v>0.007059053534686516</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004266065937426365</v>
+        <v>0.006272650339458424</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00263931102245253</v>
+        <v>0.007278489898038325</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004252254901250523</v>
+        <v>0.007059053534686516</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002748418093804572</v>
+        <v>0.01065386674301337</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002648745385733796</v>
+        <v>0.004726061164590066</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002636162290615605</v>
+        <v>0.006341881474188897</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003183400990814457</v>
+        <v>0.001715260004036621</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003181624251000153</v>
+        <v>0.001567164163008946</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003183275443933307</v>
+        <v>0.001715260004036621</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003165521453556899</v>
+        <v>0.001735374915828843</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003165521453556899</v>
+        <v>0.001735374915828844</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00318083953778368</v>
+        <v>0.001712698551005853</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003183400990814457</v>
+        <v>0.001715260004036621</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003167028501607856</v>
+        <v>0.001698887514830006</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003183400990814457</v>
+        <v>0.001715260004036621</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003183400990814457</v>
+        <v>0.001715260004036621</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003183400990814457</v>
+        <v>0.001715260004036621</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005009888663704411</v>
+        <v>0.00426862739045714</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007606034390898212</v>
+        <v>0.002610500526610448</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008147446270319972</v>
+        <v>0.00263770648872084</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006880771545345494</v>
+        <v>0.002501700226981097</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005075066828264366</v>
+        <v>0.002636958291846582</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007606027403659823</v>
+        <v>0.004266065937426376</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007608588856696102</v>
+        <v>0.002639311022452537</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007592216367483974</v>
+        <v>0.004252254901250528</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007609099571085762</v>
+        <v>0.002748418093804576</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004961616473902781</v>
+        <v>0.0026487453857338</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01032314850361841</v>
+        <v>0.00263616229061564</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006031524560798186</v>
+        <v>0.003183400990814465</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007443379053544851</v>
+        <v>0.00318162425100015</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007445156657496279</v>
+        <v>0.003183275443933321</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009060084258291327</v>
+        <v>0.003165521453556899</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007428783067693092</v>
+        <v>0.003165521453556899</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00744259434032838</v>
+        <v>0.003180839537783697</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007445155793359128</v>
+        <v>0.003183400990814465</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007428783304152535</v>
+        <v>0.003167028501607849</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007445155793359128</v>
+        <v>0.003183400990814465</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006626092668907794</v>
+        <v>0.003183400990814465</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007445155793359128</v>
+        <v>0.003183400990814465</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01269249558780865</v>
+        <v>0.005009888663704417</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004184656732816542</v>
+        <v>0.007606034390898205</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03192224295053349</v>
+        <v>0.008147446270319977</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01260147207500169</v>
+        <v>0.006880771545345487</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01260147207500169</v>
+        <v>0.005075066828264362</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0133607977355599</v>
+        <v>0.007606027403659811</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03191482320120553</v>
+        <v>0.007608588856696106</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01260147207500169</v>
+        <v>0.00759221636748397</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01847400408178218</v>
+        <v>0.007609099571085785</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01730800078548639</v>
+        <v>0.004961616473902796</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0211286983124853</v>
+        <v>0.0103231485036184</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.006031524560798192</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.007443379053544847</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.007445156657496267</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.009060084258291324</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.007428783067693097</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.007442594340328385</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.007445155793359159</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.007428783304152536</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.007445155793359159</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.006626092668907772</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.007445155793359159</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01269249558780867</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004184656732816538</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0319222429505335</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01260147207500169</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01260147207500169</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01336079773555991</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.03191482320120554</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01260147207500169</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01847400408178219</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01730800078548638</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0211286983124853</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>0.01249735257578452</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.004126695335222629</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.03144906707839096</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="C11" t="n">
+        <v>0.004126695335222626</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.03144906707839094</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.01244101569445684</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01244101569445684</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.01317603367184914</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G11" t="n">
+        <v>0.01317603367184915</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.03144614895959225</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>0.01244101569445684</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>0.01826640385518087</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>0.01704150898927293</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.02081594406070838</v>
+      <c r="L11" t="n">
+        <v>0.02081594406070841</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007103434848175363</v>
+        <v>0.01276003483294005</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005532287927936906</v>
+        <v>0.004270240289080364</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01142022564100619</v>
+        <v>0.03162138449806148</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01225451085715714</v>
+        <v>0.01281266890735597</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01225451085715714</v>
+        <v>0.01281266890735597</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01815712033422158</v>
+        <v>0.01343411267273905</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06630544994135425</v>
+        <v>0.03167467083023637</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01225451085715714</v>
+        <v>0.01281266890735597</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02868434113430156</v>
+        <v>0.01915976542083183</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01292335779125231</v>
+        <v>0.01713079920426664</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05838504761100134</v>
+        <v>0.02164202314861346</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001835046932388057</v>
+        <v>0.01299207275683034</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001607930547774586</v>
+        <v>0.004368765103869546</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001835046932388057</v>
+        <v>0.03214814777811615</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001750123958038375</v>
+        <v>0.01303964951158123</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001750123958038376</v>
+        <v>0.01303964951158123</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00183137694511261</v>
+        <v>0.0136646188068817</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001835046932388057</v>
+        <v>0.03214814777811615</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001811388639970369</v>
+        <v>0.01303964951158123</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001835046932388057</v>
+        <v>0.01947032718205377</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001835046932388057</v>
+        <v>0.01742548278710113</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001835046932388057</v>
+        <v>0.02196522189147233</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00274192368119252</v>
+        <v>0.007103434848175355</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002676149818165934</v>
+        <v>0.005532287927936909</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002735658204615726</v>
+        <v>0.01142022564100617</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002563433306903294</v>
+        <v>0.01225451085715714</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002716560433817553</v>
+        <v>0.01225451085715714</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002738253693917093</v>
+        <v>0.01815712033422194</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004711932119390473</v>
+        <v>0.06630544994135415</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002718265388774842</v>
+        <v>0.01225451085715714</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002843807945302514</v>
+        <v>0.02868434113430163</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002718714568802379</v>
+        <v>0.01292335779125226</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002751903437710997</v>
+        <v>0.0583850476110013</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003530631108976274</v>
+        <v>0.00183504693238806</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003528272599642559</v>
+        <v>0.001607930547774595</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003530499686440916</v>
+        <v>0.00183504693238806</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003505179885141848</v>
+        <v>0.001750123958038371</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003505179885141848</v>
+        <v>0.001750123958038376</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003526961121700844</v>
+        <v>0.001831376945112631</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003530631108976274</v>
+        <v>0.00183504693238806</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003506972816558557</v>
+        <v>0.001811388639970371</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003530631108976274</v>
+        <v>0.00183504693238806</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003530631108976274</v>
+        <v>0.00183504693238806</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003530631108976274</v>
+        <v>0.00183504693238806</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00555380651379861</v>
+        <v>0.00274192368119253</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008481471662969049</v>
+        <v>0.002676149818165956</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009092571244205719</v>
+        <v>0.002735658204615697</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007658643185182562</v>
+        <v>0.002563433306903276</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00562206530107049</v>
+        <v>0.002716560433817549</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008481138834936128</v>
+        <v>0.002738253693917103</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008484808822215164</v>
+        <v>0.004711932119390466</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008461150529793814</v>
+        <v>0.002718265388774836</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00848538484322545</v>
+        <v>0.002843807945302472</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005499361641626119</v>
+        <v>0.002718714568802354</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01154648581509294</v>
+        <v>0.002751903437710988</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007513877490128573</v>
+        <v>0.003530631108976245</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009329315218013456</v>
+        <v>0.003528272599642559</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009331674249963298</v>
+        <v>0.003530499686440901</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01140571298639453</v>
+        <v>0.00350517988514185</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009308014446759267</v>
+        <v>0.00350517988514185</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009328003740071731</v>
+        <v>0.003526961121700816</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009331673727347164</v>
+        <v>0.003530631108976245</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009308015434929448</v>
+        <v>0.003506972816558552</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009331673727347164</v>
+        <v>0.003530631108976245</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00827843566827628</v>
+        <v>0.003530631108976245</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009331673727347164</v>
+        <v>0.003530631108976245</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.012880608696676</v>
+        <v>0.005553806513798598</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004291681786235066</v>
+        <v>0.008481471662969055</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03193255233863061</v>
+        <v>0.009092571244205717</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01280677093188643</v>
+        <v>0.007658643185182569</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01280677093188643</v>
+        <v>0.005622065301070491</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01330466873369814</v>
+        <v>0.008481138834936081</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03084110019057143</v>
+        <v>0.008484808822215178</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01280677093188643</v>
+        <v>0.008461150529793815</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01888759825989961</v>
+        <v>0.008485384843225439</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01717626247295973</v>
+        <v>0.005499361641626117</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02084264631578013</v>
+        <v>0.01154648581509292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.007513877490128567</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.009329315218013456</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.009331674249963277</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01140571298639454</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.009308014446759268</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.009328003740071724</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.009331673727347143</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.009308015434929451</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.009331673727347143</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.008278435668276277</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.009331673727347143</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01288060869667599</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.00429168178623507</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.03193255233863061</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01280677093188643</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01280677093188643</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01330466873369814</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.03084110019057143</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01280677093188643</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01888759825989962</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01717626247295971</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.02084264631578012</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01270931833035496</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.004235167133906716</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.01270931833035494</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.004235167133906717</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.03152328788603367</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>0.01270670841145483</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01270670841145483</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G11" t="n">
         <v>0.01327033424234771</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>0.03107996001259004</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>0.01270670841145483</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.0188946219042048</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01701740316711429</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.02113124768423744</v>
+      <c r="J11" t="n">
+        <v>0.01889462190420482</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01701740316711428</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.02113124768423743</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,321 +4795,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00535408442665974</v>
+        <v>0.01187428078241977</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00517235294711183</v>
+        <v>0.004193437526145133</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006501485706427678</v>
+        <v>0.031507860328733</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008350195041873364</v>
+        <v>0.0127005373005058</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008350195041873364</v>
+        <v>0.0127005373005058</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006707667015884857</v>
+        <v>0.01325569831148559</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007554173753358338</v>
+        <v>0.03150835051956692</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008350195041873364</v>
+        <v>0.0127005373005058</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01057396227069986</v>
+        <v>0.01907155441524814</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005967534082374179</v>
+        <v>0.01692012665161818</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006730537782381709</v>
+        <v>0.02091823582988739</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001725946124658029</v>
+        <v>0.01209383774989576</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001559300971515469</v>
+        <v>0.004290828924140272</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001725946124658029</v>
+        <v>0.03203793534981106</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001772047360134173</v>
+        <v>0.01292948989296702</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001772047360134173</v>
+        <v>0.01292948989296702</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001722914569032446</v>
+        <v>0.01349545288088659</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001725946124658029</v>
+        <v>0.03203793534981106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001706431343308607</v>
+        <v>0.01292948989296702</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001725946124658029</v>
+        <v>0.01939951055461918</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001725946124658029</v>
+        <v>0.01721886653589125</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001725946124658029</v>
+        <v>0.02128041318852954</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00426692555197127</v>
+        <v>0.005354084426659751</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002595980857572844</v>
+        <v>0.005172352947111816</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002637172202506244</v>
+        <v>0.006501485706427687</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002496893742078495</v>
+        <v>0.008350195041873364</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002626680198691946</v>
+        <v>0.008350195041873364</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002634653752401187</v>
+        <v>0.006707667015885042</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004402230362985153</v>
+        <v>0.007554173753358355</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004247410770621846</v>
+        <v>0.008350195041873364</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002734974356471034</v>
+        <v>0.01057396227069985</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002633082506303072</v>
+        <v>0.005967534082374179</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002628500010218411</v>
+        <v>0.006730537782381741</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00319922332020143</v>
+        <v>0.001725946124658049</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003197375124349455</v>
+        <v>0.001559300971515467</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003199098327213346</v>
+        <v>0.001725946124658049</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003178934963023399</v>
+        <v>0.001772047360134174</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003178934963023399</v>
+        <v>0.001772047360134175</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003196191764575841</v>
+        <v>0.001722914569032443</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00319922332020143</v>
+        <v>0.001725946124658049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003179708538852003</v>
+        <v>0.001706431343308607</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00319922332020143</v>
+        <v>0.001725946124658047</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00319922332020143</v>
+        <v>0.001725946124658049</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00319922332020143</v>
+        <v>0.001725946124658049</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005022010809132915</v>
+        <v>0.004266925551971269</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007622888743013432</v>
+        <v>0.002595980857572869</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00816452240637483</v>
+        <v>0.002637172202506254</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006893359591802231</v>
+        <v>0.002496893742078493</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005084613967108603</v>
+        <v>0.002626680198691955</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007621782617816179</v>
+        <v>0.002634653752401194</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00762481417344743</v>
+        <v>0.004402230362985141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007605299392092339</v>
+        <v>0.004247410770621853</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007625325694220648</v>
+        <v>0.002734974356471027</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004973662400818486</v>
+        <v>0.002633082506303111</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01034365992591161</v>
+        <v>0.002628500010218412</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006407180663522114</v>
+        <v>0.003199223320201413</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007921286765654612</v>
+        <v>0.003197375124349456</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007923135841584</v>
+        <v>0.003199098327213352</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009652999838470185</v>
+        <v>0.003178934963023401</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00790361997718996</v>
+        <v>0.003178934963023401</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007920103405880992</v>
+        <v>0.003196191764575843</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007923134961506578</v>
+        <v>0.003199223320201413</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007903620180157158</v>
+        <v>0.003179708538852001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007923134961506578</v>
+        <v>0.003199223320201413</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006014277675361981</v>
+        <v>0.003199223320201413</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007923134961506578</v>
+        <v>0.003199223320201413</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01201542540907252</v>
+        <v>0.005022010809132893</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004215689634909166</v>
+        <v>0.007622888743013417</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03192790107988223</v>
+        <v>0.008164522406374842</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01277560070983339</v>
+        <v>0.006893359591802224</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01277560070983339</v>
+        <v>0.005084613967108604</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01338420255340505</v>
+        <v>0.007621782617816192</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03191991406148725</v>
+        <v>0.007624814173447445</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01277560070983339</v>
+        <v>0.007605299392092346</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01920142583412651</v>
+        <v>0.007625325694220648</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01712232768857952</v>
+        <v>0.00497366240081849</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02118246476235975</v>
+        <v>0.01034365992591164</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.006407180663522094</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.007921286765654612</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.00792313584158401</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.009652999838470183</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.007903619977189963</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.007920103405881</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.00792313496150659</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.007903620180157176</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.00792313496150659</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.006014277675361974</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.00792313496150659</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01201542540907253</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004215689634909169</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.03192790107988223</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01277560070983338</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01277560070983338</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01338420255340504</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.03191991406148725</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01277560070983338</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01920142583412651</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01712232768857951</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.02118246476235976</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01183860291745991</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.004159248910090277</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.0118386029174599</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.00415924891009027</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.03145779438525696</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>0.01263051723176428</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01263051723176428</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.01320507905794775</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.03145465045726807</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.01320507905794773</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.03145465045726806</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.01263051723176428</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>0.01898142523616541</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.0168762011684403</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.02087366898383702</v>
+      <c r="K11" t="n">
+        <v>0.01687620116844029</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.020873668983837</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,320 +5271,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004927105700420282</v>
+        <v>0.009587765262855636</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004990399476253659</v>
+        <v>0.004135174014235911</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005883198021152699</v>
+        <v>0.03145616342031531</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00662317905422206</v>
+        <v>0.01245082720502516</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00662317905422206</v>
+        <v>0.01245082720502516</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005840995567802894</v>
+        <v>0.01292088197374282</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006879947514365162</v>
+        <v>0.03145666628285406</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00662317905422206</v>
+        <v>0.01245082720502516</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009120230598555584</v>
+        <v>0.01829968907632123</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005356066019896508</v>
+        <v>0.01696739016030807</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006221929178749623</v>
+        <v>0.02082280161103867</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001692398078956098</v>
+        <v>0.00977168090305601</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001546963105914289</v>
+        <v>0.004232082958923917</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001692398078956098</v>
+        <v>0.03198638018479957</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001714372924653482</v>
+        <v>0.01267807874664023</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001714372924653482</v>
+        <v>0.01267807874664023</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001689997871745951</v>
+        <v>0.01315654743323986</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001692398078956098</v>
+        <v>0.03198638018479957</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001677097129221193</v>
+        <v>0.01267807874664023</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001692398078956098</v>
+        <v>0.0186172492071376</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001692398078956098</v>
+        <v>0.01726783493453986</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001692398078956098</v>
+        <v>0.02118422437499368</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004236507458257716</v>
+        <v>0.004927105700420282</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002593016331446116</v>
+        <v>0.004990399476253663</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00261893437314459</v>
+        <v>0.005883198021152717</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002484790585373179</v>
+        <v>0.006623179054222063</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002619517333004792</v>
+        <v>0.006623179054222063</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002626571021324839</v>
+        <v>0.005840995567803072</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004361080974350312</v>
+        <v>0.006879947514365172</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002613670278800083</v>
+        <v>0.006623179054222063</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004253098410881679</v>
+        <v>0.009120230598555599</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00263222290751666</v>
+        <v>0.005356066019896503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002617750444001794</v>
+        <v>0.006221929178749635</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003108881628687049</v>
+        <v>0.001692398078956092</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003107142245510629</v>
+        <v>0.001546963105914297</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003108755939527991</v>
+        <v>0.001692398078956092</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003092285227884298</v>
+        <v>0.001714372924653482</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003092285227884298</v>
+        <v>0.001714372924653482</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003106481421476908</v>
+        <v>0.001689997871745947</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003108881628687049</v>
+        <v>0.001692398078956092</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003093580678952145</v>
+        <v>0.001677097129221191</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003108881628687049</v>
+        <v>0.001692398078956092</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003108881628687049</v>
+        <v>0.001692398078956092</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003108881628687049</v>
+        <v>0.001692398078956092</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004892427061848089</v>
+        <v>0.004236507458257713</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007417626772023726</v>
+        <v>0.002593016331446116</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007944054346479103</v>
+        <v>0.002618934373144584</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006712842646065438</v>
+        <v>0.002484790585373174</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004956547027072142</v>
+        <v>0.002619517333004794</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007417554762585041</v>
+        <v>0.00262657102132484</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007419954969800909</v>
+        <v>0.004361080974350313</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007404654020060271</v>
+        <v>0.002613670278800089</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007420451696824291</v>
+        <v>0.004253098410881674</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004845476933778659</v>
+        <v>0.00263222290751666</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0100601692136958</v>
+        <v>0.0026177504440018</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005957009240330923</v>
+        <v>0.00310888162868705</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00734980013559574</v>
+        <v>0.003107142245510631</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007351540358933551</v>
+        <v>0.003108755939527986</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008945497436500081</v>
+        <v>0.003092285227884304</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007336238357414715</v>
+        <v>0.003092285227884304</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007349139311562005</v>
+        <v>0.003106481421476907</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007351539518772162</v>
+        <v>0.00310888162868705</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007336238569037242</v>
+        <v>0.003093580678952153</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007351539518772162</v>
+        <v>0.00310888162868705</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006510762100961613</v>
+        <v>0.00310888162868705</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007351539518772162</v>
+        <v>0.00310888162868705</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009702809561004493</v>
+        <v>0.004892427061848084</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004160801085830471</v>
+        <v>0.007417626772023728</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03189091433418982</v>
+        <v>0.007944054346479098</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01256548660904036</v>
+        <v>0.006712842646065441</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01256548660904036</v>
+        <v>0.004956547027072144</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01306533004994506</v>
+        <v>0.007417554762585037</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03188239471852945</v>
+        <v>0.007419954969800914</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01256548660904036</v>
+        <v>0.007404654020060279</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01845234049273591</v>
+        <v>0.007420451696824293</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01718563700937781</v>
+        <v>0.004845476933778664</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02109653736828771</v>
+        <v>0.0100601692136958</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.005957009240330935</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.007349800135595762</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.007351540358933566</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.008945497436500102</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.007336238357414726</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.007349139311562022</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.007351539518772173</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.007336238569037269</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.007351539518772174</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.006510762100961618</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.007351539518772173</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.009702809561004493</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.004160801085830473</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.03189091433418981</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01256548660904036</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01256548660904036</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01306533004994506</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.03188239471852945</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01256548660904037</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01845234049273592</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01718563700937781</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.02109653736828771</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.009556428582742247</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.00410274053481654</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.03141272615405625</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01239959742360737</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01239959742360737</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>0.009556428582742244</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.004102740534816541</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.03141272615405624</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01239959742360736</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01239959742360736</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.01287937777365115</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.03140935256431914</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01239959742360737</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="H11" t="n">
+        <v>0.03140935256431913</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01239959742360736</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.0182246550857356</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.01692998984241006</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="K11" t="n">
+        <v>0.01692998984241009</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.02078290374354555</v>
       </c>
     </row>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,321 +5747,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06345077488167671</v>
+        <v>0.01501337920853302</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03062198606440332</v>
+        <v>0.01493997827367477</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08602154121344371</v>
+        <v>0.01503661132923271</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03062198606440332</v>
+        <v>0.01493997827367477</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03062198606440332</v>
+        <v>0.01493997827367477</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08876207502400651</v>
+        <v>0.01502593972014008</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1894244824514291</v>
+        <v>0.01512995818429198</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03062198606440332</v>
+        <v>0.01493997827367477</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1467683547870894</v>
+        <v>0.01509483874215929</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0445905455326939</v>
+        <v>0.01499076994216102</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08832201248110491</v>
+        <v>0.01502993098323601</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002170093901040796</v>
+        <v>0.01521478943568195</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001935232285084627</v>
+        <v>0.01517830202296189</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002170093901040796</v>
+        <v>0.01521478943568195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001991390055907653</v>
+        <v>0.01517830202296189</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001991390055907652</v>
+        <v>0.01517830202296189</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002166018069272854</v>
+        <v>0.01520299094752872</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002170093901040796</v>
+        <v>0.01521478943568195</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002144238959910436</v>
+        <v>0.01517830202296189</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002170093901040796</v>
+        <v>0.01521478943568195</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002170093901040796</v>
+        <v>0.01521478943568195</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002170093901040796</v>
+        <v>0.01521478943568195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003321575432918575</v>
+        <v>0.06345077488167643</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003178603055135465</v>
+        <v>0.03062198606440343</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00336598833102498</v>
+        <v>0.08602154121344384</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003043491833797404</v>
+        <v>0.03062198606440343</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003282443230742118</v>
+        <v>0.03062198606440343</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003317499601150635</v>
+        <v>0.08876207502400651</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005710944429718903</v>
+        <v>0.1894244824514294</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005530932124469257</v>
+        <v>0.03062198606440343</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003474133724602417</v>
+        <v>0.1467683547870894</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003261636885275806</v>
+        <v>0.04459054553269386</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003410101416176479</v>
+        <v>0.08832201248110473</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004208076905360483</v>
+        <v>0.002170093901040797</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004182221964230141</v>
+        <v>0.001935232285084625</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004207931291394417</v>
+        <v>0.002170093901040797</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004179509206616706</v>
+        <v>0.001991390055907653</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004179509206616706</v>
+        <v>0.001991390055907652</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004204001073592556</v>
+        <v>0.002166018069272851</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004208076905360483</v>
+        <v>0.002170093901040797</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004182221964230141</v>
+        <v>0.002144238959910438</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004208076905360483</v>
+        <v>0.002170093901040797</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004208076905360483</v>
+        <v>0.002170093901040797</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004208076905360483</v>
+        <v>0.002170093901040797</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006479413638493399</v>
+        <v>0.003321575432918565</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00982537607318055</v>
+        <v>0.00317860305513543</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01055251833295686</v>
+        <v>0.003365988331024972</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008902888607986733</v>
+        <v>0.003043491833797402</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006558964312738243</v>
+        <v>0.003282443230742113</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009848910273755325</v>
+        <v>0.003317499601150626</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009852986105523338</v>
+        <v>0.005710944429718894</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009827131164392893</v>
+        <v>0.005530932124469246</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009853649104057879</v>
+        <v>0.003474133724602406</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006416747798431161</v>
+        <v>0.003261636885275815</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01337696463598973</v>
+        <v>0.003410101416176465</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009864787873805372</v>
+        <v>0.004208076905360487</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01224353397023169</v>
+        <v>0.004182221964230135</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01226938972163802</v>
+        <v>0.004207931291394401</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01501838982746909</v>
+        <v>0.004179509206616702</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01224353118079367</v>
+        <v>0.004179509206616702</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01226531307959411</v>
+        <v>0.00420400107359255</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01226938891136205</v>
+        <v>0.004208076905360487</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01224353397023169</v>
+        <v>0.004182221964230135</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01226938891136205</v>
+        <v>0.004208076905360487</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01087615396740369</v>
+        <v>0.004208076905360487</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01226938891136205</v>
+        <v>0.004208076905360487</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0137684816675265</v>
+        <v>0.006479413638493403</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01450630603016532</v>
+        <v>0.009825376073180526</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01328260862908424</v>
+        <v>0.01055251833295686</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01450630603016532</v>
+        <v>0.008902888607986735</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01450630603016532</v>
+        <v>0.006558964312738244</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01325575599586365</v>
+        <v>0.00984891027375534</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01139946380649833</v>
+        <v>0.009852986105523336</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01450630603016532</v>
+        <v>0.009827131164392898</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0120861142660371</v>
+        <v>0.009853649104057876</v>
       </c>
       <c r="K8" t="n">
-        <v>0.014243455517096</v>
+        <v>0.006416747798431157</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01344921196437925</v>
+        <v>0.01337696463598972</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.00986478787380537</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01224353397023168</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01226938972163801</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01501838982746908</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01224353118079366</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0122653130795941</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01226938891136204</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01224353397023168</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01226938891136204</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01087615396740368</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01226938891136204</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01376848166752648</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0145063060301653</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01328260862908422</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0145063060301653</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0145063060301653</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01325575599586363</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01139946380649832</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0145063060301653</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01208611426603711</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01424345551709598</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01344921196437925</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01435530456491292</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01463421795542815</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.01435530456491291</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01463421795542814</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.01415746290473586</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.01463421795542815</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01463421795542815</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01413994161166288</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01339397286429208</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01463421795542815</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01367128156947472</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01454880991374688</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01241739823118823</v>
+      <c r="E11" t="n">
+        <v>0.01463421795542814</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01463421795542814</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01413994161166286</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01339397286429207</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01463421795542814</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0136712815694747</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01454880991374687</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01241739823118822</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04716744173565754</v>
+        <v>0.01495910839575121</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03181714127897251</v>
+        <v>0.01489860452337253</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07644331850867428</v>
+        <v>0.01499479199116633</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03181714127897251</v>
+        <v>0.01489860452337253</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03181714127897251</v>
+        <v>0.01489860452337253</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07771250518033285</v>
+        <v>0.01498400899299249</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1496936545698069</v>
+        <v>0.01506226507060337</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03181714127897251</v>
+        <v>0.01489860452337253</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1146841342519506</v>
+        <v>0.01503126123070026</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0392877473161195</v>
+        <v>0.01495187377406655</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0939676100718371</v>
+        <v>0.01500454833341968</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002084733527045311</v>
+        <v>0.01517545452121129</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001910405473985353</v>
+        <v>0.01513166040362569</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002084733527045309</v>
+        <v>0.01517545452121129</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001959900121430819</v>
+        <v>0.01513166040362569</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00195990012143082</v>
+        <v>0.01513166040362569</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002081221945685417</v>
+        <v>0.01516522947138256</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002084733527045309</v>
+        <v>0.01517545452121129</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00206252698659351</v>
+        <v>0.01513166040362569</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002084733527045309</v>
+        <v>0.01517545452121129</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002084733527045309</v>
+        <v>0.01517545452121129</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002084733527045309</v>
+        <v>0.01517545452121129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003218977675976315</v>
+        <v>0.04716744173565777</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003104833051947395</v>
+        <v>0.03181714127897261</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003258596597518999</v>
+        <v>0.07644331850867435</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002973546422661817</v>
+        <v>0.03181714127897261</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003188001349013997</v>
+        <v>0.03181714127897261</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003215466094616407</v>
+        <v>0.07771250518033292</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005398290820687346</v>
+        <v>0.149693654569807</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005255264903168116</v>
+        <v>0.03181714127897261</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003359745719516503</v>
+        <v>0.1146841342519505</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003182301876143909</v>
+        <v>0.0392877473161195</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003296432207658354</v>
+        <v>0.09396761007183692</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003915955671111878</v>
+        <v>0.002084733527045315</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003893749130660065</v>
+        <v>0.001910405473985352</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003915819882532602</v>
+        <v>0.002084733527045314</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003890744228688891</v>
+        <v>0.001959900121430816</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003890744228688891</v>
+        <v>0.00195990012143082</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003912444089751964</v>
+        <v>0.002081221945685406</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003915955671111878</v>
+        <v>0.002084733527045314</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003893749130660065</v>
+        <v>0.002062526986593506</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003915955671111878</v>
+        <v>0.002084733527045314</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003915955671111878</v>
+        <v>0.002084733527045314</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003915955671111878</v>
+        <v>0.002084733527045314</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005972611184495669</v>
+        <v>0.003218977675976313</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008995108451351728</v>
+        <v>0.003104833051947394</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009651203689254628</v>
+        <v>0.003258596597518996</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008162027055324345</v>
+        <v>0.002973546422661815</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006045272427317931</v>
+        <v>0.003188001349013997</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009015915072520374</v>
+        <v>0.003215466094616419</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009019426653880669</v>
+        <v>0.005398290820687353</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008997220113428479</v>
+        <v>0.005255264903168116</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009020025435656378</v>
+        <v>0.003359745719516512</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005916015023388761</v>
+        <v>0.003182301876143907</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01220208017766773</v>
+        <v>0.003296432207658356</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0085783562526669</v>
+        <v>0.003915955671111864</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01060291807092261</v>
+        <v>0.003893749130660067</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01062512555081365</v>
+        <v>0.003915819882532597</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01296484347212849</v>
+        <v>0.003890744228688892</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01060291588254147</v>
+        <v>0.003890744228688892</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0106216130300145</v>
+        <v>0.003912444089751972</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01062512461137441</v>
+        <v>0.003915955671111864</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01060291807092261</v>
+        <v>0.003893749130660067</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01062512461137441</v>
+        <v>0.003915955671111864</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009439219381184185</v>
+        <v>0.003915955671111864</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01062512461137441</v>
+        <v>0.003915955671111864</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01405457538354193</v>
+        <v>0.005972611184495662</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0143657563219953</v>
+        <v>0.008995108451351725</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01330768150307005</v>
+        <v>0.009651203689254626</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0143657563219953</v>
+        <v>0.008162027055324334</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0143657563219953</v>
+        <v>0.006045272427317929</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01331726262547946</v>
+        <v>0.009015915072520371</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01195527697759339</v>
+        <v>0.009019426653880671</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0143657563219953</v>
+        <v>0.008997220113428477</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01256314835626184</v>
+        <v>0.009020025435656368</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01420729055345842</v>
+        <v>0.005916015023388753</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01313411884692598</v>
+        <v>0.01220208017766773</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.008578356252666898</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01060291807092262</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01062512555081366</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0129648434721285</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01060291588254148</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0106216130300145</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01062512461137442</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01060291807092262</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01062512461137442</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.009439219381184175</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01062512461137442</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01405457538354192</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01436575632199531</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01330768150307004</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01436575632199531</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01436575632199531</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01331726262547946</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01195527697759339</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01436575632199531</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01256314835626183</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0142072905534584</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01313411884692598</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01444910481608179</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.01444910481608177</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.01455011572543921</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.01414494931567265</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.01414494931567262</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.01455011572543921</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01455011572543921</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G11" t="n">
         <v>0.01414317818898565</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.01359707402616029</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="H11" t="n">
+        <v>0.01359707402616028</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.01455011572543921</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.01384265360072248</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01451135608338352</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01256498025921859</v>
+      <c r="J11" t="n">
+        <v>0.01384265360072247</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0145113560833835</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01256498025921857</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04000340417198566</v>
+        <v>0.01475236029604542</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04042864123740608</v>
+        <v>0.01461660312160478</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06265018209929724</v>
+        <v>0.01478102495380708</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04042864123740608</v>
+        <v>0.01461660312160478</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04042864123740608</v>
+        <v>0.01461660312160478</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06794068886157957</v>
+        <v>0.01477814100130589</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1084064685278095</v>
+        <v>0.01482371841175214</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04042864123740608</v>
+        <v>0.01461660312160478</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09714896391398872</v>
+        <v>0.01481191503445208</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03206996890929861</v>
+        <v>0.01474513850673239</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06293568166608257</v>
+        <v>0.01495764914689419</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002094904626450477</v>
+        <v>0.01497285049209471</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001953298113603367</v>
+        <v>0.01483351675448378</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002094904626450477</v>
+        <v>0.01497285049209471</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002001200337374846</v>
+        <v>0.01483351675448378</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002001200337374845</v>
+        <v>0.01483351675448378</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002092009988635556</v>
+        <v>0.01496593400605348</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002094904626450477</v>
+        <v>0.01497285049209471</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0020766195309266</v>
+        <v>0.01483351675448378</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002094904626450477</v>
+        <v>0.01497285049209471</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002094904626450477</v>
+        <v>0.01497285049209471</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002094904626450477</v>
+        <v>0.01497285049209471</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003246901093511738</v>
+        <v>0.04000340417198558</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003172679923459437</v>
+        <v>0.04042864123740612</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003261945322018143</v>
+        <v>0.06265018209929719</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003039348465328668</v>
+        <v>0.04042864123740612</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003229716399945267</v>
+        <v>0.04042864123740612</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005258339254587208</v>
+        <v>0.06794068886157935</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005376172444817642</v>
+        <v>0.1084064685278095</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003228615997987875</v>
+        <v>0.04042864123740612</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005293293274244153</v>
+        <v>0.09714896391398881</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00321505568626943</v>
+        <v>0.03206996890929868</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003314982070317382</v>
+        <v>0.06293568166608293</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003881219593419531</v>
+        <v>0.002094904626450459</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00386293449789567</v>
+        <v>0.001953298113603366</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003881083201104089</v>
+        <v>0.002094904626450459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003859796889507078</v>
+        <v>0.002001200337374843</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003859796889507078</v>
+        <v>0.002001200337374843</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003878324955604626</v>
+        <v>0.002092009988635558</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003881219593419529</v>
+        <v>0.002094904626450459</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00386293449789567</v>
+        <v>0.002076619530926598</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003881219593419529</v>
+        <v>0.002094904626450459</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003881219593419529</v>
+        <v>0.002094904626450459</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003881219593419529</v>
+        <v>0.002094904626450459</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005888004157988376</v>
+        <v>0.003246901093511769</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008843791493069769</v>
+        <v>0.003172679923459395</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009481487194195223</v>
+        <v>0.003261945322018148</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008030002785332616</v>
+        <v>0.003039348465328676</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005962273539566571</v>
+        <v>0.003229716399945268</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008861432581111941</v>
+        <v>0.005258339254587216</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008864327218927425</v>
+        <v>0.005376172444817674</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00884604212340297</v>
+        <v>0.003228615997987836</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008864912146942282</v>
+        <v>0.005293293274244159</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005832717429557824</v>
+        <v>0.003215055686269458</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01197334552762971</v>
+        <v>0.003314982070317397</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007973519996472873</v>
+        <v>0.003881219593419556</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009827449025311914</v>
+        <v>0.003862934497895676</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009845735188555547</v>
+        <v>0.0038810832011041</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01198794334233197</v>
+        <v>0.00385979688950708</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00982744738504065</v>
+        <v>0.00385979688950708</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009842839483020858</v>
+        <v>0.003878324955604641</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009845734120835755</v>
+        <v>0.003881219593419557</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009827449025311914</v>
+        <v>0.003862934497895676</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009845734120835755</v>
+        <v>0.003881219593419557</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008760966353506474</v>
+        <v>0.003881219593419557</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009845734120835755</v>
+        <v>0.003881219593419557</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01400312997691057</v>
+        <v>0.005888004157988418</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01382861280926614</v>
+        <v>0.008843791493069771</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01340318838130059</v>
+        <v>0.009481487194195264</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01382861280926614</v>
+        <v>0.008030002785332615</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01382861280926614</v>
+        <v>0.005962273539566573</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01331902825434068</v>
+        <v>0.008861432581111946</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01255468364081865</v>
+        <v>0.008864327218927459</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01382861280926614</v>
+        <v>0.008846042123402972</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01277246679474019</v>
+        <v>0.008864912146942301</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01415540899886473</v>
+        <v>0.005832717429557843</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009782681274645282</v>
+        <v>0.01197334552762974</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.007973519996472899</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.009827449025311923</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.009845735188555577</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01198794334233198</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.009827447385040662</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.009842839483020902</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.009845734120835808</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.009827449025311923</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.009845734120835808</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.008760966353506506</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.009845734120835808</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01400312997691057</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01382861280926614</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0134031883813006</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01382861280926614</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01382861280926614</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01331902825434069</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01255468364081864</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01382861280926614</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01277246679474019</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01415540899886473</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.009782681274645278</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>0.01431113437132072</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C11" t="n">
         <v>0.01415936862409189</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>0.01406682369117941</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>0.01415936862409189</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01415936862409189</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.01402879363589934</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01372344478818101</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.01402879363589936</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01372344478818102</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.01415936862409189</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.01381073343994899</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>0.01381073343994901</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.01437320002228129</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.0125961056128668</v>
+      <c r="L11" t="n">
+        <v>0.01259610561286681</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01692840543914726</v>
+        <v>0.01470404267485658</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01703099416577251</v>
+        <v>0.01468875498177865</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0277098130502233</v>
+        <v>0.0147177311132994</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01703099416577251</v>
+        <v>0.01468875498177865</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01703099416577251</v>
+        <v>0.01468875498177865</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03530061210928086</v>
+        <v>0.01471956332333449</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06149649393146361</v>
+        <v>0.01475226795520116</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01703099416577251</v>
+        <v>0.01468875498177865</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1132814022720284</v>
+        <v>0.01480331393746937</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02792724091914478</v>
+        <v>0.01471739051361222</v>
       </c>
       <c r="L2" t="n">
-        <v>0.105985479231758</v>
+        <v>0.01472804180439269</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001974645400646819</v>
+        <v>0.01495523800812662</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00177188700525749</v>
+        <v>0.01493988148507806</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001974645400646819</v>
+        <v>0.01495523800812662</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001824924116847684</v>
+        <v>0.01493988148507806</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001824924116847685</v>
+        <v>0.01493988148507806</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001971911005841353</v>
+        <v>0.01494969705518763</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001974645400646819</v>
+        <v>0.01495523800812662</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001957329104235275</v>
+        <v>0.01493988148507806</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001974645400646819</v>
+        <v>0.01495523800812662</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001974645400646819</v>
+        <v>0.01495523800812662</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001974645400646819</v>
+        <v>0.01495523800812662</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004877443730072614</v>
+        <v>0.01692840543914713</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002921403947351709</v>
+        <v>0.01703099416577252</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004931427316455935</v>
+        <v>0.02770981305022326</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002792805383255404</v>
+        <v>0.01703099416577252</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002977076762954861</v>
+        <v>0.01703099416577252</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004874709335267152</v>
+        <v>0.03530061210928088</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00301385159387108</v>
+        <v>0.06149649393146359</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004860127433661069</v>
+        <v>0.01703099416577252</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00492904765295557</v>
+        <v>0.1132814022720287</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002987515662220247</v>
+        <v>0.02792724091914477</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003033442754111236</v>
+        <v>0.1059854792317577</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003709970776608639</v>
+        <v>0.001974645400646817</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003692654480197097</v>
+        <v>0.001771887005257492</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00370982920436234</v>
+        <v>0.001974645400646817</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0036896870457455</v>
+        <v>0.001824924116847686</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0036896870457455</v>
+        <v>0.001824924116847686</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003707236381803173</v>
+        <v>0.001971911005841354</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003709970776608639</v>
+        <v>0.001974645400646818</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003692654480197097</v>
+        <v>0.001957329104235272</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003709970776608639</v>
+        <v>0.001974645400646816</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003709970776608639</v>
+        <v>0.001974645400646817</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003709970776608639</v>
+        <v>0.001974645400646817</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005720688715288281</v>
+        <v>0.004877443730072611</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00865680781016488</v>
+        <v>0.002921403947351694</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009289056159292907</v>
+        <v>0.004931427316455936</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007848689432506124</v>
+        <v>0.002792805383255403</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005795372107694878</v>
+        <v>0.002977076762954863</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008673475247268985</v>
+        <v>0.004874709335267154</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008676209642074556</v>
+        <v>0.003013851593871081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008658893345662909</v>
+        <v>0.004860127433661069</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008676790481614193</v>
+        <v>0.004929047652955572</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005665788397202509</v>
+        <v>0.002987515662220248</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01176349838196122</v>
+        <v>0.003033442754111235</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008308493121966139</v>
+        <v>0.003709970776608643</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0102932473509484</v>
+        <v>0.003692654480197098</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01031056456464722</v>
+        <v>0.003709829204362344</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0126035937542568</v>
+        <v>0.003689687045745503</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01029324626178686</v>
+        <v>0.003689687045745503</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01030782925255448</v>
+        <v>0.003707236381803177</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01031056364735995</v>
+        <v>0.003709970776608643</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0102932473509484</v>
+        <v>0.003692654480197098</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01031056364735995</v>
+        <v>0.003709970776608643</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009150556508016522</v>
+        <v>0.003709970776608643</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01031056364735995</v>
+        <v>0.003709970776608643</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01460894694521026</v>
+        <v>0.005720688715288282</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01459154643657613</v>
+        <v>0.008656807810164875</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0143223883131155</v>
+        <v>0.009289056159292907</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01459154643657613</v>
+        <v>0.007848689432506124</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01459154643657613</v>
+        <v>0.005795372107694883</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01416583220142603</v>
+        <v>0.00867347524726899</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01362415368271173</v>
+        <v>0.008676209642074566</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01459154643657613</v>
+        <v>0.008658893345662909</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01254747649644939</v>
+        <v>0.008676790481614205</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01432987000532755</v>
+        <v>0.005665788397202516</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0128366066500545</v>
+        <v>0.01176349838196121</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.008308493121966127</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0102932473509484</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01031056456464722</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01260359375425679</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01029324626178685</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01030782925255448</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01031056364735995</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0102932473509484</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01031056364735995</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.009150556508016518</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01031056364735995</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01460894694521026</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01459154643657614</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01432238831311551</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01459154643657614</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01459154643657614</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01416583220142604</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01362415368271172</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01459154643657614</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01254747649644938</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01432987000532755</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0128366066500545</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>0.01454647913766549</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C11" t="n">
         <v>0.01453026142463235</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>0.01442978248529703</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>0.01453026142463235</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01453026142463235</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.01436290231684392</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01414662034522333</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.01436290231684391</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01414662034522332</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.01453026142463235</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>0.01370777477657556</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.01443284607940905</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01382622262818832</v>
+      <c r="K11" t="n">
+        <v>0.01443284607940906</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01382622262818833</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,320 +7651,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01281549512995013</v>
+        <v>0.01463061790415516</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01943911558305756</v>
+        <v>0.01461958406574156</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01655882266821836</v>
+        <v>0.01463626981579043</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01943911558305756</v>
+        <v>0.01461958406574156</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01943911558305756</v>
+        <v>0.01461958406574156</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0233937968672574</v>
+        <v>0.01464140942747793</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01247214275224734</v>
+        <v>0.01462947655093697</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01943911558305756</v>
+        <v>0.01461958406574156</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06636150179752122</v>
+        <v>0.01469427129877512</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02485687648570948</v>
+        <v>0.0146466165037518</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01473287029905926</v>
+        <v>0.01463188187321028</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001881170598699895</v>
+        <v>0.01488469549381216</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001746835441367611</v>
+        <v>0.0148646833127366</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001881170598699895</v>
+        <v>0.01488469549381216</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001792359925374821</v>
+        <v>0.0148646833127366</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001792359925374822</v>
+        <v>0.0148646833127366</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001879214900365998</v>
+        <v>0.01488180951397437</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001881170598699895</v>
+        <v>0.01488469549381216</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001868861144859144</v>
+        <v>0.0148646833127366</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001881170598699895</v>
+        <v>0.01488469549381216</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001881170598699895</v>
+        <v>0.01488469549381216</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001881170598699895</v>
+        <v>0.01488469549381216</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004560750890752803</v>
+        <v>0.01281549512995013</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002837869456194276</v>
+        <v>0.01943911558305754</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002878232590194347</v>
+        <v>0.01655882266821835</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002713769022016568</v>
+        <v>0.01943911558305754</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002868102567960106</v>
+        <v>0.01943911558305754</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004558795192418906</v>
+        <v>0.02339379686725713</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004655535530328882</v>
+        <v>0.01247214275224734</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004548441436912047</v>
+        <v>0.01943911558305754</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003002583936680151</v>
+        <v>0.06636150179752107</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00289302075976169</v>
+        <v>0.02485687648570946</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002885096522996145</v>
+        <v>0.01473287029905924</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003403971790811917</v>
+        <v>0.0018811705986999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003391662336971167</v>
+        <v>0.00174683544136761</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00340383885124314</v>
+        <v>0.0018811705986999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00338937936676958</v>
+        <v>0.00179235992537482</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00338937936676958</v>
+        <v>0.00179235992537482</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003402016092478018</v>
+        <v>0.001879214900366002</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003403971790811917</v>
+        <v>0.0018811705986999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003391662336971167</v>
+        <v>0.001868861144859143</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003403971790811917</v>
+        <v>0.0018811705986999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003403971790811917</v>
+        <v>0.0018811705986999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003403971790811917</v>
+        <v>0.0018811705986999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005185108886954845</v>
+        <v>0.004560750890752803</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007784332759136546</v>
+        <v>0.002837869456194263</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008339983559602929</v>
+        <v>0.002878232590194347</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007069820696699554</v>
+        <v>0.002713769022016568</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005254346271420658</v>
+        <v>0.002868102567960106</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007796196341479953</v>
+        <v>0.004558795192418904</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007798152039813495</v>
+        <v>0.004655535530328879</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007785842585973097</v>
+        <v>0.004548441436912043</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007798665573053061</v>
+        <v>0.003002583936680146</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005136570269311432</v>
+        <v>0.002893020759761689</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01052769410768051</v>
+        <v>0.002885096522996142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007107126121122035</v>
+        <v>0.00340397179081192</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008763695421386785</v>
+        <v>0.003391662336971165</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008776006071880345</v>
+        <v>0.00340383885124314</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01068954688415019</v>
+        <v>0.003389379366769577</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00876369516916479</v>
+        <v>0.003389379366769577</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008774049176893645</v>
+        <v>0.003402016092478018</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008776004875227538</v>
+        <v>0.00340397179081192</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008763695421386785</v>
+        <v>0.003391662336971165</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008776004875227538</v>
+        <v>0.00340397179081192</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007809050474213671</v>
+        <v>0.00340397179081192</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008776004875227538</v>
+        <v>0.00340397179081192</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01461823049588637</v>
+        <v>0.005185108886954846</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01441378428614696</v>
+        <v>0.007784332759136546</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01449998077979052</v>
+        <v>0.008339983559602932</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01441378428614696</v>
+        <v>0.007069820696699551</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01441378428614696</v>
+        <v>0.005254346271420652</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01433138531604506</v>
+        <v>0.007796196341479957</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01464683613533156</v>
+        <v>0.007798152039813486</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01441378428614696</v>
+        <v>0.007785842585973089</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01329676008672108</v>
+        <v>0.007798665573053054</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01428356624008107</v>
+        <v>0.005136570269311432</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01459628269087219</v>
+        <v>0.01052769410768051</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.007107126121122031</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.008763695421386764</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.008776006071880331</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01068954688415018</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.008763695169164776</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.00877404917689362</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.008776004875227532</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.008763695421386764</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.008776004875227532</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.007809050474213657</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.008776004875227532</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01461823049588637</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01441378428614695</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01449998077979053</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01441378428614695</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01441378428614695</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01433138531604507</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01464683613533157</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01441378428614695</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01329676008672109</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01428356624008107</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0145962826908722</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01450937548092535</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01441442357171333</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.01446122339489754</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01441442357171333</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01441442357171333</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01439096466332225</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01452124978481548</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01441442357171333</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01397175562809879</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01437310077761889</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="B11" t="n">
+        <v>0.01450937548092536</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01441442357171332</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01446122339489755</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01441442357171332</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01441442357171332</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01439096466332224</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0145212497848155</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01441442357171332</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0139717556280988</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01437310077761888</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.01450065312875553</v>
       </c>
     </row>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01807678237157515</v>
+        <v>0.01445587492898321</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02247941734236921</v>
+        <v>0.01432112871071915</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0131558140809656</v>
+        <v>0.01445002232033664</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02247941734236921</v>
+        <v>0.01432112871071915</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02247941734236921</v>
+        <v>0.01432112871071915</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0210936224652352</v>
+        <v>0.01445776896542554</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01285662718898648</v>
+        <v>0.01444824359101718</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02247941734236921</v>
+        <v>0.01432112871071915</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05548379729993785</v>
+        <v>0.01449878406054448</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02082842343180167</v>
+        <v>0.0144606031453423</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01753587984786013</v>
+        <v>0.01445364820298626</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001882531329955662</v>
+        <v>0.01470054186733163</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001770934422755465</v>
+        <v>0.01455792086381076</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001882531329955662</v>
+        <v>0.01470054186733163</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001815110067441866</v>
+        <v>0.01455792086381076</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001815110067441867</v>
+        <v>0.01455792086381076</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001880699479128632</v>
+        <v>0.01469878241417817</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001882531329955662</v>
+        <v>0.01470054186733163</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001870985370198753</v>
+        <v>0.01455792086381076</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001882531329955662</v>
+        <v>0.01470054186733163</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001882531329955662</v>
+        <v>0.01470054186733163</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001882531329955662</v>
+        <v>0.01470054186733163</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002905887348348756</v>
+        <v>0.01807678237157514</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002869904906933804</v>
+        <v>0.02247941734236922</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002880430178370242</v>
+        <v>0.01315581408096558</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002744131074977734</v>
+        <v>0.02247941734236922</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002890831879118645</v>
+        <v>0.02247941734236922</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002904055497521728</v>
+        <v>0.02109362246523531</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004664746167741368</v>
+        <v>0.01285662718898647</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002894341388591847</v>
+        <v>0.02247941734236922</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003020118932723448</v>
+        <v>0.05548379729993794</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002912667775259442</v>
+        <v>0.0208284234318017</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002901417332679372</v>
+        <v>0.01753587984786013</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003380784782380354</v>
+        <v>0.001882531329955657</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003369238822623442</v>
+        <v>0.001770934422755465</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003380651270156311</v>
+        <v>0.001882531329955657</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003367105615704886</v>
+        <v>0.001815110067441865</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003367105615704886</v>
+        <v>0.001815110067441865</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00337895293155332</v>
+        <v>0.001880699479128627</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003380784782380354</v>
+        <v>0.001882531329955657</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003369238822623442</v>
+        <v>0.001870985370198751</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003380784782380354</v>
+        <v>0.001882531329955657</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003380784782380354</v>
+        <v>0.001882531329955657</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003380784782380354</v>
+        <v>0.001882531329955657</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005136671762496391</v>
+        <v>0.002905887348348759</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007699728447512611</v>
+        <v>0.002869904906933811</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008246791699433107</v>
+        <v>0.002880430178370242</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006995338545598018</v>
+        <v>0.002744131074977754</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005205587313682865</v>
+        <v>0.002890831879118645</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007710814696420259</v>
+        <v>0.002904055497521725</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007712646547246796</v>
+        <v>0.004664746167741361</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007701100587490382</v>
+        <v>0.002894341388591848</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00771315279551705</v>
+        <v>0.003020118932723437</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005088821708819267</v>
+        <v>0.00291266777525943</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01040346760504364</v>
+        <v>0.00290141733267937</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006675630537640402</v>
+        <v>0.003380784782380342</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008210892578670206</v>
+        <v>0.003369238822623444</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00822243958779606</v>
+        <v>0.0033806512701563</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009995876868372767</v>
+        <v>0.003367105615704886</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008210892343322174</v>
+        <v>0.003367105615704886</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008220606687600086</v>
+        <v>0.003378952931553319</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008222438538427114</v>
+        <v>0.003380784782380342</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008210892578670206</v>
+        <v>0.003369238822623444</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008222438538427114</v>
+        <v>0.003380784782380342</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007289851278179646</v>
+        <v>0.003380784782380342</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008222438538427114</v>
+        <v>0.003380784782380342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01429689502816451</v>
+        <v>0.005136671762496385</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01403444473939897</v>
+        <v>0.007699728447512611</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01441972419457993</v>
+        <v>0.0082467916994331</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01403444473939897</v>
+        <v>0.006995338545598024</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01403444473939897</v>
+        <v>0.005205587313682865</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01422092182280372</v>
+        <v>0.007710814696420248</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01446155358805665</v>
+        <v>0.007712646547246777</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01403444473939897</v>
+        <v>0.007701100587490396</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01340786654430863</v>
+        <v>0.007713152795517046</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01419835016472509</v>
+        <v>0.005088821708819266</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01448488094716845</v>
+        <v>0.01040346760504363</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.006675630537640405</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.00821089257867021</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.008222439587796065</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.009995876868372779</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.008210892343322188</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.008220606687600092</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.008222438538427121</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.00821089257867021</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.008222438538427117</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.007289851278179646</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.008222438538427117</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01429689502816451</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01403444473939897</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01441972419457993</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01403444473939897</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01403444473939897</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01422092182280372</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01446155358805664</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01403444473939897</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01340786654430863</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0141983501647251</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01448488094716844</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01427221433081604</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.01427221433081603</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.01408294540589233</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.0143222493843218</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.01432224938432179</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.01408294540589233</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01408294540589233</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G11" t="n">
         <v>0.01424034087349882</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.01433950316233661</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="H11" t="n">
+        <v>0.0143395031623366</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.01408294540589233</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.01391061266905719</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01423210432026633</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01434894469454066</v>
+      <c r="J11" t="n">
+        <v>0.01391061266905718</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01423210432026632</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01434894469454065</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04203748101057057</v>
+        <v>0.01490315630954538</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02762701162192967</v>
+        <v>0.01484793207645368</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07899608625087821</v>
+        <v>0.0149464422077916</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02762701162192967</v>
+        <v>0.01484793207645368</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02762701162192967</v>
+        <v>0.01484793207645368</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07580185862133827</v>
+        <v>0.01492933368884729</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1702843807430717</v>
+        <v>0.015039517253549</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02762701162192967</v>
+        <v>0.01484793207645368</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1157355039183064</v>
+        <v>0.01497634813448643</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04148189954110496</v>
+        <v>0.01490217626459751</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06423113576637009</v>
+        <v>0.01511905934715093</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002113360091671459</v>
+        <v>0.01512753764201522</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001884492281738846</v>
+        <v>0.01508845533937091</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002113360091671459</v>
+        <v>0.01512753764201522</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001939968680863803</v>
+        <v>0.01508845533937091</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001939968680863797</v>
+        <v>0.01508845533937091</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002109548616160937</v>
+        <v>0.01511703761572467</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002113360091671459</v>
+        <v>0.01512753764201522</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002089181654001942</v>
+        <v>0.01508845533937091</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002113360091671459</v>
+        <v>0.01512753764201522</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002113360091671459</v>
+        <v>0.01512753764201522</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002113360091671459</v>
+        <v>0.01512753764201522</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003234933687007746</v>
+        <v>0.04203748101057053</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003105171554694619</v>
+        <v>0.02762701162192949</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003288159746947841</v>
+        <v>0.07899608625087833</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00297273675694777</v>
+        <v>0.02762701162192949</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003198794479828963</v>
+        <v>0.02762701162192949</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005377841998331102</v>
+        <v>0.07580185862133855</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005551387412938718</v>
+        <v>0.1702843807430718</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005357475036172107</v>
+        <v>0.02762701162192949</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005439426550499915</v>
+        <v>0.1157355039183064</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003187018535465832</v>
+        <v>0.04148189954110499</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00331208552632999</v>
+        <v>0.0642311357663706</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004043112418161143</v>
+        <v>0.002113360091671455</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004018933980491625</v>
+        <v>0.001884492281738841</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004042968365744561</v>
+        <v>0.002113360091671455</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00401601903399125</v>
+        <v>0.001939968680863799</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00401601903399125</v>
+        <v>0.0019399686808638</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004039300942650616</v>
+        <v>0.002109548616160935</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004043112418161143</v>
+        <v>0.002113360091671455</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004018933980491625</v>
+        <v>0.002089181654001937</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004043112418161143</v>
+        <v>0.002113360091671455</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004043112418161143</v>
+        <v>0.002113360091671455</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004043112418161143</v>
+        <v>0.002113360091671455</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006224507236069045</v>
+        <v>0.003234933687007753</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009425305273834398</v>
+        <v>0.003105171554694608</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01012059310870639</v>
+        <v>0.003288159746947843</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008542940286282798</v>
+        <v>0.002972736756947754</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006300965338649</v>
+        <v>0.003198794479828957</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009447651366937508</v>
+        <v>0.005377841998331098</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009451462842448261</v>
+        <v>0.005551387412938738</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009427284404778493</v>
+        <v>0.0053574750361721</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009452097026583575</v>
+        <v>0.005439426550499915</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00616456487946491</v>
+        <v>0.003187018535465817</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01282228780207681</v>
+        <v>0.003312085526329998</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009490603641436453</v>
+        <v>0.004043112418161142</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01177422410307763</v>
+        <v>0.004018933980491622</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01179840308970457</v>
+        <v>0.004042968365744564</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01443737224321572</v>
+        <v>0.004016019033991257</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01177422142094051</v>
+        <v>0.004016019033991257</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0117945910652366</v>
+        <v>0.00403930094265062</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01179840254074717</v>
+        <v>0.004043112418161142</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01177422410307763</v>
+        <v>0.004018933980491622</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01179840254074717</v>
+        <v>0.004043112418161142</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01046125502595026</v>
+        <v>0.004043112418161142</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01179840254074717</v>
+        <v>0.004043112418161142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0141842202966626</v>
+        <v>0.006224507236069043</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01448611223581118</v>
+        <v>0.009425305273834398</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01327797073576356</v>
+        <v>0.01012059310870641</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01448611223581118</v>
+        <v>0.008542940286282793</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01448611223581118</v>
+        <v>0.006300965338648996</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01341339293362306</v>
+        <v>0.009447651366937497</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01139887716181871</v>
+        <v>0.009451462842448259</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01448611223581118</v>
+        <v>0.009427284404778503</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01266977983198151</v>
+        <v>0.009452097026583554</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01420578699998429</v>
+        <v>0.006164564879464909</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009744361121897799</v>
+        <v>0.01282228780207683</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.009490603641436461</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01177422410307763</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01179840308970458</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01443737224321573</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01177422142094051</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01179459106523662</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01179840254074715</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01177422410307763</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01179840254074715</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01046125502595027</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01179840254074715</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0141842202966626</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01448611223581116</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01327797073576356</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01448611223581116</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01448611223581116</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01341339293362306</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01139887716181871</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01448611223581116</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01266977983198151</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01420578699998428</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.009744361121897789</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01447394391123593</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.01447394391123594</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.01457386404478041</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.0141048833712271</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.01410488337122711</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.01457386404478041</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01457386404478041</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.0141541699292976</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01334296485252367</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.01415416992929759</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01334296485252368</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.01457386404478041</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>0.01385806049851168</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>0.01448277678502841</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.01434143366752508</v>
+      <c r="L11" t="n">
+        <v>0.01434143366752509</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,320 +9079,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.009188512898505693</v>
+        <v>0.01473237223986455</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02048889300219785</v>
+        <v>0.01471529871917241</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06352818141056957</v>
+        <v>0.01480314504135557</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02048889300219785</v>
+        <v>0.01471529871917241</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02048889300219785</v>
+        <v>0.01471529871917241</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04520113836556618</v>
+        <v>0.01477002686987247</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02487976493878941</v>
+        <v>0.01475001023059972</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02048889300219785</v>
+        <v>0.01471529871917241</v>
       </c>
       <c r="J2" t="n">
-        <v>0.085811349619662</v>
+        <v>0.01481766356607183</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02005578084967431</v>
+        <v>0.01474644826528868</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3267509925288084</v>
+        <v>0.01474355900272396</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001955118401023402</v>
+        <v>0.01499200645474763</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001799868961973639</v>
+        <v>0.01496047510725522</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001955118401023402</v>
+        <v>0.01499200645474763</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001847171953687356</v>
+        <v>0.01496047510725522</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001847171953687355</v>
+        <v>0.01496047510725522</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001952339072408244</v>
+        <v>0.01498519255235671</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001955118401023402</v>
+        <v>0.01499200645474763</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001937564460421403</v>
+        <v>0.01496047510725522</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001955118401023402</v>
+        <v>0.01499200645474763</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001955118401023402</v>
+        <v>0.01499200645474763</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001955118401023402</v>
+        <v>0.01499200645474763</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004899217635033856</v>
+        <v>0.009188512898505688</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002918772733563274</v>
+        <v>0.02048889300219784</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00307039512355556</v>
+        <v>0.06352818141056948</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002792381277128567</v>
+        <v>0.02048889300219784</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002976026345865683</v>
+        <v>0.02048889300219784</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004896438306418703</v>
+        <v>0.04520113836556623</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00500152334235898</v>
+        <v>0.02487976493878943</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004881663694431862</v>
+        <v>0.02048889300219784</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00312781965075722</v>
+        <v>0.08581134961966208</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00297081660033404</v>
+        <v>0.02005578084967431</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003099248024232899</v>
+        <v>0.3267509925288077</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00359863549562731</v>
+        <v>0.001955118401023401</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003581081555025317</v>
+        <v>0.001799868961973644</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003598501685420911</v>
+        <v>0.001955118401023401</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00357852151039782</v>
+        <v>0.001847171953687356</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00357852151039782</v>
+        <v>0.001847171953687357</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003595856167012154</v>
+        <v>0.001952339072408245</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00359863549562731</v>
+        <v>0.001955118401023401</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003581081555025317</v>
+        <v>0.001937564460421406</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00359863549562731</v>
+        <v>0.001955118401023401</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00359863549562731</v>
+        <v>0.001955118401023401</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00359863549562731</v>
+        <v>0.001955118401023401</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005504846951502575</v>
+        <v>0.004899217635033855</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008280509196174148</v>
+        <v>0.002918772733563254</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008879353091078356</v>
+        <v>0.003070395123555559</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007516270184794154</v>
+        <v>0.002792381277128567</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005574441379037768</v>
+        <v>0.002976026345865685</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008297021805598034</v>
+        <v>0.004896438306418702</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008299801134213044</v>
+        <v>0.005001523342358993</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008282247193611196</v>
+        <v>0.004881663694431864</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008300350418116229</v>
+        <v>0.003127819650757223</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005452929243093175</v>
+        <v>0.002970816600334044</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01121936448385548</v>
+        <v>0.003099248024232897</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007705232525672965</v>
+        <v>0.00359863549562731</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009512718677210227</v>
+        <v>0.003581081555025317</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009530274076900939</v>
+        <v>0.003598501685420912</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01161877662440077</v>
+        <v>0.003578521510397828</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009512717924392114</v>
+        <v>0.003578521510397828</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009527493289197055</v>
+        <v>0.003595856167012161</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009530272617812226</v>
+        <v>0.00359863549562731</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009512718677210227</v>
+        <v>0.003581081555025317</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009530272617812226</v>
+        <v>0.00359863549562731</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008472837834628212</v>
+        <v>0.00359863549562731</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009530272617812226</v>
+        <v>0.00359863549562731</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0148202807766966</v>
+        <v>0.005504846951502586</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01448934213897887</v>
+        <v>0.008280509196174181</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01333779239966726</v>
+        <v>0.008879353091078384</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01448934213897887</v>
+        <v>0.00751627018479418</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01448934213897887</v>
+        <v>0.005574441379037793</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01388684118347725</v>
+        <v>0.008297021805598064</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01446099009315956</v>
+        <v>0.008299801134213081</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01448934213897887</v>
+        <v>0.008282247193611219</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01304812269222055</v>
+        <v>0.00830035041811626</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01452576448350046</v>
+        <v>0.005452929243093194</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007958575260530761</v>
+        <v>0.01121936448385552</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.007705232525672953</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.009512718677210208</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.009530274076900918</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01161877662440075</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.009512717924392095</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.009527493289197057</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.00953027261781221</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.009512718677210208</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.00953027261781221</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.008472837834628221</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.00953027261781221</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01482028077669662</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01448934213897888</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01333779239966728</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01448934213897888</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01448934213897888</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01388684118347727</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01446099009315957</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01448934213897888</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01304812269222056</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01452576448350048</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.007958575260530787</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01465423650909405</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01450093171719497</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.01405047237462658</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01450093171719497</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01450093171719497</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>0.01465423650909407</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01450093171719498</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0140504723746266</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01450093171719498</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01450093171719498</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.01427027349679419</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.0145083960938284</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01450093171719497</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01393319025933201</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01453430668254621</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="H11" t="n">
+        <v>0.01450839609382841</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01450093171719498</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01393319025933202</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01453430668254622</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.01186483686189392</v>
       </c>
     </row>
